--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD699BF-6CC2-4284-B346-4EFCE883627C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4E09A8-C4CF-4EB3-8FA6-3DB29154F8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="8100" yWindow="0" windowWidth="20805" windowHeight="15585" activeTab="3" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="179">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -734,12 +734,36 @@
   <si>
     <t>승인</t>
   </si>
+  <si>
+    <t>쳬셔와 대화를 할때 체셔에 이미지가 그대로 보이는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대화를 할 때 한 마리만 보이게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼저 힌트 봇으로 "2개에 숫자는 반전한다." 로 힌트를 주고 숫자 7, 3이라고 순서대로 찾을 수 있게 만든다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6X6 판을 만들어 A~Z까지 배치 후 힌트로 사용할 알파벳만 7개와 3개를 따로 규정하여 배치하고 그 이외는 랜덤으로 설정한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>힌트로 사용될 기물은 히드라를 토대로 모양을 따 배치된 알파벳 위치에 따라서 머리를 배치하는 것으로 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,6 +839,14 @@
       <b/>
       <sz val="20"/>
       <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -968,7 +1000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1062,6 +1094,21 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1074,36 +1121,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1121,6 +1153,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1649,36 +1687,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -1691,17 +1729,17 @@
       <c r="D3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39" t="s">
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
       <c r="L3" s="21" t="s">
         <v>59</v>
       </c>
@@ -1720,17 +1758,17 @@
       <c r="D4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="35" t="s">
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="36"/>
-      <c r="K4" s="38"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="33"/>
       <c r="L4" s="11" t="s">
         <v>172</v>
       </c>
@@ -1746,17 +1784,17 @@
       <c r="D5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="35" t="s">
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="38"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="33"/>
       <c r="L5" s="11" t="s">
         <v>172</v>
       </c>
@@ -1772,17 +1810,17 @@
       <c r="D6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="35" t="s">
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="38"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="33"/>
       <c r="L6" s="11" t="s">
         <v>172</v>
       </c>
@@ -1798,17 +1836,17 @@
       <c r="D7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
       <c r="H7" s="19"/>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="38"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="33"/>
       <c r="L7" s="11" t="s">
         <v>172</v>
       </c>
@@ -1824,17 +1862,17 @@
       <c r="D8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="19"/>
-      <c r="I8" s="35" t="s">
+      <c r="I8" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="36"/>
-      <c r="K8" s="38"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="33"/>
       <c r="L8" s="11" t="s">
         <v>172</v>
       </c>
@@ -1850,17 +1888,17 @@
       <c r="D9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
       <c r="H9" s="19"/>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="36"/>
-      <c r="K9" s="38"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="33"/>
       <c r="L9" s="11" t="s">
         <v>172</v>
       </c>
@@ -1876,17 +1914,17 @@
       <c r="D10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="19"/>
-      <c r="I10" s="35" t="s">
+      <c r="I10" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="38"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="33"/>
       <c r="L10" s="11" t="s">
         <v>172</v>
       </c>
@@ -1902,17 +1940,17 @@
       <c r="D11" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="35" t="s">
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="36"/>
-      <c r="K11" s="38"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="11" t="s">
         <v>172</v>
       </c>
@@ -1928,17 +1966,17 @@
       <c r="D12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="35" t="s">
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="38"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="33"/>
       <c r="L12" s="11" t="s">
         <v>62</v>
       </c>
@@ -1954,17 +1992,17 @@
       <c r="D13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="35" t="s">
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="38"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="33"/>
       <c r="L13" s="11" t="s">
         <v>60</v>
       </c>
@@ -1980,17 +2018,17 @@
       <c r="D14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="35" t="s">
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="36"/>
-      <c r="K14" s="38"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="11" t="s">
         <v>62</v>
       </c>
@@ -2006,17 +2044,17 @@
       <c r="D15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="35" t="s">
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="38"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="33"/>
       <c r="L15" s="11" t="s">
         <v>172</v>
       </c>
@@ -2032,17 +2070,17 @@
       <c r="D16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="35" t="s">
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="31" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="36"/>
-      <c r="K16" s="38"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="33"/>
       <c r="L16" s="11" t="s">
         <v>172</v>
       </c>
@@ -2058,17 +2096,17 @@
       <c r="D17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="35" t="s">
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="38"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="33"/>
       <c r="L17" s="11" t="s">
         <v>172</v>
       </c>
@@ -2084,17 +2122,17 @@
       <c r="D18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="35" t="s">
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="36"/>
-      <c r="K18" s="38"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="33"/>
       <c r="L18" s="11" t="s">
         <v>172</v>
       </c>
@@ -2110,17 +2148,17 @@
       <c r="D19" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="31" t="s">
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="32"/>
-      <c r="K19" s="33"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="38"/>
       <c r="L19" s="11" t="s">
         <v>60</v>
       </c>
@@ -2136,17 +2174,17 @@
       <c r="D20" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="31" t="s">
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="32"/>
-      <c r="K20" s="33"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="38"/>
       <c r="L20" s="11" t="s">
         <v>60</v>
       </c>
@@ -2162,17 +2200,17 @@
       <c r="D21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="36" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="31" t="s">
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="36" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="32"/>
-      <c r="K21" s="33"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="38"/>
       <c r="L21" s="11" t="s">
         <v>172</v>
       </c>
@@ -2182,17 +2220,25 @@
       <c r="B22" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="33"/>
+      <c r="C22" s="24">
+        <v>46113</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="36" t="s">
+        <v>174</v>
+      </c>
+      <c r="J22" s="37"/>
+      <c r="K22" s="38"/>
       <c r="L22" s="11" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="M22" s="25"/>
     </row>
@@ -2202,13 +2248,13 @@
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="33"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="38"/>
       <c r="L23" s="11" t="s">
         <v>60</v>
       </c>
@@ -2220,13 +2266,13 @@
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="33"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="38"/>
       <c r="L24" s="11" t="s">
         <v>60</v>
       </c>
@@ -2238,13 +2284,13 @@
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="33"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="38"/>
       <c r="L25" s="11" t="s">
         <v>60</v>
       </c>
@@ -2256,13 +2302,13 @@
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="33"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="38"/>
       <c r="L26" s="11" t="s">
         <v>60</v>
       </c>
@@ -2274,13 +2320,13 @@
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="33"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="38"/>
       <c r="L27" s="11" t="s">
         <v>60</v>
       </c>
@@ -2292,13 +2338,13 @@
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="33"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="38"/>
       <c r="L28" s="11" t="s">
         <v>60</v>
       </c>
@@ -2310,13 +2356,13 @@
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="33"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="38"/>
       <c r="L29" s="11" t="s">
         <v>60</v>
       </c>
@@ -2328,13 +2374,13 @@
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="33"/>
+      <c r="E30" s="36"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="38"/>
       <c r="L30" s="11" t="s">
         <v>60</v>
       </c>
@@ -2346,13 +2392,13 @@
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="33"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="38"/>
       <c r="L31" s="11" t="s">
         <v>60</v>
       </c>
@@ -2364,13 +2410,13 @@
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="33"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="38"/>
       <c r="L32" s="11" t="s">
         <v>60</v>
       </c>
@@ -2382,13 +2428,13 @@
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="33"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="38"/>
+      <c r="I33" s="36"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="38"/>
       <c r="L33" s="11" t="s">
         <v>60</v>
       </c>
@@ -2400,13 +2446,13 @@
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="33"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="38"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="38"/>
       <c r="L34" s="11" t="s">
         <v>60</v>
       </c>
@@ -2418,13 +2464,13 @@
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="33"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="38"/>
+      <c r="I35" s="36"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="38"/>
       <c r="L35" s="11" t="s">
         <v>60</v>
       </c>
@@ -2436,13 +2482,13 @@
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="33"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="38"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="38"/>
       <c r="L36" s="11" t="s">
         <v>60</v>
       </c>
@@ -2454,13 +2500,13 @@
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="33"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="38"/>
+      <c r="I37" s="36"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="38"/>
       <c r="L37" s="11" t="s">
         <v>60</v>
       </c>
@@ -2472,13 +2518,13 @@
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="33"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="37"/>
+      <c r="K38" s="38"/>
       <c r="L38" s="11" t="s">
         <v>60</v>
       </c>
@@ -2490,13 +2536,13 @@
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="33"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="37"/>
+      <c r="K39" s="38"/>
       <c r="L39" s="11" t="s">
         <v>60</v>
       </c>
@@ -2508,13 +2554,13 @@
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="33"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="38"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="37"/>
+      <c r="K40" s="38"/>
       <c r="L40" s="11" t="s">
         <v>60</v>
       </c>
@@ -2526,13 +2572,13 @@
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="33"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="38"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="38"/>
       <c r="L41" s="11" t="s">
         <v>60</v>
       </c>
@@ -2544,13 +2590,13 @@
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="33"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="38"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="37"/>
+      <c r="K42" s="38"/>
       <c r="L42" s="11" t="s">
         <v>60</v>
       </c>
@@ -2562,13 +2608,13 @@
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="33"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="36"/>
+      <c r="J43" s="37"/>
+      <c r="K43" s="38"/>
       <c r="L43" s="11" t="s">
         <v>60</v>
       </c>
@@ -2580,13 +2626,13 @@
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="33"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="38"/>
       <c r="L44" s="11" t="s">
         <v>60</v>
       </c>
@@ -2598,13 +2644,13 @@
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="33"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="38"/>
+      <c r="I45" s="36"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="38"/>
       <c r="L45" s="11" t="s">
         <v>60</v>
       </c>
@@ -2616,13 +2662,13 @@
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="33"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="38"/>
       <c r="L46" s="11" t="s">
         <v>60</v>
       </c>
@@ -2634,13 +2680,13 @@
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="33"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="38"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="37"/>
+      <c r="K47" s="38"/>
       <c r="L47" s="11" t="s">
         <v>60</v>
       </c>
@@ -2652,13 +2698,13 @@
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="33"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="37"/>
+      <c r="K48" s="38"/>
       <c r="L48" s="11" t="s">
         <v>60</v>
       </c>
@@ -2670,13 +2716,13 @@
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="33"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="38"/>
+      <c r="I49" s="36"/>
+      <c r="J49" s="37"/>
+      <c r="K49" s="38"/>
       <c r="L49" s="11" t="s">
         <v>60</v>
       </c>
@@ -2688,13 +2734,13 @@
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="33"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="37"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="37"/>
+      <c r="K50" s="38"/>
       <c r="L50" s="11" t="s">
         <v>60</v>
       </c>
@@ -2706,13 +2752,13 @@
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="33"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="38"/>
+      <c r="I51" s="36"/>
+      <c r="J51" s="37"/>
+      <c r="K51" s="38"/>
       <c r="L51" s="11" t="s">
         <v>60</v>
       </c>
@@ -2724,13 +2770,13 @@
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="33"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="33"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="36"/>
+      <c r="J52" s="37"/>
+      <c r="K52" s="38"/>
       <c r="L52" s="11" t="s">
         <v>60</v>
       </c>
@@ -2742,13 +2788,13 @@
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="33"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="38"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="37"/>
+      <c r="K53" s="38"/>
       <c r="L53" s="11" t="s">
         <v>60</v>
       </c>
@@ -2760,13 +2806,13 @@
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="33"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="36"/>
+      <c r="J54" s="37"/>
+      <c r="K54" s="38"/>
       <c r="L54" s="11" t="s">
         <v>60</v>
       </c>
@@ -2778,13 +2824,13 @@
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="33"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="38"/>
+      <c r="I55" s="36"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="38"/>
       <c r="L55" s="11" t="s">
         <v>60</v>
       </c>
@@ -2796,13 +2842,13 @@
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="33"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="33"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="36"/>
+      <c r="J56" s="37"/>
+      <c r="K56" s="38"/>
       <c r="L56" s="11" t="s">
         <v>60</v>
       </c>
@@ -2814,13 +2860,13 @@
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="33"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="37"/>
+      <c r="G57" s="37"/>
+      <c r="H57" s="38"/>
+      <c r="I57" s="36"/>
+      <c r="J57" s="37"/>
+      <c r="K57" s="38"/>
       <c r="L57" s="11" t="s">
         <v>60</v>
       </c>
@@ -2832,13 +2878,13 @@
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="33"/>
+      <c r="E58" s="36"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="37"/>
+      <c r="K58" s="38"/>
       <c r="L58" s="11" t="s">
         <v>60</v>
       </c>
@@ -2850,13 +2896,13 @@
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="33"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="38"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="37"/>
+      <c r="K59" s="38"/>
       <c r="L59" s="11" t="s">
         <v>60</v>
       </c>
@@ -2868,13 +2914,13 @@
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="33"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="37"/>
+      <c r="G60" s="37"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="36"/>
+      <c r="J60" s="37"/>
+      <c r="K60" s="38"/>
       <c r="L60" s="11" t="s">
         <v>60</v>
       </c>
@@ -2886,13 +2932,13 @@
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="33"/>
+      <c r="E61" s="36"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="36"/>
+      <c r="J61" s="37"/>
+      <c r="K61" s="38"/>
       <c r="L61" s="11" t="s">
         <v>60</v>
       </c>
@@ -2904,13 +2950,13 @@
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="31"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="33"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="36"/>
+      <c r="J62" s="37"/>
+      <c r="K62" s="38"/>
       <c r="L62" s="11" t="s">
         <v>60</v>
       </c>
@@ -2922,13 +2968,13 @@
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="31"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="33"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="36"/>
+      <c r="J63" s="37"/>
+      <c r="K63" s="38"/>
       <c r="L63" s="11" t="s">
         <v>60</v>
       </c>
@@ -2940,13 +2986,13 @@
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="33"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="33"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="36"/>
+      <c r="J64" s="37"/>
+      <c r="K64" s="38"/>
       <c r="L64" s="11" t="s">
         <v>60</v>
       </c>
@@ -2958,13 +3004,13 @@
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="33"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="32"/>
-      <c r="K65" s="33"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="37"/>
+      <c r="G65" s="37"/>
+      <c r="H65" s="38"/>
+      <c r="I65" s="36"/>
+      <c r="J65" s="37"/>
+      <c r="K65" s="38"/>
       <c r="L65" s="11" t="s">
         <v>60</v>
       </c>
@@ -2976,13 +3022,13 @@
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="33"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="37"/>
+      <c r="H66" s="38"/>
+      <c r="I66" s="36"/>
+      <c r="J66" s="37"/>
+      <c r="K66" s="38"/>
       <c r="L66" s="11" t="s">
         <v>60</v>
       </c>
@@ -2994,13 +3040,13 @@
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="36"/>
-      <c r="H67" s="36"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="33"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="36"/>
+      <c r="J67" s="37"/>
+      <c r="K67" s="38"/>
       <c r="L67" s="11" t="s">
         <v>60</v>
       </c>
@@ -3012,13 +3058,13 @@
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="31"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="33"/>
-      <c r="I68" s="31"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="33"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="37"/>
+      <c r="G68" s="37"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="37"/>
+      <c r="K68" s="38"/>
       <c r="L68" s="11" t="s">
         <v>60</v>
       </c>
@@ -3030,13 +3076,13 @@
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="33"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="37"/>
+      <c r="H69" s="38"/>
+      <c r="I69" s="36"/>
+      <c r="J69" s="37"/>
+      <c r="K69" s="38"/>
       <c r="L69" s="11" t="s">
         <v>60</v>
       </c>
@@ -3048,13 +3094,13 @@
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="33"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="33"/>
+      <c r="E70" s="36"/>
+      <c r="F70" s="37"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="38"/>
+      <c r="I70" s="36"/>
+      <c r="J70" s="37"/>
+      <c r="K70" s="38"/>
       <c r="L70" s="11" t="s">
         <v>60</v>
       </c>
@@ -3066,13 +3112,13 @@
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="33"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="37"/>
+      <c r="G71" s="37"/>
+      <c r="H71" s="38"/>
+      <c r="I71" s="36"/>
+      <c r="J71" s="37"/>
+      <c r="K71" s="38"/>
       <c r="L71" s="11" t="s">
         <v>60</v>
       </c>
@@ -3084,13 +3130,13 @@
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="33"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="37"/>
+      <c r="H72" s="38"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="37"/>
+      <c r="K72" s="38"/>
       <c r="L72" s="11" t="s">
         <v>60</v>
       </c>
@@ -3102,13 +3148,13 @@
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="33"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="37"/>
+      <c r="H73" s="38"/>
+      <c r="I73" s="36"/>
+      <c r="J73" s="37"/>
+      <c r="K73" s="38"/>
       <c r="L73" s="11" t="s">
         <v>60</v>
       </c>
@@ -3120,13 +3166,13 @@
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-      <c r="E74" s="31"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="31"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="33"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="38"/>
       <c r="L74" s="11" t="s">
         <v>60</v>
       </c>
@@ -3138,13 +3184,13 @@
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="31"/>
-      <c r="J75" s="32"/>
-      <c r="K75" s="33"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="37"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="38"/>
+      <c r="I75" s="36"/>
+      <c r="J75" s="37"/>
+      <c r="K75" s="38"/>
       <c r="L75" s="11" t="s">
         <v>60</v>
       </c>
@@ -3156,13 +3202,13 @@
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-      <c r="E76" s="31"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="31"/>
-      <c r="J76" s="32"/>
-      <c r="K76" s="33"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="37"/>
+      <c r="G76" s="37"/>
+      <c r="H76" s="38"/>
+      <c r="I76" s="36"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="38"/>
       <c r="L76" s="11" t="s">
         <v>60</v>
       </c>
@@ -3174,13 +3220,13 @@
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="32"/>
-      <c r="K77" s="33"/>
+      <c r="E77" s="36"/>
+      <c r="F77" s="37"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="38"/>
+      <c r="I77" s="36"/>
+      <c r="J77" s="37"/>
+      <c r="K77" s="38"/>
       <c r="L77" s="11" t="s">
         <v>60</v>
       </c>
@@ -3192,13 +3238,13 @@
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-      <c r="E78" s="31"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="33"/>
-      <c r="I78" s="31"/>
-      <c r="J78" s="32"/>
-      <c r="K78" s="33"/>
+      <c r="E78" s="36"/>
+      <c r="F78" s="37"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="38"/>
+      <c r="I78" s="36"/>
+      <c r="J78" s="37"/>
+      <c r="K78" s="38"/>
       <c r="L78" s="11" t="s">
         <v>60</v>
       </c>
@@ -3210,13 +3256,13 @@
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="31"/>
-      <c r="J79" s="32"/>
-      <c r="K79" s="33"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="37"/>
+      <c r="G79" s="37"/>
+      <c r="H79" s="38"/>
+      <c r="I79" s="36"/>
+      <c r="J79" s="37"/>
+      <c r="K79" s="38"/>
       <c r="L79" s="11" t="s">
         <v>60</v>
       </c>
@@ -3228,13 +3274,13 @@
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-      <c r="E80" s="31"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="33"/>
-      <c r="I80" s="31"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="33"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="38"/>
+      <c r="I80" s="36"/>
+      <c r="J80" s="37"/>
+      <c r="K80" s="38"/>
       <c r="L80" s="11" t="s">
         <v>60</v>
       </c>
@@ -3246,13 +3292,13 @@
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-      <c r="E81" s="31"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="33"/>
-      <c r="I81" s="31"/>
-      <c r="J81" s="32"/>
-      <c r="K81" s="33"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="37"/>
+      <c r="G81" s="37"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="36"/>
+      <c r="J81" s="37"/>
+      <c r="K81" s="38"/>
       <c r="L81" s="11" t="s">
         <v>60</v>
       </c>
@@ -3264,13 +3310,13 @@
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="31"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="33"/>
-      <c r="I82" s="31"/>
-      <c r="J82" s="32"/>
-      <c r="K82" s="33"/>
+      <c r="E82" s="36"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="38"/>
+      <c r="I82" s="36"/>
+      <c r="J82" s="37"/>
+      <c r="K82" s="38"/>
       <c r="L82" s="11" t="s">
         <v>60</v>
       </c>
@@ -3282,13 +3328,13 @@
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-      <c r="E83" s="31"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="33"/>
-      <c r="I83" s="31"/>
-      <c r="J83" s="32"/>
-      <c r="K83" s="33"/>
+      <c r="E83" s="36"/>
+      <c r="F83" s="37"/>
+      <c r="G83" s="37"/>
+      <c r="H83" s="38"/>
+      <c r="I83" s="36"/>
+      <c r="J83" s="37"/>
+      <c r="K83" s="38"/>
       <c r="L83" s="11" t="s">
         <v>60</v>
       </c>
@@ -3300,13 +3346,13 @@
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="31"/>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="33"/>
-      <c r="I84" s="31"/>
-      <c r="J84" s="32"/>
-      <c r="K84" s="33"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="37"/>
+      <c r="G84" s="37"/>
+      <c r="H84" s="38"/>
+      <c r="I84" s="36"/>
+      <c r="J84" s="37"/>
+      <c r="K84" s="38"/>
       <c r="L84" s="11" t="s">
         <v>60</v>
       </c>
@@ -3318,13 +3364,13 @@
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="31"/>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="33"/>
-      <c r="I85" s="31"/>
-      <c r="J85" s="32"/>
-      <c r="K85" s="33"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="37"/>
+      <c r="G85" s="37"/>
+      <c r="H85" s="38"/>
+      <c r="I85" s="36"/>
+      <c r="J85" s="37"/>
+      <c r="K85" s="38"/>
       <c r="L85" s="11" t="s">
         <v>60</v>
       </c>
@@ -3336,13 +3382,13 @@
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="33"/>
-      <c r="I86" s="31"/>
-      <c r="J86" s="32"/>
-      <c r="K86" s="33"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="37"/>
+      <c r="G86" s="37"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="36"/>
+      <c r="J86" s="37"/>
+      <c r="K86" s="38"/>
       <c r="L86" s="11" t="s">
         <v>60</v>
       </c>
@@ -3354,13 +3400,13 @@
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="33"/>
-      <c r="I87" s="31"/>
-      <c r="J87" s="32"/>
-      <c r="K87" s="33"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="37"/>
+      <c r="G87" s="37"/>
+      <c r="H87" s="38"/>
+      <c r="I87" s="36"/>
+      <c r="J87" s="37"/>
+      <c r="K87" s="38"/>
       <c r="L87" s="11" t="s">
         <v>60</v>
       </c>
@@ -3372,13 +3418,13 @@
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="31"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="33"/>
-      <c r="I88" s="31"/>
-      <c r="J88" s="32"/>
-      <c r="K88" s="33"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="37"/>
+      <c r="G88" s="37"/>
+      <c r="H88" s="38"/>
+      <c r="I88" s="36"/>
+      <c r="J88" s="37"/>
+      <c r="K88" s="38"/>
       <c r="L88" s="11" t="s">
         <v>60</v>
       </c>
@@ -3390,13 +3436,13 @@
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="31"/>
-      <c r="F89" s="32"/>
-      <c r="G89" s="32"/>
-      <c r="H89" s="33"/>
-      <c r="I89" s="31"/>
-      <c r="J89" s="32"/>
-      <c r="K89" s="33"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="37"/>
+      <c r="G89" s="37"/>
+      <c r="H89" s="38"/>
+      <c r="I89" s="36"/>
+      <c r="J89" s="37"/>
+      <c r="K89" s="38"/>
       <c r="L89" s="11" t="s">
         <v>60</v>
       </c>
@@ -3408,13 +3454,13 @@
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="31"/>
-      <c r="F90" s="32"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="33"/>
-      <c r="I90" s="31"/>
-      <c r="J90" s="32"/>
-      <c r="K90" s="33"/>
+      <c r="E90" s="36"/>
+      <c r="F90" s="37"/>
+      <c r="G90" s="37"/>
+      <c r="H90" s="38"/>
+      <c r="I90" s="36"/>
+      <c r="J90" s="37"/>
+      <c r="K90" s="38"/>
       <c r="L90" s="11" t="s">
         <v>60</v>
       </c>
@@ -3426,13 +3472,13 @@
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="31"/>
-      <c r="F91" s="32"/>
-      <c r="G91" s="32"/>
-      <c r="H91" s="33"/>
-      <c r="I91" s="31"/>
-      <c r="J91" s="32"/>
-      <c r="K91" s="33"/>
+      <c r="E91" s="36"/>
+      <c r="F91" s="37"/>
+      <c r="G91" s="37"/>
+      <c r="H91" s="38"/>
+      <c r="I91" s="36"/>
+      <c r="J91" s="37"/>
+      <c r="K91" s="38"/>
       <c r="L91" s="11" t="s">
         <v>60</v>
       </c>
@@ -3444,13 +3490,13 @@
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="31"/>
-      <c r="F92" s="32"/>
-      <c r="G92" s="32"/>
-      <c r="H92" s="33"/>
-      <c r="I92" s="31"/>
-      <c r="J92" s="32"/>
-      <c r="K92" s="33"/>
+      <c r="E92" s="36"/>
+      <c r="F92" s="37"/>
+      <c r="G92" s="37"/>
+      <c r="H92" s="38"/>
+      <c r="I92" s="36"/>
+      <c r="J92" s="37"/>
+      <c r="K92" s="38"/>
       <c r="L92" s="11" t="s">
         <v>60</v>
       </c>
@@ -3462,13 +3508,13 @@
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="31"/>
-      <c r="F93" s="32"/>
-      <c r="G93" s="32"/>
-      <c r="H93" s="33"/>
-      <c r="I93" s="31"/>
-      <c r="J93" s="32"/>
-      <c r="K93" s="33"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="37"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="36"/>
+      <c r="J93" s="37"/>
+      <c r="K93" s="38"/>
       <c r="L93" s="11" t="s">
         <v>60</v>
       </c>
@@ -3480,13 +3526,13 @@
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="31"/>
-      <c r="F94" s="32"/>
-      <c r="G94" s="32"/>
-      <c r="H94" s="33"/>
-      <c r="I94" s="31"/>
-      <c r="J94" s="32"/>
-      <c r="K94" s="33"/>
+      <c r="E94" s="36"/>
+      <c r="F94" s="37"/>
+      <c r="G94" s="37"/>
+      <c r="H94" s="38"/>
+      <c r="I94" s="36"/>
+      <c r="J94" s="37"/>
+      <c r="K94" s="38"/>
       <c r="L94" s="11" t="s">
         <v>60</v>
       </c>
@@ -3498,13 +3544,13 @@
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="31"/>
-      <c r="F95" s="32"/>
-      <c r="G95" s="32"/>
-      <c r="H95" s="33"/>
-      <c r="I95" s="31"/>
-      <c r="J95" s="32"/>
-      <c r="K95" s="33"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="37"/>
+      <c r="G95" s="37"/>
+      <c r="H95" s="38"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="37"/>
+      <c r="K95" s="38"/>
       <c r="L95" s="11" t="s">
         <v>60</v>
       </c>
@@ -3516,13 +3562,13 @@
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="31"/>
-      <c r="F96" s="32"/>
-      <c r="G96" s="32"/>
-      <c r="H96" s="33"/>
-      <c r="I96" s="31"/>
-      <c r="J96" s="32"/>
-      <c r="K96" s="33"/>
+      <c r="E96" s="36"/>
+      <c r="F96" s="37"/>
+      <c r="G96" s="37"/>
+      <c r="H96" s="38"/>
+      <c r="I96" s="36"/>
+      <c r="J96" s="37"/>
+      <c r="K96" s="38"/>
       <c r="L96" s="11" t="s">
         <v>60</v>
       </c>
@@ -3534,13 +3580,13 @@
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="31"/>
-      <c r="F97" s="32"/>
-      <c r="G97" s="32"/>
-      <c r="H97" s="33"/>
-      <c r="I97" s="31"/>
-      <c r="J97" s="32"/>
-      <c r="K97" s="33"/>
+      <c r="E97" s="36"/>
+      <c r="F97" s="37"/>
+      <c r="G97" s="37"/>
+      <c r="H97" s="38"/>
+      <c r="I97" s="36"/>
+      <c r="J97" s="37"/>
+      <c r="K97" s="38"/>
       <c r="L97" s="11" t="s">
         <v>60</v>
       </c>
@@ -3552,13 +3598,13 @@
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="31"/>
-      <c r="F98" s="32"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="33"/>
-      <c r="I98" s="31"/>
-      <c r="J98" s="32"/>
-      <c r="K98" s="33"/>
+      <c r="E98" s="36"/>
+      <c r="F98" s="37"/>
+      <c r="G98" s="37"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="36"/>
+      <c r="J98" s="37"/>
+      <c r="K98" s="38"/>
       <c r="L98" s="11" t="s">
         <v>60</v>
       </c>
@@ -3570,13 +3616,13 @@
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="31"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32"/>
-      <c r="H99" s="33"/>
-      <c r="I99" s="31"/>
-      <c r="J99" s="32"/>
-      <c r="K99" s="33"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="37"/>
+      <c r="G99" s="37"/>
+      <c r="H99" s="38"/>
+      <c r="I99" s="36"/>
+      <c r="J99" s="37"/>
+      <c r="K99" s="38"/>
       <c r="L99" s="11" t="s">
         <v>60</v>
       </c>
@@ -3588,13 +3634,13 @@
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="31"/>
-      <c r="J100" s="32"/>
-      <c r="K100" s="33"/>
+      <c r="E100" s="39"/>
+      <c r="F100" s="39"/>
+      <c r="G100" s="39"/>
+      <c r="H100" s="39"/>
+      <c r="I100" s="36"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="38"/>
       <c r="L100" s="11" t="s">
         <v>60</v>
       </c>
@@ -3602,19 +3648,170 @@
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I16:K16"/>
@@ -3635,170 +3832,19 @@
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E5:H5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -4537,7 +4583,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282F01E4-329A-4637-8D03-08736FA999D7}">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" style="28" customWidth="1"/>
@@ -4552,11 +4598,11 @@
   <sheetData>
     <row r="1" spans="2:16" s="28" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
       <c r="E2" s="30"/>
       <c r="F2" s="45" t="s">
         <v>163</v>
@@ -4568,11 +4614,11 @@
       <c r="K2" s="46"/>
       <c r="L2" s="47"/>
       <c r="M2" s="30"/>
-      <c r="N2" s="44" t="s">
+      <c r="N2" s="42" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="43" t="e" vm="1">
@@ -4581,17 +4627,17 @@
       <c r="C3" s="43"/>
       <c r="D3" s="43"/>
       <c r="E3" s="29"/>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="44" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
       <c r="I3" s="29"/>
-      <c r="J3" s="42" t="s">
+      <c r="J3" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="44"/>
       <c r="M3" s="29"/>
       <c r="N3" s="43" t="e" vm="2">
         <v>#VALUE!</v>
@@ -4604,17 +4650,17 @@
       <c r="C4" s="43"/>
       <c r="D4" s="43"/>
       <c r="E4" s="29"/>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
       <c r="I4" s="29"/>
-      <c r="J4" s="42" t="s">
+      <c r="J4" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
       <c r="M4" s="29"/>
       <c r="N4" s="43"/>
       <c r="O4" s="43"/>
@@ -4640,18 +4686,40 @@
       <c r="P5" s="43"/>
     </row>
     <row r="6" spans="2:16" s="28" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="69" x14ac:dyDescent="0.3">
+      <c r="B9" s="52" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+    </row>
+    <row r="10" spans="2:16" ht="66" x14ac:dyDescent="0.3">
+      <c r="B10" s="51" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="66" x14ac:dyDescent="0.3">
+      <c r="B11" s="51" t="s">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="N3:P5"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:L2"/>
+    <mergeCell ref="F5:L5"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D5"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N3:P5"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:L2"/>
-    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD699BF-6CC2-4284-B346-4EFCE883627C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEE872A-F128-46E3-ADD8-0E09FFB448F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="185">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -734,12 +734,61 @@
   <si>
     <t>승인</t>
   </si>
+  <si>
+    <t>쳬셔와 대화를 할때 체셔에 이미지가 그대로 보이는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대화를 할 때 한 마리만 보이게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기획</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼저 힌트 봇으로 "2개에 숫자는 반전한다." 로 힌트를 주고 숫자 7, 3이라고 순서대로 찾을 수 있게 만든다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6X6 판을 만들어 A~Z까지 배치 후 힌트로 사용할 알파벳만 7개와 3개를 따로 규정하여 배치하고 그 이외는 랜덤으로 설정한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>힌트로 사용될 기물은 히드라를 토대로 모양을 따 배치된 알파벳 위치에 따라서 머리를 배치하는 것으로 사용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1층 열쇠로 연 방이 다른 상호작을 할 경우 다시 잠기고
+지도로 이동 시 아이템이 복구되는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용 된 문과 아이템은 유지하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽 방 문을 열고 상호작용 뒤에 체셔와 대화를 진행 할 경우 2마리가 보이는 상태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용 뒤에도 체셔에 이미지를 한마리만 보이게 수정하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>적군 오브젝트가 이동 커서보다 뒤에 있어서 커서에 그냥 스킵되는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 씬에서 적 오브젝트가 등장 시 커서 오브젝트 보다 앞에 있기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -820,6 +869,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -864,7 +921,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -905,43 +962,6 @@
         <color auto="1"/>
       </left>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -968,7 +988,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1026,15 +1046,9 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1050,9 +1064,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
@@ -1062,32 +1073,32 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1096,31 +1107,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1638,80 +1649,80 @@
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.75" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="14.625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="33.625" style="20" customWidth="1"/>
-    <col min="5" max="7" width="15.625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="19" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="19" customWidth="1"/>
+    <col min="4" max="4" width="33.625" style="19" customWidth="1"/>
+    <col min="5" max="7" width="15.625" style="20" customWidth="1"/>
     <col min="8" max="8" width="0.375" customWidth="1"/>
-    <col min="9" max="11" width="30.625" style="22" customWidth="1"/>
-    <col min="12" max="12" width="18" style="20" customWidth="1"/>
+    <col min="9" max="11" width="30.625" style="20" customWidth="1"/>
+    <col min="12" max="12" width="18" style="30" customWidth="1"/>
     <col min="13" max="13" width="44.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="27" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39" t="s">
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="21" t="s">
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="M3" s="21" t="s">
+      <c r="M3" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="204.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="26" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="24" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="18">
@@ -1720,24 +1731,25 @@
       <c r="D4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="35" t="s">
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="36"/>
-      <c r="K4" s="38"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
       <c r="L4" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M4" s="8"/>
     </row>
     <row r="5" spans="1:13" ht="173.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="24" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="18">
@@ -1746,24 +1758,25 @@
       <c r="D5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="35" t="s">
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="36"/>
-      <c r="K5" s="38"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M5" s="8"/>
     </row>
     <row r="6" spans="1:13" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="26" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="24" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="18">
@@ -1772,24 +1785,25 @@
       <c r="D6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="35" t="s">
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="36"/>
-      <c r="K6" s="38"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
       <c r="L6" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M6" s="8"/>
     </row>
     <row r="7" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="26" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="24" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="18">
@@ -1798,24 +1812,25 @@
       <c r="D7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="35" t="s">
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="36"/>
-      <c r="K7" s="38"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
       <c r="L7" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M7" s="8"/>
     </row>
     <row r="8" spans="1:13" ht="121.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="26" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="24" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="18">
@@ -1824,24 +1839,25 @@
       <c r="D8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="35" t="s">
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="36"/>
-      <c r="K8" s="38"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
       <c r="L8" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M8" s="8"/>
     </row>
     <row r="9" spans="1:13" ht="123.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="26" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="24" t="s">
         <v>17</v>
       </c>
       <c r="C9" s="18">
@@ -1850,24 +1866,25 @@
       <c r="D9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="35" t="s">
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="36"/>
-      <c r="K9" s="38"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
       <c r="L9" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M9" s="8"/>
     </row>
     <row r="10" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="26" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="24" t="s">
         <v>18</v>
       </c>
       <c r="C10" s="18">
@@ -1876,24 +1893,25 @@
       <c r="D10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="35" t="s">
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="36"/>
-      <c r="K10" s="38"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
       <c r="L10" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M10" s="8"/>
     </row>
     <row r="11" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="26" t="s">
+      <c r="A11" s="8"/>
+      <c r="B11" s="24" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="18">
@@ -1902,24 +1920,25 @@
       <c r="D11" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="35" t="s">
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="36"/>
-      <c r="K11" s="38"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
       <c r="L11" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M11" s="8"/>
     </row>
     <row r="12" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="26" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="24" t="s">
         <v>20</v>
       </c>
       <c r="C12" s="18">
@@ -1928,24 +1947,25 @@
       <c r="D12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="35" t="s">
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="36"/>
-      <c r="K12" s="38"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
       <c r="L12" s="11" t="s">
         <v>62</v>
       </c>
       <c r="M12" s="8"/>
     </row>
     <row r="13" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="24" t="s">
         <v>21</v>
       </c>
       <c r="C13" s="18">
@@ -1954,1667 +1974,1937 @@
       <c r="D13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="36"/>
-      <c r="I13" s="35" t="s">
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="38"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
       <c r="L13" s="11" t="s">
         <v>60</v>
       </c>
       <c r="M13" s="8"/>
     </row>
     <row r="14" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="26" t="s">
+      <c r="A14" s="8"/>
+      <c r="B14" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="21">
         <v>46098</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="35" t="s">
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="36"/>
-      <c r="K14" s="38"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="11" t="s">
         <v>62</v>
       </c>
       <c r="M14" s="8"/>
     </row>
     <row r="15" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="26" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="22">
         <v>46103</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="35" t="s">
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="36"/>
-      <c r="K15" s="38"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
       <c r="L15" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M15" s="8"/>
     </row>
     <row r="16" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="26" t="s">
+      <c r="A16" s="8"/>
+      <c r="B16" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="22">
         <v>46103</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="35" t="s">
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="36"/>
-      <c r="K16" s="38"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
       <c r="L16" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="2:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="26" t="s">
+    <row r="17" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="22">
         <v>46103</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="35" t="s">
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="36"/>
-      <c r="K17" s="38"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
       <c r="L17" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="26" t="s">
+    <row r="18" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="22">
         <v>46107</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="35" t="s">
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="36"/>
-      <c r="K18" s="38"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
       <c r="L18" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="M18" s="25"/>
-    </row>
-    <row r="19" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="26" t="s">
+      <c r="M18" s="23"/>
+    </row>
+    <row r="19" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="23"/>
+      <c r="B19" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="22">
         <v>46107</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="35" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="31" t="s">
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="32"/>
-      <c r="K19" s="33"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
       <c r="L19" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M19" s="25"/>
-    </row>
-    <row r="20" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="26" t="s">
+      <c r="M19" s="23"/>
+    </row>
+    <row r="20" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="23"/>
+      <c r="B20" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="22">
         <v>46107</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="31" t="s">
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="32"/>
-      <c r="K20" s="33"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
       <c r="L20" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M20" s="25"/>
-    </row>
-    <row r="21" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="26" t="s">
+      <c r="M20" s="23"/>
+    </row>
+    <row r="21" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="22">
         <v>46107</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="31" t="s">
+      <c r="E21" s="35" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="31" t="s">
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="32"/>
-      <c r="K21" s="33"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
       <c r="L21" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="M21" s="25"/>
-    </row>
-    <row r="22" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="26" t="s">
+      <c r="M21" s="23"/>
+    </row>
+    <row r="22" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="23"/>
+      <c r="B22" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="33"/>
+      <c r="C22" s="22">
+        <v>46113</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
       <c r="L22" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M22" s="25"/>
-    </row>
-    <row r="23" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="M22" s="23"/>
+    </row>
+    <row r="23" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23"/>
+      <c r="B23" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="31"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="33"/>
+      <c r="C23" s="22">
+        <v>46117</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>179</v>
+      </c>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
       <c r="L23" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M23" s="25"/>
-    </row>
-    <row r="24" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="26" t="s">
+      <c r="M23" s="23"/>
+    </row>
+    <row r="24" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="23"/>
+      <c r="B24" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="33"/>
+      <c r="C24" s="22">
+        <v>46117</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
       <c r="L24" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M24" s="25"/>
-    </row>
-    <row r="25" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="26" t="s">
+      <c r="M24" s="23"/>
+    </row>
+    <row r="25" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="23"/>
+      <c r="B25" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="33"/>
+      <c r="C25" s="22">
+        <v>46117</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
       <c r="L25" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M25" s="25"/>
-    </row>
-    <row r="26" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="26" t="s">
+      <c r="M25" s="23"/>
+    </row>
+    <row r="26" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="23"/>
+      <c r="B26" s="24" t="s">
         <v>81</v>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="33"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
       <c r="L26" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M26" s="25"/>
-    </row>
-    <row r="27" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="26" t="s">
+      <c r="M26" s="23"/>
+    </row>
+    <row r="27" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="23"/>
+      <c r="B27" s="24" t="s">
         <v>82</v>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="31"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="33"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
       <c r="L27" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M27" s="25"/>
-    </row>
-    <row r="28" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="26" t="s">
+      <c r="M27" s="23"/>
+    </row>
+    <row r="28" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="23"/>
+      <c r="B28" s="24" t="s">
         <v>83</v>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="33"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
       <c r="L28" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M28" s="25"/>
-    </row>
-    <row r="29" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="26" t="s">
+      <c r="M28" s="23"/>
+    </row>
+    <row r="29" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="23"/>
+      <c r="B29" s="24" t="s">
         <v>84</v>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="33"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
       <c r="L29" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M29" s="25"/>
-    </row>
-    <row r="30" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="26" t="s">
+      <c r="M29" s="23"/>
+    </row>
+    <row r="30" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="23"/>
+      <c r="B30" s="24" t="s">
         <v>85</v>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="33"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
       <c r="L30" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M30" s="25"/>
-    </row>
-    <row r="31" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="26" t="s">
+      <c r="M30" s="23"/>
+    </row>
+    <row r="31" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="23"/>
+      <c r="B31" s="24" t="s">
         <v>86</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="33"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
       <c r="L31" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M31" s="25"/>
-    </row>
-    <row r="32" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="26" t="s">
+      <c r="M31" s="23"/>
+    </row>
+    <row r="32" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="23"/>
+      <c r="B32" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="33"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
       <c r="L32" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M32" s="25"/>
-    </row>
-    <row r="33" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="26" t="s">
+      <c r="M32" s="23"/>
+    </row>
+    <row r="33" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="23"/>
+      <c r="B33" s="24" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="33"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
       <c r="L33" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M33" s="25"/>
-    </row>
-    <row r="34" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="26" t="s">
+      <c r="M33" s="23"/>
+    </row>
+    <row r="34" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="23"/>
+      <c r="B34" s="24" t="s">
         <v>89</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="33"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="33"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
       <c r="L34" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M34" s="25"/>
-    </row>
-    <row r="35" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="26" t="s">
+      <c r="M34" s="23"/>
+    </row>
+    <row r="35" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="23"/>
+      <c r="B35" s="24" t="s">
         <v>90</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="33"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="33"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
       <c r="L35" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M35" s="25"/>
-    </row>
-    <row r="36" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="26" t="s">
+      <c r="M35" s="23"/>
+    </row>
+    <row r="36" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="23"/>
+      <c r="B36" s="24" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="33"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="33"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
       <c r="L36" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M36" s="25"/>
-    </row>
-    <row r="37" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="26" t="s">
+      <c r="M36" s="23"/>
+    </row>
+    <row r="37" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="23"/>
+      <c r="B37" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="33"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
       <c r="L37" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M37" s="25"/>
-    </row>
-    <row r="38" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="26" t="s">
+      <c r="M37" s="23"/>
+    </row>
+    <row r="38" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="23"/>
+      <c r="B38" s="24" t="s">
         <v>93</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="33"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="33"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
       <c r="L38" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M38" s="25"/>
-    </row>
-    <row r="39" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="26" t="s">
+      <c r="M38" s="23"/>
+    </row>
+    <row r="39" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="23"/>
+      <c r="B39" s="24" t="s">
         <v>94</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="33"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
       <c r="L39" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M39" s="25"/>
-    </row>
-    <row r="40" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="26" t="s">
+      <c r="M39" s="23"/>
+    </row>
+    <row r="40" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="23"/>
+      <c r="B40" s="24" t="s">
         <v>95</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="31"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="33"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="33"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
       <c r="L40" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M40" s="25"/>
-    </row>
-    <row r="41" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="26" t="s">
+      <c r="M40" s="23"/>
+    </row>
+    <row r="41" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="23"/>
+      <c r="B41" s="24" t="s">
         <v>96</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="33"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="35"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="35"/>
+      <c r="I41" s="35"/>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
       <c r="L41" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M41" s="25"/>
-    </row>
-    <row r="42" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="26" t="s">
+      <c r="M41" s="23"/>
+    </row>
+    <row r="42" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="23"/>
+      <c r="B42" s="24" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="33"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
       <c r="L42" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M42" s="25"/>
-    </row>
-    <row r="43" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="26" t="s">
+      <c r="M42" s="23"/>
+    </row>
+    <row r="43" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="23"/>
+      <c r="B43" s="24" t="s">
         <v>98</v>
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="31"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="33"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
       <c r="L43" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M43" s="25"/>
-    </row>
-    <row r="44" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="26" t="s">
+      <c r="M43" s="23"/>
+    </row>
+    <row r="44" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="23"/>
+      <c r="B44" s="24" t="s">
         <v>99</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="31"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="33"/>
+      <c r="E44" s="35"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="35"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
       <c r="L44" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M44" s="25"/>
-    </row>
-    <row r="45" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="26" t="s">
+      <c r="M44" s="23"/>
+    </row>
+    <row r="45" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="23"/>
+      <c r="B45" s="24" t="s">
         <v>100</v>
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="31"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="33"/>
+      <c r="E45" s="35"/>
+      <c r="F45" s="35"/>
+      <c r="G45" s="35"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
       <c r="L45" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M45" s="25"/>
-    </row>
-    <row r="46" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="26" t="s">
+      <c r="M45" s="23"/>
+    </row>
+    <row r="46" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="23"/>
+      <c r="B46" s="24" t="s">
         <v>101</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="31"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="33"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="33"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
       <c r="L46" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M46" s="25"/>
-    </row>
-    <row r="47" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="26" t="s">
+      <c r="M46" s="23"/>
+    </row>
+    <row r="47" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="23"/>
+      <c r="B47" s="24" t="s">
         <v>102</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="33"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
       <c r="L47" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M47" s="25"/>
-    </row>
-    <row r="48" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="26" t="s">
+      <c r="M47" s="23"/>
+    </row>
+    <row r="48" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="23"/>
+      <c r="B48" s="24" t="s">
         <v>103</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="31"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="33"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="35"/>
       <c r="L48" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M48" s="25"/>
-    </row>
-    <row r="49" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="26" t="s">
+      <c r="M48" s="23"/>
+    </row>
+    <row r="49" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="23"/>
+      <c r="B49" s="24" t="s">
         <v>104</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="31"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="33"/>
+      <c r="E49" s="35"/>
+      <c r="F49" s="35"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="35"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="35"/>
       <c r="L49" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M49" s="25"/>
-    </row>
-    <row r="50" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="26" t="s">
+      <c r="M49" s="23"/>
+    </row>
+    <row r="50" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="23"/>
+      <c r="B50" s="24" t="s">
         <v>105</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="33"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="33"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
       <c r="L50" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M50" s="25"/>
-    </row>
-    <row r="51" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="26" t="s">
+      <c r="M50" s="23"/>
+    </row>
+    <row r="51" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="23"/>
+      <c r="B51" s="24" t="s">
         <v>106</v>
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="33"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="35"/>
       <c r="L51" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M51" s="25"/>
-    </row>
-    <row r="52" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="26" t="s">
+      <c r="M51" s="23"/>
+    </row>
+    <row r="52" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="23"/>
+      <c r="B52" s="24" t="s">
         <v>107</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="33"/>
-      <c r="I52" s="31"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="33"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
       <c r="L52" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M52" s="25"/>
-    </row>
-    <row r="53" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="26" t="s">
+      <c r="M52" s="23"/>
+    </row>
+    <row r="53" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="23"/>
+      <c r="B53" s="24" t="s">
         <v>108</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-      <c r="E53" s="31"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="33"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
       <c r="L53" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M53" s="25"/>
-    </row>
-    <row r="54" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="26" t="s">
+      <c r="M53" s="23"/>
+    </row>
+    <row r="54" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="23"/>
+      <c r="B54" s="24" t="s">
         <v>109</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="31"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="31"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="33"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
       <c r="L54" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M54" s="25"/>
-    </row>
-    <row r="55" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="26" t="s">
+      <c r="M54" s="23"/>
+    </row>
+    <row r="55" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="23"/>
+      <c r="B55" s="24" t="s">
         <v>110</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="31"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="33"/>
-      <c r="I55" s="31"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="33"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
+      <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
       <c r="L55" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M55" s="25"/>
-    </row>
-    <row r="56" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="26" t="s">
+      <c r="M55" s="23"/>
+    </row>
+    <row r="56" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="23"/>
+      <c r="B56" s="24" t="s">
         <v>111</v>
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="33"/>
-      <c r="I56" s="31"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="33"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
       <c r="L56" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M56" s="25"/>
-    </row>
-    <row r="57" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="26" t="s">
+      <c r="M56" s="23"/>
+    </row>
+    <row r="57" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="23"/>
+      <c r="B57" s="24" t="s">
         <v>112</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="33"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="33"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
       <c r="L57" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M57" s="25"/>
-    </row>
-    <row r="58" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="26" t="s">
+      <c r="M57" s="23"/>
+    </row>
+    <row r="58" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="23"/>
+      <c r="B58" s="24" t="s">
         <v>113</v>
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-      <c r="E58" s="31"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="33"/>
-      <c r="I58" s="31"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="33"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="35"/>
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
       <c r="L58" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M58" s="25"/>
-    </row>
-    <row r="59" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="26" t="s">
+      <c r="M58" s="23"/>
+    </row>
+    <row r="59" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="23"/>
+      <c r="B59" s="24" t="s">
         <v>114</v>
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-      <c r="E59" s="31"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="31"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="33"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
       <c r="L59" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M59" s="25"/>
-    </row>
-    <row r="60" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="26" t="s">
+      <c r="M59" s="23"/>
+    </row>
+    <row r="60" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="23"/>
+      <c r="B60" s="24" t="s">
         <v>115</v>
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-      <c r="E60" s="31"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="31"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="33"/>
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
       <c r="L60" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M60" s="25"/>
-    </row>
-    <row r="61" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="26" t="s">
+      <c r="M60" s="23"/>
+    </row>
+    <row r="61" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="23"/>
+      <c r="B61" s="24" t="s">
         <v>116</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-      <c r="E61" s="31"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="31"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="33"/>
+      <c r="E61" s="35"/>
+      <c r="F61" s="35"/>
+      <c r="G61" s="35"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="35"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="35"/>
       <c r="L61" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M61" s="25"/>
-    </row>
-    <row r="62" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="26" t="s">
+      <c r="M61" s="23"/>
+    </row>
+    <row r="62" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="23"/>
+      <c r="B62" s="24" t="s">
         <v>117</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="33"/>
-      <c r="I62" s="31"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="33"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="35"/>
       <c r="L62" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M62" s="25"/>
-    </row>
-    <row r="63" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="26" t="s">
+      <c r="M62" s="23"/>
+    </row>
+    <row r="63" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="23"/>
+      <c r="B63" s="24" t="s">
         <v>118</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="31"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="33"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
       <c r="L63" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M63" s="25"/>
-    </row>
-    <row r="64" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="26" t="s">
+      <c r="M63" s="23"/>
+    </row>
+    <row r="64" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="23"/>
+      <c r="B64" s="24" t="s">
         <v>119</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="33"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="33"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="35"/>
+      <c r="J64" s="35"/>
+      <c r="K64" s="35"/>
       <c r="L64" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M64" s="25"/>
-    </row>
-    <row r="65" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="26" t="s">
+      <c r="M64" s="23"/>
+    </row>
+    <row r="65" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="23"/>
+      <c r="B65" s="24" t="s">
         <v>120</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="31"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="33"/>
-      <c r="I65" s="31"/>
-      <c r="J65" s="32"/>
-      <c r="K65" s="33"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="35"/>
+      <c r="J65" s="35"/>
+      <c r="K65" s="35"/>
       <c r="L65" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M65" s="25"/>
-    </row>
-    <row r="66" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="26" t="s">
+      <c r="M65" s="23"/>
+    </row>
+    <row r="66" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="23"/>
+      <c r="B66" s="24" t="s">
         <v>121</v>
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="31"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="31"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="33"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="35"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="35"/>
+      <c r="I66" s="35"/>
+      <c r="J66" s="35"/>
+      <c r="K66" s="35"/>
       <c r="L66" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M66" s="25"/>
-    </row>
-    <row r="67" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="26" t="s">
+      <c r="M66" s="23"/>
+    </row>
+    <row r="67" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="23"/>
+      <c r="B67" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="36"/>
-      <c r="G67" s="36"/>
-      <c r="H67" s="36"/>
-      <c r="I67" s="31"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="33"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="35"/>
+      <c r="J67" s="35"/>
+      <c r="K67" s="35"/>
       <c r="L67" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M67" s="25"/>
-    </row>
-    <row r="68" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="26" t="s">
+      <c r="M67" s="23"/>
+    </row>
+    <row r="68" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="23"/>
+      <c r="B68" s="24" t="s">
         <v>123</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="31"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="33"/>
-      <c r="I68" s="31"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="33"/>
+      <c r="E68" s="35"/>
+      <c r="F68" s="35"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="35"/>
       <c r="L68" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M68" s="25"/>
-    </row>
-    <row r="69" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="26" t="s">
+      <c r="M68" s="23"/>
+    </row>
+    <row r="69" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="23"/>
+      <c r="B69" s="24" t="s">
         <v>124</v>
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="31"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="31"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="33"/>
+      <c r="E69" s="35"/>
+      <c r="F69" s="35"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="35"/>
+      <c r="I69" s="35"/>
+      <c r="J69" s="35"/>
+      <c r="K69" s="35"/>
       <c r="L69" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M69" s="25"/>
-    </row>
-    <row r="70" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="26" t="s">
+      <c r="M69" s="23"/>
+    </row>
+    <row r="70" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="23"/>
+      <c r="B70" s="24" t="s">
         <v>125</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="31"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="33"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="33"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="35"/>
+      <c r="I70" s="35"/>
+      <c r="J70" s="35"/>
+      <c r="K70" s="35"/>
       <c r="L70" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M70" s="25"/>
-    </row>
-    <row r="71" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="26" t="s">
+      <c r="M70" s="23"/>
+    </row>
+    <row r="71" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="23"/>
+      <c r="B71" s="24" t="s">
         <v>126</v>
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-      <c r="E71" s="31"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="33"/>
+      <c r="E71" s="35"/>
+      <c r="F71" s="35"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="35"/>
+      <c r="I71" s="35"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="35"/>
       <c r="L71" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M71" s="25"/>
-    </row>
-    <row r="72" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B72" s="26" t="s">
+      <c r="M71" s="23"/>
+    </row>
+    <row r="72" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="23"/>
+      <c r="B72" s="24" t="s">
         <v>127</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="33"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="35"/>
+      <c r="J72" s="35"/>
+      <c r="K72" s="35"/>
       <c r="L72" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M72" s="25"/>
-    </row>
-    <row r="73" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="26" t="s">
+      <c r="M72" s="23"/>
+    </row>
+    <row r="73" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="23"/>
+      <c r="B73" s="24" t="s">
         <v>128</v>
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="33"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="35"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="35"/>
+      <c r="I73" s="35"/>
+      <c r="J73" s="35"/>
+      <c r="K73" s="35"/>
       <c r="L73" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M73" s="25"/>
-    </row>
-    <row r="74" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="26" t="s">
+      <c r="M73" s="23"/>
+    </row>
+    <row r="74" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="23"/>
+      <c r="B74" s="24" t="s">
         <v>129</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-      <c r="E74" s="31"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="31"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="33"/>
+      <c r="E74" s="35"/>
+      <c r="F74" s="35"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="35"/>
+      <c r="I74" s="35"/>
+      <c r="J74" s="35"/>
+      <c r="K74" s="35"/>
       <c r="L74" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M74" s="25"/>
-    </row>
-    <row r="75" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="26" t="s">
+      <c r="M74" s="23"/>
+    </row>
+    <row r="75" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="23"/>
+      <c r="B75" s="24" t="s">
         <v>130</v>
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-      <c r="E75" s="31"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="31"/>
-      <c r="J75" s="32"/>
-      <c r="K75" s="33"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="35"/>
       <c r="L75" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M75" s="25"/>
-    </row>
-    <row r="76" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="26" t="s">
+      <c r="M75" s="23"/>
+    </row>
+    <row r="76" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="23"/>
+      <c r="B76" s="24" t="s">
         <v>131</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-      <c r="E76" s="31"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="31"/>
-      <c r="J76" s="32"/>
-      <c r="K76" s="33"/>
+      <c r="E76" s="35"/>
+      <c r="F76" s="35"/>
+      <c r="G76" s="35"/>
+      <c r="H76" s="35"/>
+      <c r="I76" s="35"/>
+      <c r="J76" s="35"/>
+      <c r="K76" s="35"/>
       <c r="L76" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M76" s="25"/>
-    </row>
-    <row r="77" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="26" t="s">
+      <c r="M76" s="23"/>
+    </row>
+    <row r="77" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="23"/>
+      <c r="B77" s="24" t="s">
         <v>132</v>
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="32"/>
-      <c r="K77" s="33"/>
+      <c r="E77" s="35"/>
+      <c r="F77" s="35"/>
+      <c r="G77" s="35"/>
+      <c r="H77" s="35"/>
+      <c r="I77" s="35"/>
+      <c r="J77" s="35"/>
+      <c r="K77" s="35"/>
       <c r="L77" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M77" s="25"/>
-    </row>
-    <row r="78" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="26" t="s">
+      <c r="M77" s="23"/>
+    </row>
+    <row r="78" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="23"/>
+      <c r="B78" s="24" t="s">
         <v>133</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-      <c r="E78" s="31"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="33"/>
-      <c r="I78" s="31"/>
-      <c r="J78" s="32"/>
-      <c r="K78" s="33"/>
+      <c r="E78" s="35"/>
+      <c r="F78" s="35"/>
+      <c r="G78" s="35"/>
+      <c r="H78" s="35"/>
+      <c r="I78" s="35"/>
+      <c r="J78" s="35"/>
+      <c r="K78" s="35"/>
       <c r="L78" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M78" s="25"/>
-    </row>
-    <row r="79" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="26" t="s">
+      <c r="M78" s="23"/>
+    </row>
+    <row r="79" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="23"/>
+      <c r="B79" s="24" t="s">
         <v>134</v>
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="31"/>
-      <c r="J79" s="32"/>
-      <c r="K79" s="33"/>
+      <c r="E79" s="35"/>
+      <c r="F79" s="35"/>
+      <c r="G79" s="35"/>
+      <c r="H79" s="35"/>
+      <c r="I79" s="35"/>
+      <c r="J79" s="35"/>
+      <c r="K79" s="35"/>
       <c r="L79" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M79" s="25"/>
-    </row>
-    <row r="80" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="26" t="s">
+      <c r="M79" s="23"/>
+    </row>
+    <row r="80" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="23"/>
+      <c r="B80" s="24" t="s">
         <v>135</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-      <c r="E80" s="31"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="33"/>
-      <c r="I80" s="31"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="33"/>
+      <c r="E80" s="35"/>
+      <c r="F80" s="35"/>
+      <c r="G80" s="35"/>
+      <c r="H80" s="35"/>
+      <c r="I80" s="35"/>
+      <c r="J80" s="35"/>
+      <c r="K80" s="35"/>
       <c r="L80" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M80" s="25"/>
-    </row>
-    <row r="81" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B81" s="26" t="s">
+      <c r="M80" s="23"/>
+    </row>
+    <row r="81" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="23"/>
+      <c r="B81" s="24" t="s">
         <v>136</v>
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-      <c r="E81" s="31"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="33"/>
-      <c r="I81" s="31"/>
-      <c r="J81" s="32"/>
-      <c r="K81" s="33"/>
+      <c r="E81" s="35"/>
+      <c r="F81" s="35"/>
+      <c r="G81" s="35"/>
+      <c r="H81" s="35"/>
+      <c r="I81" s="35"/>
+      <c r="J81" s="35"/>
+      <c r="K81" s="35"/>
       <c r="L81" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M81" s="25"/>
-    </row>
-    <row r="82" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="26" t="s">
+      <c r="M81" s="23"/>
+    </row>
+    <row r="82" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="23"/>
+      <c r="B82" s="24" t="s">
         <v>137</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="31"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="33"/>
-      <c r="I82" s="31"/>
-      <c r="J82" s="32"/>
-      <c r="K82" s="33"/>
+      <c r="E82" s="35"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="35"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="35"/>
+      <c r="K82" s="35"/>
       <c r="L82" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M82" s="25"/>
-    </row>
-    <row r="83" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B83" s="26" t="s">
+      <c r="M82" s="23"/>
+    </row>
+    <row r="83" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="23"/>
+      <c r="B83" s="24" t="s">
         <v>138</v>
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-      <c r="E83" s="31"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="33"/>
-      <c r="I83" s="31"/>
-      <c r="J83" s="32"/>
-      <c r="K83" s="33"/>
+      <c r="E83" s="35"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="35"/>
+      <c r="H83" s="35"/>
+      <c r="I83" s="35"/>
+      <c r="J83" s="35"/>
+      <c r="K83" s="35"/>
       <c r="L83" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M83" s="25"/>
-    </row>
-    <row r="84" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B84" s="26" t="s">
+      <c r="M83" s="23"/>
+    </row>
+    <row r="84" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="23"/>
+      <c r="B84" s="24" t="s">
         <v>139</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="31"/>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="33"/>
-      <c r="I84" s="31"/>
-      <c r="J84" s="32"/>
-      <c r="K84" s="33"/>
+      <c r="E84" s="35"/>
+      <c r="F84" s="35"/>
+      <c r="G84" s="35"/>
+      <c r="H84" s="35"/>
+      <c r="I84" s="35"/>
+      <c r="J84" s="35"/>
+      <c r="K84" s="35"/>
       <c r="L84" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M84" s="25"/>
-    </row>
-    <row r="85" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B85" s="26" t="s">
+      <c r="M84" s="23"/>
+    </row>
+    <row r="85" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="23"/>
+      <c r="B85" s="24" t="s">
         <v>140</v>
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="31"/>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="33"/>
-      <c r="I85" s="31"/>
-      <c r="J85" s="32"/>
-      <c r="K85" s="33"/>
+      <c r="E85" s="35"/>
+      <c r="F85" s="35"/>
+      <c r="G85" s="35"/>
+      <c r="H85" s="35"/>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
       <c r="L85" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M85" s="25"/>
-    </row>
-    <row r="86" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="26" t="s">
+      <c r="M85" s="23"/>
+    </row>
+    <row r="86" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="23"/>
+      <c r="B86" s="24" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="33"/>
-      <c r="I86" s="31"/>
-      <c r="J86" s="32"/>
-      <c r="K86" s="33"/>
+      <c r="E86" s="35"/>
+      <c r="F86" s="35"/>
+      <c r="G86" s="35"/>
+      <c r="H86" s="35"/>
+      <c r="I86" s="35"/>
+      <c r="J86" s="35"/>
+      <c r="K86" s="35"/>
       <c r="L86" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M86" s="25"/>
-    </row>
-    <row r="87" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="26" t="s">
+      <c r="M86" s="23"/>
+    </row>
+    <row r="87" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="23"/>
+      <c r="B87" s="24" t="s">
         <v>142</v>
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="31"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="33"/>
-      <c r="I87" s="31"/>
-      <c r="J87" s="32"/>
-      <c r="K87" s="33"/>
+      <c r="E87" s="35"/>
+      <c r="F87" s="35"/>
+      <c r="G87" s="35"/>
+      <c r="H87" s="35"/>
+      <c r="I87" s="35"/>
+      <c r="J87" s="35"/>
+      <c r="K87" s="35"/>
       <c r="L87" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M87" s="25"/>
-    </row>
-    <row r="88" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="26" t="s">
+      <c r="M87" s="23"/>
+    </row>
+    <row r="88" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="23"/>
+      <c r="B88" s="24" t="s">
         <v>143</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="31"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="33"/>
-      <c r="I88" s="31"/>
-      <c r="J88" s="32"/>
-      <c r="K88" s="33"/>
+      <c r="E88" s="35"/>
+      <c r="F88" s="35"/>
+      <c r="G88" s="35"/>
+      <c r="H88" s="35"/>
+      <c r="I88" s="35"/>
+      <c r="J88" s="35"/>
+      <c r="K88" s="35"/>
       <c r="L88" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M88" s="25"/>
-    </row>
-    <row r="89" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="26" t="s">
+      <c r="M88" s="23"/>
+    </row>
+    <row r="89" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="23"/>
+      <c r="B89" s="24" t="s">
         <v>144</v>
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="31"/>
-      <c r="F89" s="32"/>
-      <c r="G89" s="32"/>
-      <c r="H89" s="33"/>
-      <c r="I89" s="31"/>
-      <c r="J89" s="32"/>
-      <c r="K89" s="33"/>
+      <c r="E89" s="35"/>
+      <c r="F89" s="35"/>
+      <c r="G89" s="35"/>
+      <c r="H89" s="35"/>
+      <c r="I89" s="35"/>
+      <c r="J89" s="35"/>
+      <c r="K89" s="35"/>
       <c r="L89" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M89" s="25"/>
-    </row>
-    <row r="90" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="26" t="s">
+      <c r="M89" s="23"/>
+    </row>
+    <row r="90" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="23"/>
+      <c r="B90" s="24" t="s">
         <v>145</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="31"/>
-      <c r="F90" s="32"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="33"/>
-      <c r="I90" s="31"/>
-      <c r="J90" s="32"/>
-      <c r="K90" s="33"/>
+      <c r="E90" s="35"/>
+      <c r="F90" s="35"/>
+      <c r="G90" s="35"/>
+      <c r="H90" s="35"/>
+      <c r="I90" s="35"/>
+      <c r="J90" s="35"/>
+      <c r="K90" s="35"/>
       <c r="L90" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M90" s="25"/>
-    </row>
-    <row r="91" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="26" t="s">
+      <c r="M90" s="23"/>
+    </row>
+    <row r="91" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="23"/>
+      <c r="B91" s="24" t="s">
         <v>146</v>
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="31"/>
-      <c r="F91" s="32"/>
-      <c r="G91" s="32"/>
-      <c r="H91" s="33"/>
-      <c r="I91" s="31"/>
-      <c r="J91" s="32"/>
-      <c r="K91" s="33"/>
+      <c r="E91" s="35"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="35"/>
+      <c r="H91" s="35"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="35"/>
+      <c r="K91" s="35"/>
       <c r="L91" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M91" s="25"/>
-    </row>
-    <row r="92" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B92" s="26" t="s">
+      <c r="M91" s="23"/>
+    </row>
+    <row r="92" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="23"/>
+      <c r="B92" s="24" t="s">
         <v>147</v>
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="31"/>
-      <c r="F92" s="32"/>
-      <c r="G92" s="32"/>
-      <c r="H92" s="33"/>
-      <c r="I92" s="31"/>
-      <c r="J92" s="32"/>
-      <c r="K92" s="33"/>
+      <c r="E92" s="35"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="35"/>
+      <c r="I92" s="35"/>
+      <c r="J92" s="35"/>
+      <c r="K92" s="35"/>
       <c r="L92" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M92" s="25"/>
-    </row>
-    <row r="93" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B93" s="26" t="s">
+      <c r="M92" s="23"/>
+    </row>
+    <row r="93" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="23"/>
+      <c r="B93" s="24" t="s">
         <v>148</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="31"/>
-      <c r="F93" s="32"/>
-      <c r="G93" s="32"/>
-      <c r="H93" s="33"/>
-      <c r="I93" s="31"/>
-      <c r="J93" s="32"/>
-      <c r="K93" s="33"/>
+      <c r="E93" s="35"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="35"/>
+      <c r="I93" s="35"/>
+      <c r="J93" s="35"/>
+      <c r="K93" s="35"/>
       <c r="L93" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M93" s="25"/>
-    </row>
-    <row r="94" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B94" s="26" t="s">
+      <c r="M93" s="23"/>
+    </row>
+    <row r="94" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="23"/>
+      <c r="B94" s="24" t="s">
         <v>149</v>
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="31"/>
-      <c r="F94" s="32"/>
-      <c r="G94" s="32"/>
-      <c r="H94" s="33"/>
-      <c r="I94" s="31"/>
-      <c r="J94" s="32"/>
-      <c r="K94" s="33"/>
+      <c r="E94" s="35"/>
+      <c r="F94" s="35"/>
+      <c r="G94" s="35"/>
+      <c r="H94" s="35"/>
+      <c r="I94" s="35"/>
+      <c r="J94" s="35"/>
+      <c r="K94" s="35"/>
       <c r="L94" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M94" s="25"/>
-    </row>
-    <row r="95" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="26" t="s">
+      <c r="M94" s="23"/>
+    </row>
+    <row r="95" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="23"/>
+      <c r="B95" s="24" t="s">
         <v>150</v>
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="31"/>
-      <c r="F95" s="32"/>
-      <c r="G95" s="32"/>
-      <c r="H95" s="33"/>
-      <c r="I95" s="31"/>
-      <c r="J95" s="32"/>
-      <c r="K95" s="33"/>
+      <c r="E95" s="35"/>
+      <c r="F95" s="35"/>
+      <c r="G95" s="35"/>
+      <c r="H95" s="35"/>
+      <c r="I95" s="35"/>
+      <c r="J95" s="35"/>
+      <c r="K95" s="35"/>
       <c r="L95" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M95" s="25"/>
-    </row>
-    <row r="96" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B96" s="26" t="s">
+      <c r="M95" s="23"/>
+    </row>
+    <row r="96" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="23"/>
+      <c r="B96" s="24" t="s">
         <v>151</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="31"/>
-      <c r="F96" s="32"/>
-      <c r="G96" s="32"/>
-      <c r="H96" s="33"/>
-      <c r="I96" s="31"/>
-      <c r="J96" s="32"/>
-      <c r="K96" s="33"/>
+      <c r="E96" s="35"/>
+      <c r="F96" s="35"/>
+      <c r="G96" s="35"/>
+      <c r="H96" s="35"/>
+      <c r="I96" s="35"/>
+      <c r="J96" s="35"/>
+      <c r="K96" s="35"/>
       <c r="L96" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M96" s="25"/>
-    </row>
-    <row r="97" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B97" s="26" t="s">
+      <c r="M96" s="23"/>
+    </row>
+    <row r="97" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="23"/>
+      <c r="B97" s="24" t="s">
         <v>152</v>
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="31"/>
-      <c r="F97" s="32"/>
-      <c r="G97" s="32"/>
-      <c r="H97" s="33"/>
-      <c r="I97" s="31"/>
-      <c r="J97" s="32"/>
-      <c r="K97" s="33"/>
+      <c r="E97" s="35"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="35"/>
+      <c r="H97" s="35"/>
+      <c r="I97" s="35"/>
+      <c r="J97" s="35"/>
+      <c r="K97" s="35"/>
       <c r="L97" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M97" s="25"/>
-    </row>
-    <row r="98" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="26" t="s">
+      <c r="M97" s="23"/>
+    </row>
+    <row r="98" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="23"/>
+      <c r="B98" s="24" t="s">
         <v>153</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="31"/>
-      <c r="F98" s="32"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="33"/>
-      <c r="I98" s="31"/>
-      <c r="J98" s="32"/>
-      <c r="K98" s="33"/>
+      <c r="E98" s="35"/>
+      <c r="F98" s="35"/>
+      <c r="G98" s="35"/>
+      <c r="H98" s="35"/>
+      <c r="I98" s="35"/>
+      <c r="J98" s="35"/>
+      <c r="K98" s="35"/>
       <c r="L98" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M98" s="25"/>
-    </row>
-    <row r="99" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B99" s="26" t="s">
+      <c r="M98" s="23"/>
+    </row>
+    <row r="99" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="23"/>
+      <c r="B99" s="24" t="s">
         <v>154</v>
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="31"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32"/>
-      <c r="H99" s="33"/>
-      <c r="I99" s="31"/>
-      <c r="J99" s="32"/>
-      <c r="K99" s="33"/>
+      <c r="E99" s="35"/>
+      <c r="F99" s="35"/>
+      <c r="G99" s="35"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="35"/>
+      <c r="J99" s="35"/>
+      <c r="K99" s="35"/>
       <c r="L99" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M99" s="25"/>
-    </row>
-    <row r="100" spans="2:13" s="22" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B100" s="26" t="s">
+      <c r="M99" s="23"/>
+    </row>
+    <row r="100" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="23"/>
+      <c r="B100" s="24" t="s">
         <v>155</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="34"/>
-      <c r="F100" s="34"/>
-      <c r="G100" s="34"/>
-      <c r="H100" s="34"/>
-      <c r="I100" s="31"/>
-      <c r="J100" s="32"/>
-      <c r="K100" s="33"/>
+      <c r="E100" s="35"/>
+      <c r="F100" s="35"/>
+      <c r="G100" s="35"/>
+      <c r="H100" s="35"/>
+      <c r="I100" s="35"/>
+      <c r="J100" s="35"/>
+      <c r="K100" s="35"/>
       <c r="L100" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M100" s="25"/>
+      <c r="M100" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="I93:K93"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="I87:K87"/>
+    <mergeCell ref="I88:K88"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I90:K90"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="I33:K33"/>
+    <mergeCell ref="I34:K34"/>
+    <mergeCell ref="I35:K35"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="I46:K46"/>
+    <mergeCell ref="I52:K52"/>
+    <mergeCell ref="I53:K53"/>
+    <mergeCell ref="I54:K54"/>
+    <mergeCell ref="I55:K55"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="I47:K47"/>
+    <mergeCell ref="I48:K48"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I50:K50"/>
+    <mergeCell ref="I51:K51"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
     <mergeCell ref="A1:M2"/>
     <mergeCell ref="E16:H16"/>
     <mergeCell ref="I16:K16"/>
@@ -3635,170 +3925,19 @@
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="I93:K93"/>
-    <mergeCell ref="I92:K92"/>
-    <mergeCell ref="I87:K87"/>
-    <mergeCell ref="I88:K88"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I90:K90"/>
-    <mergeCell ref="I91:K91"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="I33:K33"/>
-    <mergeCell ref="I34:K34"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I46:K46"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I52:K52"/>
-    <mergeCell ref="I53:K53"/>
-    <mergeCell ref="I54:K54"/>
-    <mergeCell ref="I55:K55"/>
-    <mergeCell ref="I56:K56"/>
-    <mergeCell ref="I47:K47"/>
-    <mergeCell ref="I48:K48"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I50:K50"/>
-    <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E5:H5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -3836,42 +3975,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4207,32 +4346,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
     </row>
     <row r="2" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
     </row>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4537,121 +4676,143 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282F01E4-329A-4637-8D03-08736FA999D7}">
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.625" style="28" customWidth="1"/>
+    <col min="1" max="1" width="1.625" style="25" customWidth="1"/>
     <col min="2" max="4" width="30.625" customWidth="1"/>
     <col min="5" max="5" width="1.625" customWidth="1"/>
     <col min="6" max="8" width="9.625" customWidth="1"/>
     <col min="9" max="9" width="1.625" customWidth="1"/>
     <col min="13" max="13" width="1.625" customWidth="1"/>
     <col min="14" max="16" width="30.625" customWidth="1"/>
-    <col min="17" max="17" width="1.625" style="28" customWidth="1"/>
+    <col min="17" max="17" width="1.625" style="25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" s="28" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:16" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="45" t="s">
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="44" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="40" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="43" t="e" vm="1">
+      <c r="B3" s="39" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="42" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="47" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="42" t="s">
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="47" t="s">
         <v>165</v>
       </c>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="29"/>
-      <c r="N3" s="43" t="e" vm="2">
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="39" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="42" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="42" t="s">
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="47" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="29"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="48" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="49"/>
-      <c r="H5" s="49"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-    </row>
-    <row r="6" spans="2:16" s="28" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="39"/>
+    </row>
+    <row r="6" spans="2:16" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" ht="69" x14ac:dyDescent="0.3">
+      <c r="B9" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+    </row>
+    <row r="10" spans="2:16" ht="66" x14ac:dyDescent="0.3">
+      <c r="B10" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" ht="66" x14ac:dyDescent="0.3">
+      <c r="B11" s="28" t="s">
+        <v>178</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="N3:P5"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="F2:L2"/>
+    <mergeCell ref="F5:L5"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D5"/>
     <mergeCell ref="F3:H3"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="N3:P5"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="F2:L2"/>
-    <mergeCell ref="F5:L5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AEE872A-F128-46E3-ADD8-0E09FFB448F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1AA49F-F70F-4D26-8670-00058D87B19E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
@@ -18,42 +18,31 @@
     <sheet name="버그" sheetId="4" r:id="rId3"/>
     <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -1085,20 +1074,20 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1660,36 +1649,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
@@ -1702,17 +1691,17 @@
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34" t="s">
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
       <c r="L3" s="5" t="s">
         <v>59</v>
       </c>
@@ -1731,17 +1720,17 @@
       <c r="D4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32" t="s">
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="32"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
       <c r="L4" s="11" t="s">
         <v>172</v>
       </c>
@@ -1758,17 +1747,17 @@
       <c r="D5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32" t="s">
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
       <c r="L5" s="11" t="s">
         <v>172</v>
       </c>
@@ -1785,17 +1774,17 @@
       <c r="D6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="33" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32" t="s">
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
       <c r="L6" s="11" t="s">
         <v>172</v>
       </c>
@@ -1812,17 +1801,17 @@
       <c r="D7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
+      <c r="F7" s="33"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="13"/>
-      <c r="I7" s="32" t="s">
+      <c r="I7" s="33" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
       <c r="L7" s="11" t="s">
         <v>172</v>
       </c>
@@ -1839,17 +1828,17 @@
       <c r="D8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="13"/>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
       <c r="L8" s="11" t="s">
         <v>172</v>
       </c>
@@ -1866,17 +1855,17 @@
       <c r="D9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="13"/>
-      <c r="I9" s="32" t="s">
+      <c r="I9" s="33" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
       <c r="L9" s="11" t="s">
         <v>172</v>
       </c>
@@ -1893,17 +1882,17 @@
       <c r="D10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="32" t="s">
+      <c r="I10" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
       <c r="L10" s="11" t="s">
         <v>172</v>
       </c>
@@ -1920,17 +1909,17 @@
       <c r="D11" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32" t="s">
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="11" t="s">
         <v>172</v>
       </c>
@@ -1947,17 +1936,17 @@
       <c r="D12" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32" t="s">
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
       <c r="L12" s="11" t="s">
         <v>62</v>
       </c>
@@ -1974,19 +1963,19 @@
       <c r="D13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32" t="s">
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="33"/>
       <c r="L13" s="11" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="M13" s="8"/>
     </row>
@@ -2001,17 +1990,17 @@
       <c r="D14" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32" t="s">
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="11" t="s">
         <v>62</v>
       </c>
@@ -2028,17 +2017,17 @@
       <c r="D15" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32" t="s">
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
       <c r="L15" s="11" t="s">
         <v>172</v>
       </c>
@@ -2055,17 +2044,17 @@
       <c r="D16" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32" t="s">
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
       <c r="L16" s="11" t="s">
         <v>172</v>
       </c>
@@ -2082,17 +2071,17 @@
       <c r="D17" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32" t="s">
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
       <c r="L17" s="11" t="s">
         <v>172</v>
       </c>
@@ -2109,17 +2098,17 @@
       <c r="D18" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32" t="s">
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
       <c r="L18" s="11" t="s">
         <v>172</v>
       </c>
@@ -2136,19 +2125,19 @@
       <c r="D19" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35" t="s">
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
       <c r="L19" s="11" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="M19" s="23"/>
     </row>
@@ -2163,17 +2152,17 @@
       <c r="D20" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35" t="s">
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
       <c r="L20" s="11" t="s">
         <v>60</v>
       </c>
@@ -2190,17 +2179,17 @@
       <c r="D21" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35" t="s">
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
       <c r="L21" s="11" t="s">
         <v>172</v>
       </c>
@@ -2217,17 +2206,17 @@
       <c r="D22" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35" t="s">
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
       <c r="L22" s="11" t="s">
         <v>172</v>
       </c>
@@ -2244,17 +2233,17 @@
       <c r="D23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="36" t="s">
+      <c r="E23" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="35" t="s">
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="32" t="s">
         <v>180</v>
       </c>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
       <c r="L23" s="11" t="s">
         <v>60</v>
       </c>
@@ -2271,17 +2260,17 @@
       <c r="D24" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="36" t="s">
+      <c r="E24" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="F24" s="36"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="35" t="s">
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
       <c r="L24" s="11" t="s">
         <v>60</v>
       </c>
@@ -2298,17 +2287,17 @@
       <c r="D25" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="36" t="s">
+      <c r="E25" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="F25" s="36"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="35" t="s">
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
       <c r="L25" s="11" t="s">
         <v>60</v>
       </c>
@@ -2321,13 +2310,13 @@
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
       <c r="L26" s="11" t="s">
         <v>60</v>
       </c>
@@ -2340,13 +2329,13 @@
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
       <c r="L27" s="11" t="s">
         <v>60</v>
       </c>
@@ -2359,13 +2348,13 @@
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
-      <c r="E28" s="35"/>
-      <c r="F28" s="35"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="35"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
       <c r="L28" s="11" t="s">
         <v>60</v>
       </c>
@@ -2378,13 +2367,13 @@
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
       <c r="L29" s="11" t="s">
         <v>60</v>
       </c>
@@ -2397,13 +2386,13 @@
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
-      <c r="E30" s="35"/>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
       <c r="L30" s="11" t="s">
         <v>60</v>
       </c>
@@ -2416,13 +2405,13 @@
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
       <c r="L31" s="11" t="s">
         <v>60</v>
       </c>
@@ -2435,13 +2424,13 @@
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="35"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
       <c r="L32" s="11" t="s">
         <v>60</v>
       </c>
@@ -2454,13 +2443,13 @@
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="35"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
       <c r="L33" s="11" t="s">
         <v>60</v>
       </c>
@@ -2473,13 +2462,13 @@
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="35"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
       <c r="L34" s="11" t="s">
         <v>60</v>
       </c>
@@ -2492,13 +2481,13 @@
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="35"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="35"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
       <c r="L35" s="11" t="s">
         <v>60</v>
       </c>
@@ -2511,13 +2500,13 @@
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
       <c r="L36" s="11" t="s">
         <v>60</v>
       </c>
@@ -2530,13 +2519,13 @@
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
       <c r="L37" s="11" t="s">
         <v>60</v>
       </c>
@@ -2549,13 +2538,13 @@
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="35"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
       <c r="L38" s="11" t="s">
         <v>60</v>
       </c>
@@ -2568,13 +2557,13 @@
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
       <c r="L39" s="11" t="s">
         <v>60</v>
       </c>
@@ -2587,13 +2576,13 @@
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
       <c r="L40" s="11" t="s">
         <v>60</v>
       </c>
@@ -2606,13 +2595,13 @@
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="35"/>
-      <c r="F41" s="35"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="35"/>
-      <c r="I41" s="35"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="35"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
       <c r="L41" s="11" t="s">
         <v>60</v>
       </c>
@@ -2625,13 +2614,13 @@
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="35"/>
-      <c r="F42" s="35"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="35"/>
-      <c r="I42" s="35"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="35"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
       <c r="L42" s="11" t="s">
         <v>60</v>
       </c>
@@ -2644,13 +2633,13 @@
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
       <c r="L43" s="11" t="s">
         <v>60</v>
       </c>
@@ -2663,13 +2652,13 @@
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
       <c r="L44" s="11" t="s">
         <v>60</v>
       </c>
@@ -2682,13 +2671,13 @@
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
       <c r="L45" s="11" t="s">
         <v>60</v>
       </c>
@@ -2701,13 +2690,13 @@
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="35"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="35"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
       <c r="L46" s="11" t="s">
         <v>60</v>
       </c>
@@ -2720,13 +2709,13 @@
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
       <c r="L47" s="11" t="s">
         <v>60</v>
       </c>
@@ -2739,13 +2728,13 @@
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
-      <c r="J48" s="35"/>
-      <c r="K48" s="35"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
       <c r="L48" s="11" t="s">
         <v>60</v>
       </c>
@@ -2758,13 +2747,13 @@
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="35"/>
-      <c r="F49" s="35"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="35"/>
-      <c r="I49" s="35"/>
-      <c r="J49" s="35"/>
-      <c r="K49" s="35"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
       <c r="L49" s="11" t="s">
         <v>60</v>
       </c>
@@ -2777,13 +2766,13 @@
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="35"/>
-      <c r="F50" s="35"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
-      <c r="J50" s="35"/>
-      <c r="K50" s="35"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
       <c r="L50" s="11" t="s">
         <v>60</v>
       </c>
@@ -2796,13 +2785,13 @@
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="35"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="35"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
       <c r="L51" s="11" t="s">
         <v>60</v>
       </c>
@@ -2815,13 +2804,13 @@
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-      <c r="E52" s="35"/>
-      <c r="F52" s="35"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="35"/>
-      <c r="I52" s="35"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="35"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
       <c r="L52" s="11" t="s">
         <v>60</v>
       </c>
@@ -2834,13 +2823,13 @@
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="35"/>
-      <c r="J53" s="35"/>
-      <c r="K53" s="35"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
       <c r="L53" s="11" t="s">
         <v>60</v>
       </c>
@@ -2853,13 +2842,13 @@
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="35"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="35"/>
-      <c r="I54" s="35"/>
-      <c r="J54" s="35"/>
-      <c r="K54" s="35"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
       <c r="L54" s="11" t="s">
         <v>60</v>
       </c>
@@ -2872,13 +2861,13 @@
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="35"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="35"/>
-      <c r="I55" s="35"/>
-      <c r="J55" s="35"/>
-      <c r="K55" s="35"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
       <c r="L55" s="11" t="s">
         <v>60</v>
       </c>
@@ -2891,13 +2880,13 @@
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-      <c r="E56" s="35"/>
-      <c r="F56" s="35"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="35"/>
-      <c r="I56" s="35"/>
-      <c r="J56" s="35"/>
-      <c r="K56" s="35"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
       <c r="L56" s="11" t="s">
         <v>60</v>
       </c>
@@ -2910,13 +2899,13 @@
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-      <c r="E57" s="35"/>
-      <c r="F57" s="35"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="35"/>
-      <c r="I57" s="35"/>
-      <c r="J57" s="35"/>
-      <c r="K57" s="35"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
       <c r="L57" s="11" t="s">
         <v>60</v>
       </c>
@@ -2929,13 +2918,13 @@
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-      <c r="E58" s="35"/>
-      <c r="F58" s="35"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
       <c r="L58" s="11" t="s">
         <v>60</v>
       </c>
@@ -2948,13 +2937,13 @@
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="35"/>
-      <c r="I59" s="35"/>
-      <c r="J59" s="35"/>
-      <c r="K59" s="35"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
       <c r="L59" s="11" t="s">
         <v>60</v>
       </c>
@@ -2967,13 +2956,13 @@
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="35"/>
-      <c r="I60" s="35"/>
-      <c r="J60" s="35"/>
-      <c r="K60" s="35"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="32"/>
       <c r="L60" s="11" t="s">
         <v>60</v>
       </c>
@@ -2986,13 +2975,13 @@
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-      <c r="E61" s="35"/>
-      <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
-      <c r="H61" s="35"/>
-      <c r="I61" s="35"/>
-      <c r="J61" s="35"/>
-      <c r="K61" s="35"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
       <c r="L61" s="11" t="s">
         <v>60</v>
       </c>
@@ -3005,13 +2994,13 @@
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-      <c r="E62" s="35"/>
-      <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
-      <c r="I62" s="35"/>
-      <c r="J62" s="35"/>
-      <c r="K62" s="35"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
       <c r="L62" s="11" t="s">
         <v>60</v>
       </c>
@@ -3024,13 +3013,13 @@
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-      <c r="E63" s="35"/>
-      <c r="F63" s="35"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="35"/>
-      <c r="I63" s="35"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="32"/>
+      <c r="K63" s="32"/>
       <c r="L63" s="11" t="s">
         <v>60</v>
       </c>
@@ -3043,13 +3032,13 @@
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="35"/>
-      <c r="F64" s="35"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="35"/>
-      <c r="I64" s="35"/>
-      <c r="J64" s="35"/>
-      <c r="K64" s="35"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
       <c r="L64" s="11" t="s">
         <v>60</v>
       </c>
@@ -3062,13 +3051,13 @@
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="35"/>
-      <c r="F65" s="35"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
-      <c r="J65" s="35"/>
-      <c r="K65" s="35"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="32"/>
       <c r="L65" s="11" t="s">
         <v>60</v>
       </c>
@@ -3081,13 +3070,13 @@
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="35"/>
-      <c r="F66" s="35"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="35"/>
-      <c r="I66" s="35"/>
-      <c r="J66" s="35"/>
-      <c r="K66" s="35"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="32"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="32"/>
       <c r="L66" s="11" t="s">
         <v>60</v>
       </c>
@@ -3100,13 +3089,13 @@
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="32"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="35"/>
-      <c r="J67" s="35"/>
-      <c r="K67" s="35"/>
+      <c r="E67" s="33"/>
+      <c r="F67" s="33"/>
+      <c r="G67" s="33"/>
+      <c r="H67" s="33"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
       <c r="L67" s="11" t="s">
         <v>60</v>
       </c>
@@ -3119,13 +3108,13 @@
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="35"/>
-      <c r="I68" s="35"/>
-      <c r="J68" s="35"/>
-      <c r="K68" s="35"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
       <c r="L68" s="11" t="s">
         <v>60</v>
       </c>
@@ -3138,13 +3127,13 @@
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="35"/>
-      <c r="F69" s="35"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="35"/>
-      <c r="I69" s="35"/>
-      <c r="J69" s="35"/>
-      <c r="K69" s="35"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
       <c r="L69" s="11" t="s">
         <v>60</v>
       </c>
@@ -3157,13 +3146,13 @@
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="35"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
       <c r="L70" s="11" t="s">
         <v>60</v>
       </c>
@@ -3176,13 +3165,13 @@
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-      <c r="E71" s="35"/>
-      <c r="F71" s="35"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="35"/>
-      <c r="J71" s="35"/>
-      <c r="K71" s="35"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
       <c r="L71" s="11" t="s">
         <v>60</v>
       </c>
@@ -3195,13 +3184,13 @@
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="J72" s="35"/>
-      <c r="K72" s="35"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="32"/>
       <c r="L72" s="11" t="s">
         <v>60</v>
       </c>
@@ -3214,13 +3203,13 @@
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="35"/>
-      <c r="F73" s="35"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="35"/>
-      <c r="I73" s="35"/>
-      <c r="J73" s="35"/>
-      <c r="K73" s="35"/>
+      <c r="E73" s="32"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="32"/>
+      <c r="K73" s="32"/>
       <c r="L73" s="11" t="s">
         <v>60</v>
       </c>
@@ -3233,13 +3222,13 @@
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-      <c r="E74" s="35"/>
-      <c r="F74" s="35"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="35"/>
-      <c r="I74" s="35"/>
-      <c r="J74" s="35"/>
-      <c r="K74" s="35"/>
+      <c r="E74" s="32"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="32"/>
+      <c r="J74" s="32"/>
+      <c r="K74" s="32"/>
       <c r="L74" s="11" t="s">
         <v>60</v>
       </c>
@@ -3252,13 +3241,13 @@
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-      <c r="E75" s="35"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="35"/>
-      <c r="J75" s="35"/>
-      <c r="K75" s="35"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="32"/>
       <c r="L75" s="11" t="s">
         <v>60</v>
       </c>
@@ -3271,13 +3260,13 @@
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-      <c r="E76" s="35"/>
-      <c r="F76" s="35"/>
-      <c r="G76" s="35"/>
-      <c r="H76" s="35"/>
-      <c r="I76" s="35"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="35"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
+      <c r="J76" s="32"/>
+      <c r="K76" s="32"/>
       <c r="L76" s="11" t="s">
         <v>60</v>
       </c>
@@ -3290,13 +3279,13 @@
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="35"/>
-      <c r="G77" s="35"/>
-      <c r="H77" s="35"/>
-      <c r="I77" s="35"/>
-      <c r="J77" s="35"/>
-      <c r="K77" s="35"/>
+      <c r="E77" s="32"/>
+      <c r="F77" s="32"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="32"/>
+      <c r="J77" s="32"/>
+      <c r="K77" s="32"/>
       <c r="L77" s="11" t="s">
         <v>60</v>
       </c>
@@ -3309,13 +3298,13 @@
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-      <c r="E78" s="35"/>
-      <c r="F78" s="35"/>
-      <c r="G78" s="35"/>
-      <c r="H78" s="35"/>
-      <c r="I78" s="35"/>
-      <c r="J78" s="35"/>
-      <c r="K78" s="35"/>
+      <c r="E78" s="32"/>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
+      <c r="J78" s="32"/>
+      <c r="K78" s="32"/>
       <c r="L78" s="11" t="s">
         <v>60</v>
       </c>
@@ -3328,13 +3317,13 @@
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35"/>
-      <c r="G79" s="35"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="35"/>
-      <c r="J79" s="35"/>
-      <c r="K79" s="35"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="32"/>
+      <c r="K79" s="32"/>
       <c r="L79" s="11" t="s">
         <v>60</v>
       </c>
@@ -3347,13 +3336,13 @@
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-      <c r="E80" s="35"/>
-      <c r="F80" s="35"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="35"/>
-      <c r="I80" s="35"/>
-      <c r="J80" s="35"/>
-      <c r="K80" s="35"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
+      <c r="J80" s="32"/>
+      <c r="K80" s="32"/>
       <c r="L80" s="11" t="s">
         <v>60</v>
       </c>
@@ -3366,13 +3355,13 @@
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-      <c r="E81" s="35"/>
-      <c r="F81" s="35"/>
-      <c r="G81" s="35"/>
-      <c r="H81" s="35"/>
-      <c r="I81" s="35"/>
-      <c r="J81" s="35"/>
-      <c r="K81" s="35"/>
+      <c r="E81" s="32"/>
+      <c r="F81" s="32"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
+      <c r="J81" s="32"/>
+      <c r="K81" s="32"/>
       <c r="L81" s="11" t="s">
         <v>60</v>
       </c>
@@ -3385,13 +3374,13 @@
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="35"/>
-      <c r="F82" s="35"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="35"/>
-      <c r="I82" s="35"/>
-      <c r="J82" s="35"/>
-      <c r="K82" s="35"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+      <c r="I82" s="32"/>
+      <c r="J82" s="32"/>
+      <c r="K82" s="32"/>
       <c r="L82" s="11" t="s">
         <v>60</v>
       </c>
@@ -3404,13 +3393,13 @@
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-      <c r="E83" s="35"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="35"/>
-      <c r="H83" s="35"/>
-      <c r="I83" s="35"/>
-      <c r="J83" s="35"/>
-      <c r="K83" s="35"/>
+      <c r="E83" s="32"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
+      <c r="J83" s="32"/>
+      <c r="K83" s="32"/>
       <c r="L83" s="11" t="s">
         <v>60</v>
       </c>
@@ -3423,13 +3412,13 @@
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="35"/>
-      <c r="F84" s="35"/>
-      <c r="G84" s="35"/>
-      <c r="H84" s="35"/>
-      <c r="I84" s="35"/>
-      <c r="J84" s="35"/>
-      <c r="K84" s="35"/>
+      <c r="E84" s="32"/>
+      <c r="F84" s="32"/>
+      <c r="G84" s="32"/>
+      <c r="H84" s="32"/>
+      <c r="I84" s="32"/>
+      <c r="J84" s="32"/>
+      <c r="K84" s="32"/>
       <c r="L84" s="11" t="s">
         <v>60</v>
       </c>
@@ -3442,13 +3431,13 @@
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="35"/>
-      <c r="F85" s="35"/>
-      <c r="G85" s="35"/>
-      <c r="H85" s="35"/>
-      <c r="I85" s="35"/>
-      <c r="J85" s="35"/>
-      <c r="K85" s="35"/>
+      <c r="E85" s="32"/>
+      <c r="F85" s="32"/>
+      <c r="G85" s="32"/>
+      <c r="H85" s="32"/>
+      <c r="I85" s="32"/>
+      <c r="J85" s="32"/>
+      <c r="K85" s="32"/>
       <c r="L85" s="11" t="s">
         <v>60</v>
       </c>
@@ -3461,13 +3450,13 @@
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="35"/>
-      <c r="F86" s="35"/>
-      <c r="G86" s="35"/>
-      <c r="H86" s="35"/>
-      <c r="I86" s="35"/>
-      <c r="J86" s="35"/>
-      <c r="K86" s="35"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
+      <c r="J86" s="32"/>
+      <c r="K86" s="32"/>
       <c r="L86" s="11" t="s">
         <v>60</v>
       </c>
@@ -3480,13 +3469,13 @@
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="35"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="35"/>
-      <c r="J87" s="35"/>
-      <c r="K87" s="35"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
+      <c r="J87" s="32"/>
+      <c r="K87" s="32"/>
       <c r="L87" s="11" t="s">
         <v>60</v>
       </c>
@@ -3499,13 +3488,13 @@
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="35"/>
-      <c r="F88" s="35"/>
-      <c r="G88" s="35"/>
-      <c r="H88" s="35"/>
-      <c r="I88" s="35"/>
-      <c r="J88" s="35"/>
-      <c r="K88" s="35"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+      <c r="I88" s="32"/>
+      <c r="J88" s="32"/>
+      <c r="K88" s="32"/>
       <c r="L88" s="11" t="s">
         <v>60</v>
       </c>
@@ -3518,13 +3507,13 @@
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="35"/>
-      <c r="F89" s="35"/>
-      <c r="G89" s="35"/>
-      <c r="H89" s="35"/>
-      <c r="I89" s="35"/>
-      <c r="J89" s="35"/>
-      <c r="K89" s="35"/>
+      <c r="E89" s="32"/>
+      <c r="F89" s="32"/>
+      <c r="G89" s="32"/>
+      <c r="H89" s="32"/>
+      <c r="I89" s="32"/>
+      <c r="J89" s="32"/>
+      <c r="K89" s="32"/>
       <c r="L89" s="11" t="s">
         <v>60</v>
       </c>
@@ -3537,13 +3526,13 @@
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="35"/>
-      <c r="F90" s="35"/>
-      <c r="G90" s="35"/>
-      <c r="H90" s="35"/>
-      <c r="I90" s="35"/>
-      <c r="J90" s="35"/>
-      <c r="K90" s="35"/>
+      <c r="E90" s="32"/>
+      <c r="F90" s="32"/>
+      <c r="G90" s="32"/>
+      <c r="H90" s="32"/>
+      <c r="I90" s="32"/>
+      <c r="J90" s="32"/>
+      <c r="K90" s="32"/>
       <c r="L90" s="11" t="s">
         <v>60</v>
       </c>
@@ -3556,13 +3545,13 @@
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="35"/>
-      <c r="F91" s="35"/>
-      <c r="G91" s="35"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="35"/>
-      <c r="J91" s="35"/>
-      <c r="K91" s="35"/>
+      <c r="E91" s="32"/>
+      <c r="F91" s="32"/>
+      <c r="G91" s="32"/>
+      <c r="H91" s="32"/>
+      <c r="I91" s="32"/>
+      <c r="J91" s="32"/>
+      <c r="K91" s="32"/>
       <c r="L91" s="11" t="s">
         <v>60</v>
       </c>
@@ -3575,13 +3564,13 @@
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="35"/>
-      <c r="F92" s="35"/>
-      <c r="G92" s="35"/>
-      <c r="H92" s="35"/>
-      <c r="I92" s="35"/>
-      <c r="J92" s="35"/>
-      <c r="K92" s="35"/>
+      <c r="E92" s="32"/>
+      <c r="F92" s="32"/>
+      <c r="G92" s="32"/>
+      <c r="H92" s="32"/>
+      <c r="I92" s="32"/>
+      <c r="J92" s="32"/>
+      <c r="K92" s="32"/>
       <c r="L92" s="11" t="s">
         <v>60</v>
       </c>
@@ -3594,13 +3583,13 @@
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="35"/>
-      <c r="F93" s="35"/>
-      <c r="G93" s="35"/>
-      <c r="H93" s="35"/>
-      <c r="I93" s="35"/>
-      <c r="J93" s="35"/>
-      <c r="K93" s="35"/>
+      <c r="E93" s="32"/>
+      <c r="F93" s="32"/>
+      <c r="G93" s="32"/>
+      <c r="H93" s="32"/>
+      <c r="I93" s="32"/>
+      <c r="J93" s="32"/>
+      <c r="K93" s="32"/>
       <c r="L93" s="11" t="s">
         <v>60</v>
       </c>
@@ -3613,13 +3602,13 @@
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="35"/>
-      <c r="F94" s="35"/>
-      <c r="G94" s="35"/>
-      <c r="H94" s="35"/>
-      <c r="I94" s="35"/>
-      <c r="J94" s="35"/>
-      <c r="K94" s="35"/>
+      <c r="E94" s="32"/>
+      <c r="F94" s="32"/>
+      <c r="G94" s="32"/>
+      <c r="H94" s="32"/>
+      <c r="I94" s="32"/>
+      <c r="J94" s="32"/>
+      <c r="K94" s="32"/>
       <c r="L94" s="11" t="s">
         <v>60</v>
       </c>
@@ -3632,13 +3621,13 @@
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="35"/>
-      <c r="F95" s="35"/>
-      <c r="G95" s="35"/>
-      <c r="H95" s="35"/>
-      <c r="I95" s="35"/>
-      <c r="J95" s="35"/>
-      <c r="K95" s="35"/>
+      <c r="E95" s="32"/>
+      <c r="F95" s="32"/>
+      <c r="G95" s="32"/>
+      <c r="H95" s="32"/>
+      <c r="I95" s="32"/>
+      <c r="J95" s="32"/>
+      <c r="K95" s="32"/>
       <c r="L95" s="11" t="s">
         <v>60</v>
       </c>
@@ -3651,13 +3640,13 @@
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="35"/>
-      <c r="F96" s="35"/>
-      <c r="G96" s="35"/>
-      <c r="H96" s="35"/>
-      <c r="I96" s="35"/>
-      <c r="J96" s="35"/>
-      <c r="K96" s="35"/>
+      <c r="E96" s="32"/>
+      <c r="F96" s="32"/>
+      <c r="G96" s="32"/>
+      <c r="H96" s="32"/>
+      <c r="I96" s="32"/>
+      <c r="J96" s="32"/>
+      <c r="K96" s="32"/>
       <c r="L96" s="11" t="s">
         <v>60</v>
       </c>
@@ -3670,13 +3659,13 @@
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="35"/>
-      <c r="F97" s="35"/>
-      <c r="G97" s="35"/>
-      <c r="H97" s="35"/>
-      <c r="I97" s="35"/>
-      <c r="J97" s="35"/>
-      <c r="K97" s="35"/>
+      <c r="E97" s="32"/>
+      <c r="F97" s="32"/>
+      <c r="G97" s="32"/>
+      <c r="H97" s="32"/>
+      <c r="I97" s="32"/>
+      <c r="J97" s="32"/>
+      <c r="K97" s="32"/>
       <c r="L97" s="11" t="s">
         <v>60</v>
       </c>
@@ -3689,13 +3678,13 @@
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="35"/>
-      <c r="F98" s="35"/>
-      <c r="G98" s="35"/>
-      <c r="H98" s="35"/>
-      <c r="I98" s="35"/>
-      <c r="J98" s="35"/>
-      <c r="K98" s="35"/>
+      <c r="E98" s="32"/>
+      <c r="F98" s="32"/>
+      <c r="G98" s="32"/>
+      <c r="H98" s="32"/>
+      <c r="I98" s="32"/>
+      <c r="J98" s="32"/>
+      <c r="K98" s="32"/>
       <c r="L98" s="11" t="s">
         <v>60</v>
       </c>
@@ -3708,13 +3697,13 @@
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="35"/>
-      <c r="F99" s="35"/>
-      <c r="G99" s="35"/>
-      <c r="H99" s="35"/>
-      <c r="I99" s="35"/>
-      <c r="J99" s="35"/>
-      <c r="K99" s="35"/>
+      <c r="E99" s="32"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="32"/>
+      <c r="H99" s="32"/>
+      <c r="I99" s="32"/>
+      <c r="J99" s="32"/>
+      <c r="K99" s="32"/>
       <c r="L99" s="11" t="s">
         <v>60</v>
       </c>
@@ -3727,13 +3716,13 @@
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="35"/>
-      <c r="F100" s="35"/>
-      <c r="G100" s="35"/>
-      <c r="H100" s="35"/>
-      <c r="I100" s="35"/>
-      <c r="J100" s="35"/>
-      <c r="K100" s="35"/>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+      <c r="I100" s="32"/>
+      <c r="J100" s="32"/>
+      <c r="K100" s="32"/>
       <c r="L100" s="11" t="s">
         <v>60</v>
       </c>
@@ -3741,50 +3730,135 @@
     </row>
   </sheetData>
   <mergeCells count="197">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E27:H27"/>
+    <mergeCell ref="E28:H28"/>
+    <mergeCell ref="E29:H29"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -3809,135 +3883,50 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">

--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -1,48 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1AA49F-F70F-4D26-8670-00058D87B19E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305F9200-A857-463B-BCAA-81F230598A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
-    <sheet name="TC" sheetId="2" r:id="rId2"/>
-    <sheet name="버그" sheetId="4" r:id="rId3"/>
-    <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId4"/>
+    <sheet name="편의성" sheetId="10" r:id="rId2"/>
+    <sheet name="TC" sheetId="2" r:id="rId3"/>
+    <sheet name="버그" sheetId="4" r:id="rId4"/>
+    <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -60,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="203">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -732,19 +744,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기획</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>먼저 힌트 봇으로 "2개에 숫자는 반전한다." 로 힌트를 주고 숫자 7, 3이라고 순서대로 찾을 수 있게 만든다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>6X6 판을 만들어 A~Z까지 배치 후 힌트로 사용할 알파벳만 7개와 3개를 따로 규정하여 배치하고 그 이외는 랜덤으로 설정한다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>힌트로 사용될 기물은 히드라를 토대로 모양을 따 배치된 알파벳 위치에 따라서 머리를 배치하는 것으로 사용</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -770,6 +774,88 @@
   </si>
   <si>
     <t>모든 씬에서 적 오브젝트가 등장 시 커서 오브젝트 보다 앞에 있기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>힌트로 사용될 기물은 배치되는 알파벳 위치에 따라서 확인 후 맞춤제작 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체셔를 사용하는것으로 해결</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정 의견 및 해결 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱크대에서 수도꼭지보다 큰 사각형 박스 형식으로 물이 내려오는 방식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물에 넓이를 줄이고 흐르기 시작하는 것이 아닌 수도꼭지를 키면 물이 한번에 생겨서 흐르는 형식과 물 소리를 추가하는 형식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">책장 4개을 그대로 활용
+특정 알파벳을 찾기 (RED, BLUE) 7자 체크 
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그대로 기용하고 퍼즐형식 기물을 지급 예정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">게임 플레이 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문이 열린 것을 육안으로 체크할 수 있게 변경하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오른쪽 복도 끝 방에서 열쇠를 사용하여도 문이 열리는 장면이 육안으로 확인 불가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서재 기획(기존 기획에서 변경 기용)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>게임플레이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가정부 방에서 자물쇠 번호를 확인함에 있어 힌트가 없음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가적인 힌트를 지정을 해서 책 속을 확인해서 힌트를 알 수 있게 변경하기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">게임플레이 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가정부 방에서 나온 뒤에 지도를 확인하면 방이 다시 잠겨 있는 것을 볼 수 있음</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도에서 가정부 방을 연 후 지도에서 연 상태로 보이게 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유저 편의성 테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1주차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2주차</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -777,7 +863,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -866,8 +952,16 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -909,8 +1003,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -964,6 +1070,43 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -977,7 +1120,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1032,21 +1175,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1062,32 +1196,101 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1121,6 +1324,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1129,7 +1341,7 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
     <cellStyle name="표준 2" xfId="2" xr:uid="{E5ED1C55-8C74-49FF-A6AC-1A927F2C2FB4}"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill>
@@ -1170,6 +1382,22 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF99FF99"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.89996032593768116"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1634,55 +1862,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB156A54-7967-4D1A-B536-B4953C786998}">
-  <dimension ref="A1:M100"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q100"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.75" customWidth="1"/>
-    <col min="2" max="2" width="5.625" style="19" customWidth="1"/>
-    <col min="3" max="3" width="14.625" style="19" customWidth="1"/>
-    <col min="4" max="4" width="33.625" style="19" customWidth="1"/>
-    <col min="5" max="7" width="15.625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="18" customWidth="1"/>
+    <col min="3" max="3" width="14.625" style="18" customWidth="1"/>
+    <col min="4" max="4" width="33.625" style="18" customWidth="1"/>
+    <col min="5" max="7" width="15.625" style="19" customWidth="1"/>
     <col min="8" max="8" width="0.375" customWidth="1"/>
-    <col min="9" max="11" width="30.625" style="20" customWidth="1"/>
-    <col min="12" max="12" width="18" style="30" customWidth="1"/>
+    <col min="9" max="11" width="30.625" style="19" customWidth="1"/>
+    <col min="12" max="12" width="18" style="25" customWidth="1"/>
     <col min="13" max="13" width="44.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="35"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1691,17 +1919,17 @@
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="36" t="s">
+      <c r="E3" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="36"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="36"/>
-      <c r="I3" s="36" t="s">
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
       <c r="L3" s="5" t="s">
         <v>59</v>
       </c>
@@ -1709,2156 +1937,2112 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="204.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="204.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="28">
         <v>46088</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33" t="s">
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
       <c r="L4" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M4" s="8"/>
     </row>
-    <row r="5" spans="1:13" ht="173.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="173.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="28">
         <v>46088</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="33" t="s">
+      <c r="E5" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33" t="s">
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
       <c r="L5" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M5" s="8"/>
     </row>
-    <row r="6" spans="1:13" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="258.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="28">
         <v>46090</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33" t="s">
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
       <c r="L6" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M6" s="8"/>
     </row>
-    <row r="7" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="36.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="28">
         <v>46090</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="E7" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="33" t="s">
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
       <c r="L7" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M7" s="8"/>
     </row>
-    <row r="8" spans="1:13" ht="121.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="121.5" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="28">
         <v>46092</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="33" t="s">
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
       <c r="L8" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M8" s="8"/>
     </row>
-    <row r="9" spans="1:13" ht="123.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="123.75" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="28">
         <v>46092</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="33" t="s">
+      <c r="E9" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="33" t="s">
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
       <c r="L9" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M9" s="8"/>
     </row>
-    <row r="10" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="28">
         <v>46095</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="33" t="s">
+      <c r="E10" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="33" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
       <c r="L10" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M10" s="8"/>
     </row>
-    <row r="11" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="28">
         <v>46095</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
       <c r="L11" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M11" s="8"/>
     </row>
-    <row r="12" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="28">
         <v>46096</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33" t="s">
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="K12" s="33"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
       <c r="L12" s="11" t="s">
         <v>62</v>
       </c>
       <c r="M12" s="8"/>
     </row>
-    <row r="13" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="28">
         <v>46096</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33" t="s">
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="33"/>
-      <c r="K13" s="33"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
       <c r="L13" s="11" t="s">
-        <v>172</v>
+        <v>60</v>
       </c>
       <c r="M13" s="8"/>
     </row>
-    <row r="14" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="33">
         <v>46098</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="33"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33" t="s">
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
       <c r="L14" s="11" t="s">
         <v>62</v>
       </c>
       <c r="M14" s="8"/>
     </row>
-    <row r="15" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="34">
         <v>46103</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="33"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33" t="s">
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="33"/>
-      <c r="K15" s="33"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
       <c r="L15" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M15" s="8"/>
     </row>
-    <row r="16" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="34">
         <v>46103</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="33" t="s">
+      <c r="E16" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
       <c r="L16" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M16" s="8"/>
     </row>
-    <row r="17" spans="1:13" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="34">
         <v>46103</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="33" t="s">
+      <c r="E17" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33" t="s">
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
       <c r="L17" s="11" t="s">
         <v>172</v>
       </c>
       <c r="M17" s="8"/>
     </row>
-    <row r="18" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23"/>
-      <c r="B18" s="24" t="s">
+    <row r="18" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="20"/>
+      <c r="B18" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="34">
         <v>46107</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="33" t="s">
+      <c r="E18" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33" t="s">
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
       <c r="L18" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="M18" s="23"/>
-    </row>
-    <row r="19" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24" t="s">
+      <c r="M18" s="20"/>
+    </row>
+    <row r="19" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="20"/>
+      <c r="B19" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="34">
         <v>46107</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32" t="s">
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
       <c r="L19" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="M19" s="23"/>
-    </row>
-    <row r="20" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23"/>
-      <c r="B20" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="M19" s="20"/>
+    </row>
+    <row r="20" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="20"/>
+      <c r="B20" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="34">
         <v>46107</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32" t="s">
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
       <c r="L20" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M20" s="23"/>
-    </row>
-    <row r="21" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23"/>
-      <c r="B21" s="24" t="s">
+      <c r="M20" s="20"/>
+    </row>
+    <row r="21" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="20"/>
+      <c r="B21" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="34">
         <v>46107</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32" t="s">
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
       <c r="L21" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="M21" s="23"/>
-    </row>
-    <row r="22" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23"/>
-      <c r="B22" s="24" t="s">
+      <c r="M21" s="20"/>
+    </row>
+    <row r="22" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20"/>
+      <c r="B22" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="22">
+      <c r="C22" s="34">
         <v>46113</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32" t="s">
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
       <c r="L22" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="M22" s="23"/>
-    </row>
-    <row r="23" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23"/>
-      <c r="B23" s="24" t="s">
+      <c r="M22" s="20"/>
+    </row>
+    <row r="23" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="20"/>
+      <c r="B23" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="C23" s="22">
+      <c r="C23" s="34">
         <v>46117</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="34" t="s">
+      <c r="E23" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M23" s="20"/>
+    </row>
+    <row r="24" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="20"/>
+      <c r="B24" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="34">
+        <v>46117</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="32" t="s">
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M23" s="23"/>
-    </row>
-    <row r="24" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23"/>
-      <c r="B24" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="22">
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M24" s="20"/>
+    </row>
+    <row r="25" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20"/>
+      <c r="B25" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="34">
         <v>46117</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D25" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="34" t="s">
+      <c r="E25" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="F24" s="34"/>
-      <c r="G24" s="34"/>
-      <c r="H24" s="34"/>
-      <c r="I24" s="32" t="s">
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M24" s="23"/>
-    </row>
-    <row r="25" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="23"/>
-      <c r="B25" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="22">
-        <v>46117</v>
-      </c>
-      <c r="D25" s="11" t="s">
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M25" s="20"/>
+    </row>
+    <row r="26" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="20"/>
+      <c r="B26" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="36">
+        <v>46120</v>
+      </c>
+      <c r="D26" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="34" t="s">
-        <v>183</v>
-      </c>
-      <c r="F25" s="34"/>
-      <c r="G25" s="34"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="32" t="s">
-        <v>184</v>
-      </c>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M25" s="23"/>
-    </row>
-    <row r="26" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="23"/>
-      <c r="B26" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
+      <c r="E26" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
       <c r="L26" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M26" s="23"/>
-    </row>
-    <row r="27" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23"/>
-      <c r="B27" s="24" t="s">
+      <c r="M26" s="20"/>
+      <c r="P26" s="40" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q26" s="41" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="20"/>
+      <c r="B27" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
+      <c r="C27" s="36">
+        <v>46120</v>
+      </c>
+      <c r="D27" s="37" t="s">
+        <v>190</v>
+      </c>
+      <c r="E27" s="50" t="s">
+        <v>192</v>
+      </c>
+      <c r="F27" s="51"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="J27" s="55"/>
+      <c r="K27" s="56"/>
       <c r="L27" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M27" s="23"/>
-    </row>
-    <row r="28" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="23"/>
-      <c r="B28" s="24" t="s">
+      <c r="M27" s="20"/>
+    </row>
+    <row r="28" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="20"/>
+      <c r="B28" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
+      <c r="C28" s="36">
+        <v>46120</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>194</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="39"/>
+      <c r="G28" s="39"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="J28" s="39"/>
+      <c r="K28" s="39"/>
       <c r="L28" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M28" s="23"/>
-    </row>
-    <row r="29" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="23"/>
-      <c r="B29" s="24" t="s">
+      <c r="M28" s="20"/>
+    </row>
+    <row r="29" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="20"/>
+      <c r="B29" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
+      <c r="C29" s="36">
+        <v>46120</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="F29" s="51"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="54" t="s">
+        <v>199</v>
+      </c>
+      <c r="J29" s="55"/>
+      <c r="K29" s="56"/>
       <c r="L29" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M29" s="23"/>
-    </row>
-    <row r="30" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="23"/>
-      <c r="B30" s="24" t="s">
+      <c r="M29" s="20"/>
+    </row>
+    <row r="30" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="20"/>
+      <c r="B30" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
+      <c r="C30" s="36">
+        <v>46120</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="49"/>
+      <c r="I30" s="49"/>
+      <c r="J30" s="49"/>
+      <c r="K30" s="49"/>
       <c r="L30" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M30" s="23"/>
-    </row>
-    <row r="31" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="23"/>
-      <c r="B31" s="24" t="s">
+      <c r="M30" s="20"/>
+    </row>
+    <row r="31" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="20"/>
+      <c r="B31" s="21" t="s">
         <v>86</v>
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
       <c r="L31" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M31" s="23"/>
-    </row>
-    <row r="32" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="23"/>
-      <c r="B32" s="24" t="s">
+      <c r="M31" s="20"/>
+    </row>
+    <row r="32" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="20"/>
+      <c r="B32" s="21" t="s">
         <v>87</v>
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
       <c r="L32" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M32" s="23"/>
-    </row>
-    <row r="33" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="23"/>
-      <c r="B33" s="24" t="s">
+      <c r="M32" s="20"/>
+    </row>
+    <row r="33" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="20"/>
+      <c r="B33" s="21" t="s">
         <v>88</v>
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
       <c r="L33" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M33" s="23"/>
-    </row>
-    <row r="34" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="23"/>
-      <c r="B34" s="24" t="s">
+      <c r="M33" s="20"/>
+    </row>
+    <row r="34" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="20"/>
+      <c r="B34" s="21" t="s">
         <v>89</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
       <c r="L34" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M34" s="23"/>
-    </row>
-    <row r="35" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="23"/>
-      <c r="B35" s="24" t="s">
+      <c r="M34" s="20"/>
+    </row>
+    <row r="35" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="20"/>
+      <c r="B35" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
       <c r="L35" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M35" s="23"/>
-    </row>
-    <row r="36" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="23"/>
-      <c r="B36" s="24" t="s">
+      <c r="M35" s="20"/>
+    </row>
+    <row r="36" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="20"/>
+      <c r="B36" s="21" t="s">
         <v>91</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
       <c r="L36" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M36" s="23"/>
-    </row>
-    <row r="37" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="23"/>
-      <c r="B37" s="24" t="s">
+      <c r="M36" s="20"/>
+    </row>
+    <row r="37" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="20"/>
+      <c r="B37" s="21" t="s">
         <v>92</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
       <c r="L37" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M37" s="23"/>
-    </row>
-    <row r="38" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="23"/>
-      <c r="B38" s="24" t="s">
+      <c r="M37" s="20"/>
+    </row>
+    <row r="38" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="20"/>
+      <c r="B38" s="21" t="s">
         <v>93</v>
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="48"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="48"/>
       <c r="L38" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M38" s="23"/>
-    </row>
-    <row r="39" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="23"/>
-      <c r="B39" s="24" t="s">
+      <c r="M38" s="20"/>
+    </row>
+    <row r="39" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="20"/>
+      <c r="B39" s="21" t="s">
         <v>94</v>
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
       <c r="L39" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M39" s="23"/>
-    </row>
-    <row r="40" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="23"/>
-      <c r="B40" s="24" t="s">
+      <c r="M39" s="20"/>
+    </row>
+    <row r="40" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="20"/>
+      <c r="B40" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
       <c r="L40" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M40" s="23"/>
-    </row>
-    <row r="41" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="23"/>
-      <c r="B41" s="24" t="s">
+      <c r="M40" s="20"/>
+    </row>
+    <row r="41" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="20"/>
+      <c r="B41" s="21" t="s">
         <v>96</v>
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
       <c r="L41" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M41" s="23"/>
-    </row>
-    <row r="42" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="23"/>
-      <c r="B42" s="24" t="s">
+      <c r="M41" s="20"/>
+    </row>
+    <row r="42" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="20"/>
+      <c r="B42" s="21" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="48"/>
       <c r="L42" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M42" s="23"/>
-    </row>
-    <row r="43" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="23"/>
-      <c r="B43" s="24" t="s">
+      <c r="M42" s="20"/>
+    </row>
+    <row r="43" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="20"/>
+      <c r="B43" s="21" t="s">
         <v>98</v>
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
       <c r="L43" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M43" s="23"/>
-    </row>
-    <row r="44" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="23"/>
-      <c r="B44" s="24" t="s">
+      <c r="M43" s="20"/>
+    </row>
+    <row r="44" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="20"/>
+      <c r="B44" s="21" t="s">
         <v>99</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="32"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
       <c r="L44" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M44" s="23"/>
-    </row>
-    <row r="45" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="23"/>
-      <c r="B45" s="24" t="s">
+      <c r="M44" s="20"/>
+    </row>
+    <row r="45" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="20"/>
+      <c r="B45" s="21" t="s">
         <v>100</v>
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="32"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
       <c r="L45" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M45" s="23"/>
-    </row>
-    <row r="46" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="23"/>
-      <c r="B46" s="24" t="s">
+      <c r="M45" s="20"/>
+    </row>
+    <row r="46" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="20"/>
+      <c r="B46" s="21" t="s">
         <v>101</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="32"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
       <c r="L46" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M46" s="23"/>
-    </row>
-    <row r="47" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="23"/>
-      <c r="B47" s="24" t="s">
+      <c r="M46" s="20"/>
+    </row>
+    <row r="47" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="20"/>
+      <c r="B47" s="21" t="s">
         <v>102</v>
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="32"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
       <c r="L47" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M47" s="23"/>
-    </row>
-    <row r="48" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="23"/>
-      <c r="B48" s="24" t="s">
+      <c r="M47" s="20"/>
+    </row>
+    <row r="48" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="20"/>
+      <c r="B48" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="32"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
       <c r="L48" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M48" s="23"/>
-    </row>
-    <row r="49" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="23"/>
-      <c r="B49" s="24" t="s">
+      <c r="M48" s="20"/>
+    </row>
+    <row r="49" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="20"/>
+      <c r="B49" s="21" t="s">
         <v>104</v>
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
       <c r="L49" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M49" s="23"/>
-    </row>
-    <row r="50" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="23"/>
-      <c r="B50" s="24" t="s">
+      <c r="M49" s="20"/>
+    </row>
+    <row r="50" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="20"/>
+      <c r="B50" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="32"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="48"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="48"/>
       <c r="L50" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M50" s="23"/>
-    </row>
-    <row r="51" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="23"/>
-      <c r="B51" s="24" t="s">
+      <c r="M50" s="20"/>
+    </row>
+    <row r="51" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="20"/>
+      <c r="B51" s="21" t="s">
         <v>106</v>
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
       <c r="L51" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M51" s="23"/>
-    </row>
-    <row r="52" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="23"/>
-      <c r="B52" s="24" t="s">
+      <c r="M51" s="20"/>
+    </row>
+    <row r="52" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="20"/>
+      <c r="B52" s="21" t="s">
         <v>107</v>
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="48"/>
+      <c r="I52" s="48"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="48"/>
       <c r="L52" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M52" s="23"/>
-    </row>
-    <row r="53" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="23"/>
-      <c r="B53" s="24" t="s">
+      <c r="M52" s="20"/>
+    </row>
+    <row r="53" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="20"/>
+      <c r="B53" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="32"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
       <c r="L53" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M53" s="23"/>
-    </row>
-    <row r="54" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="23"/>
-      <c r="B54" s="24" t="s">
+      <c r="M53" s="20"/>
+    </row>
+    <row r="54" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="20"/>
+      <c r="B54" s="21" t="s">
         <v>109</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="48"/>
+      <c r="H54" s="48"/>
+      <c r="I54" s="48"/>
+      <c r="J54" s="48"/>
+      <c r="K54" s="48"/>
       <c r="L54" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M54" s="23"/>
-    </row>
-    <row r="55" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="23"/>
-      <c r="B55" s="24" t="s">
+      <c r="M54" s="20"/>
+    </row>
+    <row r="55" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="20"/>
+      <c r="B55" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
       <c r="L55" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M55" s="23"/>
-    </row>
-    <row r="56" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="23"/>
-      <c r="B56" s="24" t="s">
+      <c r="M55" s="20"/>
+    </row>
+    <row r="56" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="20"/>
+      <c r="B56" s="21" t="s">
         <v>111</v>
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="32"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="48"/>
       <c r="L56" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M56" s="23"/>
-    </row>
-    <row r="57" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="23"/>
-      <c r="B57" s="24" t="s">
+      <c r="M56" s="20"/>
+    </row>
+    <row r="57" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="20"/>
+      <c r="B57" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
       <c r="L57" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M57" s="23"/>
-    </row>
-    <row r="58" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="23"/>
-      <c r="B58" s="24" t="s">
+      <c r="M57" s="20"/>
+    </row>
+    <row r="58" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="20"/>
+      <c r="B58" s="21" t="s">
         <v>113</v>
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
       <c r="L58" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M58" s="23"/>
-    </row>
-    <row r="59" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="23"/>
-      <c r="B59" s="24" t="s">
+      <c r="M58" s="20"/>
+    </row>
+    <row r="59" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="20"/>
+      <c r="B59" s="21" t="s">
         <v>114</v>
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
       <c r="L59" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M59" s="23"/>
-    </row>
-    <row r="60" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="23"/>
-      <c r="B60" s="24" t="s">
+      <c r="M59" s="20"/>
+    </row>
+    <row r="60" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="20"/>
+      <c r="B60" s="21" t="s">
         <v>115</v>
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="32"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
       <c r="L60" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M60" s="23"/>
-    </row>
-    <row r="61" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="23"/>
-      <c r="B61" s="24" t="s">
+      <c r="M60" s="20"/>
+    </row>
+    <row r="61" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="20"/>
+      <c r="B61" s="21" t="s">
         <v>116</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="32"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
       <c r="L61" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M61" s="23"/>
-    </row>
-    <row r="62" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="23"/>
-      <c r="B62" s="24" t="s">
+      <c r="M61" s="20"/>
+    </row>
+    <row r="62" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="20"/>
+      <c r="B62" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="32"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
       <c r="L62" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M62" s="23"/>
-    </row>
-    <row r="63" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="23"/>
-      <c r="B63" s="24" t="s">
+      <c r="M62" s="20"/>
+    </row>
+    <row r="63" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="20"/>
+      <c r="B63" s="21" t="s">
         <v>118</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="32"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
       <c r="L63" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M63" s="23"/>
-    </row>
-    <row r="64" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="23"/>
-      <c r="B64" s="24" t="s">
+      <c r="M63" s="20"/>
+    </row>
+    <row r="64" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="20"/>
+      <c r="B64" s="21" t="s">
         <v>119</v>
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="32"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
       <c r="L64" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M64" s="23"/>
-    </row>
-    <row r="65" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="23"/>
-      <c r="B65" s="24" t="s">
+      <c r="M64" s="20"/>
+    </row>
+    <row r="65" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="20"/>
+      <c r="B65" s="21" t="s">
         <v>120</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="32"/>
-      <c r="K65" s="32"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="48"/>
       <c r="L65" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M65" s="23"/>
-    </row>
-    <row r="66" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="23"/>
-      <c r="B66" s="24" t="s">
+      <c r="M65" s="20"/>
+    </row>
+    <row r="66" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="20"/>
+      <c r="B66" s="21" t="s">
         <v>121</v>
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="32"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="32"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
       <c r="L66" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M66" s="23"/>
-    </row>
-    <row r="67" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="23"/>
-      <c r="B67" s="24" t="s">
+      <c r="M66" s="20"/>
+    </row>
+    <row r="67" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="20"/>
+      <c r="B67" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="33"/>
-      <c r="H67" s="33"/>
-      <c r="I67" s="32"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="32"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="53"/>
+      <c r="H67" s="53"/>
+      <c r="I67" s="48"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
       <c r="L67" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M67" s="23"/>
-    </row>
-    <row r="68" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="23"/>
-      <c r="B68" s="24" t="s">
+      <c r="M67" s="20"/>
+    </row>
+    <row r="68" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="20"/>
+      <c r="B68" s="21" t="s">
         <v>123</v>
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="32"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="48"/>
       <c r="L68" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M68" s="23"/>
-    </row>
-    <row r="69" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="23"/>
-      <c r="B69" s="24" t="s">
+      <c r="M68" s="20"/>
+    </row>
+    <row r="69" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="20"/>
+      <c r="B69" s="21" t="s">
         <v>124</v>
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="48"/>
+      <c r="I69" s="48"/>
+      <c r="J69" s="48"/>
+      <c r="K69" s="48"/>
       <c r="L69" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M69" s="23"/>
-    </row>
-    <row r="70" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="23"/>
-      <c r="B70" s="24" t="s">
+      <c r="M69" s="20"/>
+    </row>
+    <row r="70" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="20"/>
+      <c r="B70" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
       <c r="L70" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M70" s="23"/>
-    </row>
-    <row r="71" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="23"/>
-      <c r="B71" s="24" t="s">
+      <c r="M70" s="20"/>
+    </row>
+    <row r="71" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="20"/>
+      <c r="B71" s="21" t="s">
         <v>126</v>
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
       <c r="L71" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M71" s="23"/>
-    </row>
-    <row r="72" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="23"/>
-      <c r="B72" s="24" t="s">
+      <c r="M71" s="20"/>
+    </row>
+    <row r="72" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="20"/>
+      <c r="B72" s="21" t="s">
         <v>127</v>
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="32"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="48"/>
       <c r="L72" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M72" s="23"/>
-    </row>
-    <row r="73" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="23"/>
-      <c r="B73" s="24" t="s">
+      <c r="M72" s="20"/>
+    </row>
+    <row r="73" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="20"/>
+      <c r="B73" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="32"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="32"/>
+      <c r="E73" s="48"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="48"/>
+      <c r="H73" s="48"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="48"/>
+      <c r="K73" s="48"/>
       <c r="L73" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M73" s="23"/>
-    </row>
-    <row r="74" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="23"/>
-      <c r="B74" s="24" t="s">
+      <c r="M73" s="20"/>
+    </row>
+    <row r="74" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="20"/>
+      <c r="B74" s="21" t="s">
         <v>129</v>
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="32"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="48"/>
+      <c r="K74" s="48"/>
       <c r="L74" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M74" s="23"/>
-    </row>
-    <row r="75" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="23"/>
-      <c r="B75" s="24" t="s">
+      <c r="M74" s="20"/>
+    </row>
+    <row r="75" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="20"/>
+      <c r="B75" s="21" t="s">
         <v>130</v>
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
-      <c r="J75" s="32"/>
-      <c r="K75" s="32"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
       <c r="L75" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M75" s="23"/>
-    </row>
-    <row r="76" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="23"/>
-      <c r="B76" s="24" t="s">
+      <c r="M75" s="20"/>
+    </row>
+    <row r="76" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="20"/>
+      <c r="B76" s="21" t="s">
         <v>131</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
-      <c r="J76" s="32"/>
-      <c r="K76" s="32"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="48"/>
+      <c r="K76" s="48"/>
       <c r="L76" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M76" s="23"/>
-    </row>
-    <row r="77" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="23"/>
-      <c r="B77" s="24" t="s">
+      <c r="M76" s="20"/>
+    </row>
+    <row r="77" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="20"/>
+      <c r="B77" s="21" t="s">
         <v>132</v>
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-      <c r="E77" s="32"/>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="32"/>
-      <c r="J77" s="32"/>
-      <c r="K77" s="32"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="48"/>
+      <c r="H77" s="48"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="48"/>
+      <c r="K77" s="48"/>
       <c r="L77" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M77" s="23"/>
-    </row>
-    <row r="78" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="23"/>
-      <c r="B78" s="24" t="s">
+      <c r="M77" s="20"/>
+    </row>
+    <row r="78" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="20"/>
+      <c r="B78" s="21" t="s">
         <v>133</v>
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="32"/>
-      <c r="K78" s="32"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="48"/>
       <c r="L78" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M78" s="23"/>
-    </row>
-    <row r="79" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="23"/>
-      <c r="B79" s="24" t="s">
+      <c r="M78" s="20"/>
+    </row>
+    <row r="79" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="20"/>
+      <c r="B79" s="21" t="s">
         <v>134</v>
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="32"/>
-      <c r="K79" s="32"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="48"/>
       <c r="L79" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M79" s="23"/>
-    </row>
-    <row r="80" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="23"/>
-      <c r="B80" s="24" t="s">
+      <c r="M79" s="20"/>
+    </row>
+    <row r="80" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="20"/>
+      <c r="B80" s="21" t="s">
         <v>135</v>
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="32"/>
+      <c r="E80" s="48"/>
+      <c r="F80" s="48"/>
+      <c r="G80" s="48"/>
+      <c r="H80" s="48"/>
+      <c r="I80" s="48"/>
+      <c r="J80" s="48"/>
+      <c r="K80" s="48"/>
       <c r="L80" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M80" s="23"/>
-    </row>
-    <row r="81" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="23"/>
-      <c r="B81" s="24" t="s">
+      <c r="M80" s="20"/>
+    </row>
+    <row r="81" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="20"/>
+      <c r="B81" s="21" t="s">
         <v>136</v>
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-      <c r="E81" s="32"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="32"/>
-      <c r="J81" s="32"/>
-      <c r="K81" s="32"/>
+      <c r="E81" s="48"/>
+      <c r="F81" s="48"/>
+      <c r="G81" s="48"/>
+      <c r="H81" s="48"/>
+      <c r="I81" s="48"/>
+      <c r="J81" s="48"/>
+      <c r="K81" s="48"/>
       <c r="L81" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M81" s="23"/>
-    </row>
-    <row r="82" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="23"/>
-      <c r="B82" s="24" t="s">
+      <c r="M81" s="20"/>
+    </row>
+    <row r="82" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="20"/>
+      <c r="B82" s="21" t="s">
         <v>137</v>
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="32"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
-      <c r="J82" s="32"/>
-      <c r="K82" s="32"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="48"/>
+      <c r="G82" s="48"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="48"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="48"/>
       <c r="L82" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M82" s="23"/>
-    </row>
-    <row r="83" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="23"/>
-      <c r="B83" s="24" t="s">
+      <c r="M82" s="20"/>
+    </row>
+    <row r="83" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="20"/>
+      <c r="B83" s="21" t="s">
         <v>138</v>
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-      <c r="E83" s="32"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="32"/>
-      <c r="I83" s="32"/>
-      <c r="J83" s="32"/>
-      <c r="K83" s="32"/>
+      <c r="E83" s="48"/>
+      <c r="F83" s="48"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="48"/>
+      <c r="I83" s="48"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48"/>
       <c r="L83" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M83" s="23"/>
-    </row>
-    <row r="84" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="23"/>
-      <c r="B84" s="24" t="s">
+      <c r="M83" s="20"/>
+    </row>
+    <row r="84" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="20"/>
+      <c r="B84" s="21" t="s">
         <v>139</v>
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="32"/>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="32"/>
-      <c r="I84" s="32"/>
-      <c r="J84" s="32"/>
-      <c r="K84" s="32"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="48"/>
       <c r="L84" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M84" s="23"/>
-    </row>
-    <row r="85" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="23"/>
-      <c r="B85" s="24" t="s">
+      <c r="M84" s="20"/>
+    </row>
+    <row r="85" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="20"/>
+      <c r="B85" s="21" t="s">
         <v>140</v>
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="32"/>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
-      <c r="J85" s="32"/>
-      <c r="K85" s="32"/>
+      <c r="E85" s="48"/>
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
+      <c r="H85" s="48"/>
+      <c r="I85" s="48"/>
+      <c r="J85" s="48"/>
+      <c r="K85" s="48"/>
       <c r="L85" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M85" s="23"/>
-    </row>
-    <row r="86" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="23"/>
-      <c r="B86" s="24" t="s">
+      <c r="M85" s="20"/>
+    </row>
+    <row r="86" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="20"/>
+      <c r="B86" s="21" t="s">
         <v>141</v>
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="32"/>
-      <c r="I86" s="32"/>
-      <c r="J86" s="32"/>
-      <c r="K86" s="32"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
+      <c r="J86" s="48"/>
+      <c r="K86" s="48"/>
       <c r="L86" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M86" s="23"/>
-    </row>
-    <row r="87" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="23"/>
-      <c r="B87" s="24" t="s">
+      <c r="M86" s="20"/>
+    </row>
+    <row r="87" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="20"/>
+      <c r="B87" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
-      <c r="J87" s="32"/>
-      <c r="K87" s="32"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
       <c r="L87" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M87" s="23"/>
-    </row>
-    <row r="88" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="23"/>
-      <c r="B88" s="24" t="s">
+      <c r="M87" s="20"/>
+    </row>
+    <row r="88" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="20"/>
+      <c r="B88" s="21" t="s">
         <v>143</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
-      <c r="J88" s="32"/>
-      <c r="K88" s="32"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
+      <c r="J88" s="48"/>
+      <c r="K88" s="48"/>
       <c r="L88" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M88" s="23"/>
-    </row>
-    <row r="89" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="23"/>
-      <c r="B89" s="24" t="s">
+      <c r="M88" s="20"/>
+    </row>
+    <row r="89" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="20"/>
+      <c r="B89" s="21" t="s">
         <v>144</v>
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="32"/>
-      <c r="F89" s="32"/>
-      <c r="G89" s="32"/>
-      <c r="H89" s="32"/>
-      <c r="I89" s="32"/>
-      <c r="J89" s="32"/>
-      <c r="K89" s="32"/>
+      <c r="E89" s="48"/>
+      <c r="F89" s="48"/>
+      <c r="G89" s="48"/>
+      <c r="H89" s="48"/>
+      <c r="I89" s="48"/>
+      <c r="J89" s="48"/>
+      <c r="K89" s="48"/>
       <c r="L89" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M89" s="23"/>
-    </row>
-    <row r="90" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="23"/>
-      <c r="B90" s="24" t="s">
+      <c r="M89" s="20"/>
+    </row>
+    <row r="90" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="20"/>
+      <c r="B90" s="21" t="s">
         <v>145</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="32"/>
-      <c r="F90" s="32"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="32"/>
-      <c r="I90" s="32"/>
-      <c r="J90" s="32"/>
-      <c r="K90" s="32"/>
+      <c r="E90" s="48"/>
+      <c r="F90" s="48"/>
+      <c r="G90" s="48"/>
+      <c r="H90" s="48"/>
+      <c r="I90" s="48"/>
+      <c r="J90" s="48"/>
+      <c r="K90" s="48"/>
       <c r="L90" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M90" s="23"/>
-    </row>
-    <row r="91" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="23"/>
-      <c r="B91" s="24" t="s">
+      <c r="M90" s="20"/>
+    </row>
+    <row r="91" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="20"/>
+      <c r="B91" s="21" t="s">
         <v>146</v>
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="32"/>
-      <c r="F91" s="32"/>
-      <c r="G91" s="32"/>
-      <c r="H91" s="32"/>
-      <c r="I91" s="32"/>
-      <c r="J91" s="32"/>
-      <c r="K91" s="32"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="48"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="48"/>
       <c r="L91" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M91" s="23"/>
-    </row>
-    <row r="92" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="23"/>
-      <c r="B92" s="24" t="s">
+      <c r="M91" s="20"/>
+    </row>
+    <row r="92" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="20"/>
+      <c r="B92" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="32"/>
-      <c r="F92" s="32"/>
-      <c r="G92" s="32"/>
-      <c r="H92" s="32"/>
-      <c r="I92" s="32"/>
-      <c r="J92" s="32"/>
-      <c r="K92" s="32"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="48"/>
+      <c r="K92" s="48"/>
       <c r="L92" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M92" s="23"/>
-    </row>
-    <row r="93" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="23"/>
-      <c r="B93" s="24" t="s">
+      <c r="M92" s="20"/>
+    </row>
+    <row r="93" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="20"/>
+      <c r="B93" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="32"/>
-      <c r="F93" s="32"/>
-      <c r="G93" s="32"/>
-      <c r="H93" s="32"/>
-      <c r="I93" s="32"/>
-      <c r="J93" s="32"/>
-      <c r="K93" s="32"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
+      <c r="H93" s="48"/>
+      <c r="I93" s="48"/>
+      <c r="J93" s="48"/>
+      <c r="K93" s="48"/>
       <c r="L93" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M93" s="23"/>
-    </row>
-    <row r="94" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="23"/>
-      <c r="B94" s="24" t="s">
+      <c r="M93" s="20"/>
+    </row>
+    <row r="94" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="20"/>
+      <c r="B94" s="21" t="s">
         <v>149</v>
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="32"/>
-      <c r="F94" s="32"/>
-      <c r="G94" s="32"/>
-      <c r="H94" s="32"/>
-      <c r="I94" s="32"/>
-      <c r="J94" s="32"/>
-      <c r="K94" s="32"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="48"/>
+      <c r="I94" s="48"/>
+      <c r="J94" s="48"/>
+      <c r="K94" s="48"/>
       <c r="L94" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M94" s="23"/>
-    </row>
-    <row r="95" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="23"/>
-      <c r="B95" s="24" t="s">
+      <c r="M94" s="20"/>
+    </row>
+    <row r="95" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="20"/>
+      <c r="B95" s="21" t="s">
         <v>150</v>
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="32"/>
-      <c r="F95" s="32"/>
-      <c r="G95" s="32"/>
-      <c r="H95" s="32"/>
-      <c r="I95" s="32"/>
-      <c r="J95" s="32"/>
-      <c r="K95" s="32"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="48"/>
+      <c r="I95" s="48"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="48"/>
       <c r="L95" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M95" s="23"/>
-    </row>
-    <row r="96" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="23"/>
-      <c r="B96" s="24" t="s">
+      <c r="M95" s="20"/>
+    </row>
+    <row r="96" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="20"/>
+      <c r="B96" s="21" t="s">
         <v>151</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="32"/>
-      <c r="F96" s="32"/>
-      <c r="G96" s="32"/>
-      <c r="H96" s="32"/>
-      <c r="I96" s="32"/>
-      <c r="J96" s="32"/>
-      <c r="K96" s="32"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="48"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="48"/>
+      <c r="K96" s="48"/>
       <c r="L96" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M96" s="23"/>
-    </row>
-    <row r="97" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="23"/>
-      <c r="B97" s="24" t="s">
+      <c r="M96" s="20"/>
+    </row>
+    <row r="97" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="20"/>
+      <c r="B97" s="21" t="s">
         <v>152</v>
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="32"/>
-      <c r="F97" s="32"/>
-      <c r="G97" s="32"/>
-      <c r="H97" s="32"/>
-      <c r="I97" s="32"/>
-      <c r="J97" s="32"/>
-      <c r="K97" s="32"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="48"/>
+      <c r="I97" s="48"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="48"/>
       <c r="L97" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M97" s="23"/>
-    </row>
-    <row r="98" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="23"/>
-      <c r="B98" s="24" t="s">
+      <c r="M97" s="20"/>
+    </row>
+    <row r="98" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="20"/>
+      <c r="B98" s="21" t="s">
         <v>153</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="32"/>
-      <c r="F98" s="32"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="32"/>
-      <c r="I98" s="32"/>
-      <c r="J98" s="32"/>
-      <c r="K98" s="32"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
       <c r="L98" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M98" s="23"/>
-    </row>
-    <row r="99" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="23"/>
-      <c r="B99" s="24" t="s">
+      <c r="M98" s="20"/>
+    </row>
+    <row r="99" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="20"/>
+      <c r="B99" s="21" t="s">
         <v>154</v>
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="32"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32"/>
-      <c r="H99" s="32"/>
-      <c r="I99" s="32"/>
-      <c r="J99" s="32"/>
-      <c r="K99" s="32"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="48"/>
       <c r="L99" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M99" s="23"/>
-    </row>
-    <row r="100" spans="1:13" s="20" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="23"/>
-      <c r="B100" s="24" t="s">
+      <c r="M99" s="20"/>
+    </row>
+    <row r="100" spans="1:13" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="20"/>
+      <c r="B100" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="32"/>
-      <c r="J100" s="32"/>
-      <c r="K100" s="32"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="48"/>
       <c r="L100" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="M100" s="23"/>
+      <c r="M100" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="197">
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E27:H27"/>
-    <mergeCell ref="E28:H28"/>
-    <mergeCell ref="E29:H29"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
+  <mergeCells count="195">
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -3883,60 +4067,144 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E5:H5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"검토 중"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"거부"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"승인"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3951,6 +4219,375 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2DE762C-FA58-405A-90C9-B76434EC7F3A}">
+  <dimension ref="A1:P28"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.75" customWidth="1"/>
+    <col min="2" max="2" width="5.625" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="4" max="5" width="33.625" customWidth="1"/>
+    <col min="6" max="10" width="11.625" customWidth="1"/>
+    <col min="11" max="11" width="9.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+    </row>
+    <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+    </row>
+    <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+    </row>
+    <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="8"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="8"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="8"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="2:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P2"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="F4:F9">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>"미완료"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+      <formula>"완료"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F9" xr:uid="{647DEC2F-6979-4A69-A4CB-B83067E147BB}">
+      <formula1>"완료, 미완료"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CC69D8A-576D-408F-8480-FC63A1DBEDF5}">
   <dimension ref="A1:P28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -3964,42 +4601,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
     </row>
     <row r="2" spans="1:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="38"/>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4319,7 +4956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7353F672-0C5B-433E-BDEF-D5FF0D1A8B1F}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -4335,32 +4972,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
     </row>
     <row r="2" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
     </row>
     <row r="3" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
@@ -4663,135 +5300,165 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{282F01E4-329A-4637-8D03-08736FA999D7}">
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.625" style="25" customWidth="1"/>
+    <col min="1" max="1" width="1.625" style="22" customWidth="1"/>
     <col min="2" max="4" width="30.625" customWidth="1"/>
     <col min="5" max="5" width="1.625" customWidth="1"/>
     <col min="6" max="8" width="9.625" customWidth="1"/>
     <col min="9" max="9" width="1.625" customWidth="1"/>
     <col min="13" max="13" width="1.625" customWidth="1"/>
     <col min="14" max="16" width="30.625" customWidth="1"/>
-    <col min="17" max="17" width="1.625" style="25" customWidth="1"/>
+    <col min="17" max="17" width="1.625" style="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:16" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="1" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="41" t="s">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="61" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="40" t="s">
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="39" t="e" vm="1">
+      <c r="B3" s="59" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="47" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="47" t="s">
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="39" t="e" vm="2">
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="59" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="39"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="47" t="s">
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="47" t="s">
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="44" t="s">
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="46"/>
-      <c r="M5" s="26"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-      <c r="P5" s="39"/>
-    </row>
-    <row r="6" spans="2:16" s="25" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="66"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+    </row>
+    <row r="6" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="B8" s="68" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+    </row>
+    <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="69" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="9" spans="2:16" ht="69" x14ac:dyDescent="0.3">
-      <c r="B9" s="29" t="s">
+      <c r="C9" s="69"/>
+      <c r="D9" s="65" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
+    </row>
+    <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="65" t="s">
         <v>176</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-    </row>
-    <row r="10" spans="2:16" ht="66" x14ac:dyDescent="0.3">
-      <c r="B10" s="28" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" ht="66" x14ac:dyDescent="0.3">
-      <c r="B11" s="28" t="s">
-        <v>178</v>
-      </c>
+      <c r="C10" s="65"/>
+      <c r="D10" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+    </row>
+    <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C11" s="65"/>
+      <c r="D11" s="70" t="s">
+        <v>189</v>
+      </c>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="18">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>

--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305F9200-A857-463B-BCAA-81F230598A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE079306-8DF1-4F45-A7D1-ABAC11630107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="205">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,6 +856,14 @@
   </si>
   <si>
     <t>2주차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱크대에서 물통에 물을 채운 뒤 열쇠를 가져갈 때 질문이 2번 나오는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱크대에서 열쇠를 가져갈 때 질문이 한번만 나오도록 수정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1247,57 +1255,69 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1316,23 +1336,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1877,36 +1885,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
@@ -1919,17 +1927,17 @@
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
       <c r="L3" s="5" t="s">
         <v>59</v>
       </c>
@@ -1948,17 +1956,17 @@
       <c r="D4" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
       <c r="L4" s="11" t="s">
         <v>172</v>
       </c>
@@ -1975,17 +1983,17 @@
       <c r="D5" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42" t="s">
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
       <c r="L5" s="11" t="s">
         <v>172</v>
       </c>
@@ -2002,17 +2010,17 @@
       <c r="D6" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42" t="s">
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
       <c r="L6" s="11" t="s">
         <v>172</v>
       </c>
@@ -2029,17 +2037,17 @@
       <c r="D7" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
       <c r="H7" s="30"/>
-      <c r="I7" s="42" t="s">
+      <c r="I7" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
       <c r="L7" s="11" t="s">
         <v>172</v>
       </c>
@@ -2056,17 +2064,17 @@
       <c r="D8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
       <c r="L8" s="11" t="s">
         <v>172</v>
       </c>
@@ -2083,17 +2091,17 @@
       <c r="D9" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
       <c r="H9" s="30"/>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
       <c r="L9" s="11" t="s">
         <v>172</v>
       </c>
@@ -2110,17 +2118,17 @@
       <c r="D10" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
       <c r="H10" s="30"/>
-      <c r="I10" s="42" t="s">
+      <c r="I10" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
       <c r="L10" s="11" t="s">
         <v>172</v>
       </c>
@@ -2137,17 +2145,17 @@
       <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42" t="s">
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
       <c r="L11" s="11" t="s">
         <v>172</v>
       </c>
@@ -2164,17 +2172,17 @@
       <c r="D12" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42" t="s">
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
       <c r="L12" s="11" t="s">
         <v>62</v>
       </c>
@@ -2191,17 +2199,17 @@
       <c r="D13" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42" t="s">
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
       <c r="L13" s="11" t="s">
         <v>60</v>
       </c>
@@ -2218,17 +2226,17 @@
       <c r="D14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42" t="s">
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
       <c r="L14" s="11" t="s">
         <v>62</v>
       </c>
@@ -2245,17 +2253,17 @@
       <c r="D15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42" t="s">
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
       <c r="L15" s="11" t="s">
         <v>172</v>
       </c>
@@ -2272,17 +2280,17 @@
       <c r="D16" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
       <c r="L16" s="11" t="s">
         <v>172</v>
       </c>
@@ -2299,17 +2307,17 @@
       <c r="D17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
       <c r="L17" s="11" t="s">
         <v>172</v>
       </c>
@@ -2326,17 +2334,17 @@
       <c r="D18" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42" t="s">
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
       <c r="L18" s="11" t="s">
         <v>172</v>
       </c>
@@ -2353,17 +2361,17 @@
       <c r="D19" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="45" t="s">
+      <c r="E19" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45" t="s">
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
       <c r="L19" s="11" t="s">
         <v>60</v>
       </c>
@@ -2380,17 +2388,17 @@
       <c r="D20" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45" t="s">
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
       <c r="L20" s="11" t="s">
         <v>60</v>
       </c>
@@ -2407,17 +2415,17 @@
       <c r="D21" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45" t="s">
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
       <c r="L21" s="11" t="s">
         <v>172</v>
       </c>
@@ -2434,17 +2442,17 @@
       <c r="D22" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45" t="s">
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
       <c r="L22" s="11" t="s">
         <v>172</v>
       </c>
@@ -2461,17 +2469,17 @@
       <c r="D23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="46" t="s">
+      <c r="E23" s="52" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="45" t="s">
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
       <c r="L23" s="11" t="s">
         <v>60</v>
       </c>
@@ -2488,17 +2496,17 @@
       <c r="D24" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="45" t="s">
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
       <c r="L24" s="11" t="s">
         <v>60</v>
       </c>
@@ -2515,17 +2523,17 @@
       <c r="D25" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="45" t="s">
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
       <c r="L25" s="11" t="s">
         <v>60</v>
       </c>
@@ -2542,17 +2550,17 @@
       <c r="D26" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="47" t="s">
+      <c r="E26" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47" t="s">
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53" t="s">
         <v>187</v>
       </c>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
       <c r="L26" s="11" t="s">
         <v>60</v>
       </c>
@@ -2575,17 +2583,17 @@
       <c r="D27" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="F27" s="51"/>
-      <c r="G27" s="52"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="50"/>
       <c r="H27" s="38"/>
-      <c r="I27" s="54" t="s">
+      <c r="I27" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="J27" s="55"/>
-      <c r="K27" s="56"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
       <c r="L27" s="11" t="s">
         <v>60</v>
       </c>
@@ -2608,11 +2616,11 @@
       <c r="F28" s="39"/>
       <c r="G28" s="39"/>
       <c r="H28" s="39"/>
-      <c r="I28" s="39" t="s">
+      <c r="I28" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="45"/>
       <c r="L28" s="11" t="s">
         <v>60</v>
       </c>
@@ -2629,17 +2637,17 @@
       <c r="D29" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E29" s="50" t="s">
+      <c r="E29" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="F29" s="51"/>
-      <c r="G29" s="52"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="50"/>
       <c r="H29" s="38"/>
-      <c r="I29" s="54" t="s">
+      <c r="I29" s="43" t="s">
         <v>199</v>
       </c>
-      <c r="J29" s="55"/>
-      <c r="K29" s="56"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="45"/>
       <c r="L29" s="11" t="s">
         <v>60</v>
       </c>
@@ -2651,18 +2659,22 @@
         <v>85</v>
       </c>
       <c r="C30" s="36">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="D30" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
+      <c r="E30" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="46" t="s">
+        <v>204</v>
+      </c>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
       <c r="L30" s="11" t="s">
         <v>60</v>
       </c>
@@ -2675,13 +2687,13 @@
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
       <c r="L31" s="11" t="s">
         <v>60</v>
       </c>
@@ -2694,13 +2706,13 @@
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
       <c r="L32" s="11" t="s">
         <v>60</v>
       </c>
@@ -2713,13 +2725,13 @@
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
       <c r="L33" s="11" t="s">
         <v>60</v>
       </c>
@@ -2732,13 +2744,13 @@
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
       <c r="L34" s="11" t="s">
         <v>60</v>
       </c>
@@ -2751,13 +2763,13 @@
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
       <c r="L35" s="11" t="s">
         <v>60</v>
       </c>
@@ -2770,13 +2782,13 @@
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
       <c r="L36" s="11" t="s">
         <v>60</v>
       </c>
@@ -2789,13 +2801,13 @@
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
       <c r="L37" s="11" t="s">
         <v>60</v>
       </c>
@@ -2808,13 +2820,13 @@
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
       <c r="L38" s="11" t="s">
         <v>60</v>
       </c>
@@ -2827,13 +2839,13 @@
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42"/>
       <c r="L39" s="11" t="s">
         <v>60</v>
       </c>
@@ -2846,13 +2858,13 @@
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
       <c r="L40" s="11" t="s">
         <v>60</v>
       </c>
@@ -2865,13 +2877,13 @@
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
       <c r="L41" s="11" t="s">
         <v>60</v>
       </c>
@@ -2884,13 +2896,13 @@
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
       <c r="L42" s="11" t="s">
         <v>60</v>
       </c>
@@ -2903,13 +2915,13 @@
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
       <c r="L43" s="11" t="s">
         <v>60</v>
       </c>
@@ -2922,13 +2934,13 @@
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
       <c r="L44" s="11" t="s">
         <v>60</v>
       </c>
@@ -2941,13 +2953,13 @@
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
       <c r="L45" s="11" t="s">
         <v>60</v>
       </c>
@@ -2960,13 +2972,13 @@
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
       <c r="L46" s="11" t="s">
         <v>60</v>
       </c>
@@ -2979,13 +2991,13 @@
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
       <c r="L47" s="11" t="s">
         <v>60</v>
       </c>
@@ -2998,13 +3010,13 @@
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
       <c r="L48" s="11" t="s">
         <v>60</v>
       </c>
@@ -3017,13 +3029,13 @@
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
       <c r="L49" s="11" t="s">
         <v>60</v>
       </c>
@@ -3036,13 +3048,13 @@
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="48"/>
-      <c r="K50" s="48"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
       <c r="L50" s="11" t="s">
         <v>60</v>
       </c>
@@ -3055,13 +3067,13 @@
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
       <c r="L51" s="11" t="s">
         <v>60</v>
       </c>
@@ -3074,13 +3086,13 @@
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="48"/>
-      <c r="K52" s="48"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
       <c r="L52" s="11" t="s">
         <v>60</v>
       </c>
@@ -3093,13 +3105,13 @@
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
       <c r="L53" s="11" t="s">
         <v>60</v>
       </c>
@@ -3112,13 +3124,13 @@
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="J54" s="48"/>
-      <c r="K54" s="48"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
       <c r="L54" s="11" t="s">
         <v>60</v>
       </c>
@@ -3131,13 +3143,13 @@
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="48"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
       <c r="L55" s="11" t="s">
         <v>60</v>
       </c>
@@ -3150,13 +3162,13 @@
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="48"/>
-      <c r="J56" s="48"/>
-      <c r="K56" s="48"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="42"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
       <c r="L56" s="11" t="s">
         <v>60</v>
       </c>
@@ -3169,13 +3181,13 @@
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48"/>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="42"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="42"/>
+      <c r="K57" s="42"/>
       <c r="L57" s="11" t="s">
         <v>60</v>
       </c>
@@ -3188,13 +3200,13 @@
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="42"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="42"/>
+      <c r="K58" s="42"/>
       <c r="L58" s="11" t="s">
         <v>60</v>
       </c>
@@ -3207,13 +3219,13 @@
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="42"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
       <c r="L59" s="11" t="s">
         <v>60</v>
       </c>
@@ -3226,13 +3238,13 @@
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
       <c r="L60" s="11" t="s">
         <v>60</v>
       </c>
@@ -3245,13 +3257,13 @@
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48"/>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="42"/>
+      <c r="H61" s="42"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
       <c r="L61" s="11" t="s">
         <v>60</v>
       </c>
@@ -3264,13 +3276,13 @@
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="42"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
       <c r="L62" s="11" t="s">
         <v>60</v>
       </c>
@@ -3283,13 +3295,13 @@
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
       <c r="L63" s="11" t="s">
         <v>60</v>
       </c>
@@ -3302,13 +3314,13 @@
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48"/>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
       <c r="L64" s="11" t="s">
         <v>60</v>
       </c>
@@ -3321,13 +3333,13 @@
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48"/>
-      <c r="J65" s="48"/>
-      <c r="K65" s="48"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="42"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
       <c r="L65" s="11" t="s">
         <v>60</v>
       </c>
@@ -3340,13 +3352,13 @@
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
       <c r="L66" s="11" t="s">
         <v>60</v>
       </c>
@@ -3359,13 +3371,13 @@
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="53"/>
-      <c r="F67" s="53"/>
-      <c r="G67" s="53"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="48"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
       <c r="L67" s="11" t="s">
         <v>60</v>
       </c>
@@ -3378,13 +3390,13 @@
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
-      <c r="I68" s="48"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="48"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
       <c r="L68" s="11" t="s">
         <v>60</v>
       </c>
@@ -3397,13 +3409,13 @@
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48"/>
-      <c r="J69" s="48"/>
-      <c r="K69" s="48"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
       <c r="L69" s="11" t="s">
         <v>60</v>
       </c>
@@ -3416,13 +3428,13 @@
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="48"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
       <c r="L70" s="11" t="s">
         <v>60</v>
       </c>
@@ -3435,13 +3447,13 @@
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="48"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="42"/>
+      <c r="I71" s="42"/>
+      <c r="J71" s="42"/>
+      <c r="K71" s="42"/>
       <c r="L71" s="11" t="s">
         <v>60</v>
       </c>
@@ -3454,13 +3466,13 @@
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
-      <c r="J72" s="48"/>
-      <c r="K72" s="48"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="42"/>
+      <c r="K72" s="42"/>
       <c r="L72" s="11" t="s">
         <v>60</v>
       </c>
@@ -3473,13 +3485,13 @@
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
-      <c r="H73" s="48"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="48"/>
-      <c r="K73" s="48"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="42"/>
+      <c r="I73" s="42"/>
+      <c r="J73" s="42"/>
+      <c r="K73" s="42"/>
       <c r="L73" s="11" t="s">
         <v>60</v>
       </c>
@@ -3492,13 +3504,13 @@
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
-      <c r="J74" s="48"/>
-      <c r="K74" s="48"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="42"/>
+      <c r="I74" s="42"/>
+      <c r="J74" s="42"/>
+      <c r="K74" s="42"/>
       <c r="L74" s="11" t="s">
         <v>60</v>
       </c>
@@ -3511,13 +3523,13 @@
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="42"/>
+      <c r="H75" s="42"/>
+      <c r="I75" s="42"/>
+      <c r="J75" s="42"/>
+      <c r="K75" s="42"/>
       <c r="L75" s="11" t="s">
         <v>60</v>
       </c>
@@ -3530,13 +3542,13 @@
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
-      <c r="J76" s="48"/>
-      <c r="K76" s="48"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="42"/>
+      <c r="I76" s="42"/>
+      <c r="J76" s="42"/>
+      <c r="K76" s="42"/>
       <c r="L76" s="11" t="s">
         <v>60</v>
       </c>
@@ -3549,13 +3561,13 @@
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="48"/>
-      <c r="H77" s="48"/>
-      <c r="I77" s="48"/>
-      <c r="J77" s="48"/>
-      <c r="K77" s="48"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="42"/>
+      <c r="H77" s="42"/>
+      <c r="I77" s="42"/>
+      <c r="J77" s="42"/>
+      <c r="K77" s="42"/>
       <c r="L77" s="11" t="s">
         <v>60</v>
       </c>
@@ -3568,13 +3580,13 @@
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
+      <c r="E78" s="42"/>
+      <c r="F78" s="42"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="42"/>
+      <c r="I78" s="42"/>
+      <c r="J78" s="42"/>
+      <c r="K78" s="42"/>
       <c r="L78" s="11" t="s">
         <v>60</v>
       </c>
@@ -3587,13 +3599,13 @@
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="48"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="42"/>
+      <c r="I79" s="42"/>
+      <c r="J79" s="42"/>
+      <c r="K79" s="42"/>
       <c r="L79" s="11" t="s">
         <v>60</v>
       </c>
@@ -3606,13 +3618,13 @@
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
-      <c r="J80" s="48"/>
-      <c r="K80" s="48"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="42"/>
+      <c r="K80" s="42"/>
       <c r="L80" s="11" t="s">
         <v>60</v>
       </c>
@@ -3625,13 +3637,13 @@
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48"/>
-      <c r="J81" s="48"/>
-      <c r="K81" s="48"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="42"/>
+      <c r="I81" s="42"/>
+      <c r="J81" s="42"/>
+      <c r="K81" s="42"/>
       <c r="L81" s="11" t="s">
         <v>60</v>
       </c>
@@ -3644,13 +3656,13 @@
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48"/>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="42"/>
+      <c r="I82" s="42"/>
+      <c r="J82" s="42"/>
+      <c r="K82" s="42"/>
       <c r="L82" s="11" t="s">
         <v>60</v>
       </c>
@@ -3663,13 +3675,13 @@
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48"/>
-      <c r="J83" s="48"/>
-      <c r="K83" s="48"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="42"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="42"/>
+      <c r="I83" s="42"/>
+      <c r="J83" s="42"/>
+      <c r="K83" s="42"/>
       <c r="L83" s="11" t="s">
         <v>60</v>
       </c>
@@ -3682,13 +3694,13 @@
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48"/>
-      <c r="J84" s="48"/>
-      <c r="K84" s="48"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="42"/>
+      <c r="H84" s="42"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="42"/>
+      <c r="K84" s="42"/>
       <c r="L84" s="11" t="s">
         <v>60</v>
       </c>
@@ -3701,13 +3713,13 @@
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48"/>
-      <c r="J85" s="48"/>
-      <c r="K85" s="48"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="42"/>
+      <c r="J85" s="42"/>
+      <c r="K85" s="42"/>
       <c r="L85" s="11" t="s">
         <v>60</v>
       </c>
@@ -3720,13 +3732,13 @@
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
-      <c r="J86" s="48"/>
-      <c r="K86" s="48"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="42"/>
+      <c r="K86" s="42"/>
       <c r="L86" s="11" t="s">
         <v>60</v>
       </c>
@@ -3739,13 +3751,13 @@
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="42"/>
+      <c r="G87" s="42"/>
+      <c r="H87" s="42"/>
+      <c r="I87" s="42"/>
+      <c r="J87" s="42"/>
+      <c r="K87" s="42"/>
       <c r="L87" s="11" t="s">
         <v>60</v>
       </c>
@@ -3758,13 +3770,13 @@
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
-      <c r="J88" s="48"/>
-      <c r="K88" s="48"/>
+      <c r="E88" s="42"/>
+      <c r="F88" s="42"/>
+      <c r="G88" s="42"/>
+      <c r="H88" s="42"/>
+      <c r="I88" s="42"/>
+      <c r="J88" s="42"/>
+      <c r="K88" s="42"/>
       <c r="L88" s="11" t="s">
         <v>60</v>
       </c>
@@ -3777,13 +3789,13 @@
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="48"/>
-      <c r="F89" s="48"/>
-      <c r="G89" s="48"/>
-      <c r="H89" s="48"/>
-      <c r="I89" s="48"/>
-      <c r="J89" s="48"/>
-      <c r="K89" s="48"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="42"/>
+      <c r="H89" s="42"/>
+      <c r="I89" s="42"/>
+      <c r="J89" s="42"/>
+      <c r="K89" s="42"/>
       <c r="L89" s="11" t="s">
         <v>60</v>
       </c>
@@ -3796,13 +3808,13 @@
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="48"/>
-      <c r="F90" s="48"/>
-      <c r="G90" s="48"/>
-      <c r="H90" s="48"/>
-      <c r="I90" s="48"/>
-      <c r="J90" s="48"/>
-      <c r="K90" s="48"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="42"/>
+      <c r="H90" s="42"/>
+      <c r="I90" s="42"/>
+      <c r="J90" s="42"/>
+      <c r="K90" s="42"/>
       <c r="L90" s="11" t="s">
         <v>60</v>
       </c>
@@ -3815,13 +3827,13 @@
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="48"/>
-      <c r="I91" s="48"/>
-      <c r="J91" s="48"/>
-      <c r="K91" s="48"/>
+      <c r="E91" s="42"/>
+      <c r="F91" s="42"/>
+      <c r="G91" s="42"/>
+      <c r="H91" s="42"/>
+      <c r="I91" s="42"/>
+      <c r="J91" s="42"/>
+      <c r="K91" s="42"/>
       <c r="L91" s="11" t="s">
         <v>60</v>
       </c>
@@ -3834,13 +3846,13 @@
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="48"/>
-      <c r="J92" s="48"/>
-      <c r="K92" s="48"/>
+      <c r="E92" s="42"/>
+      <c r="F92" s="42"/>
+      <c r="G92" s="42"/>
+      <c r="H92" s="42"/>
+      <c r="I92" s="42"/>
+      <c r="J92" s="42"/>
+      <c r="K92" s="42"/>
       <c r="L92" s="11" t="s">
         <v>60</v>
       </c>
@@ -3853,13 +3865,13 @@
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="48"/>
-      <c r="H93" s="48"/>
-      <c r="I93" s="48"/>
-      <c r="J93" s="48"/>
-      <c r="K93" s="48"/>
+      <c r="E93" s="42"/>
+      <c r="F93" s="42"/>
+      <c r="G93" s="42"/>
+      <c r="H93" s="42"/>
+      <c r="I93" s="42"/>
+      <c r="J93" s="42"/>
+      <c r="K93" s="42"/>
       <c r="L93" s="11" t="s">
         <v>60</v>
       </c>
@@ -3872,13 +3884,13 @@
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="48"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="48"/>
-      <c r="H94" s="48"/>
-      <c r="I94" s="48"/>
-      <c r="J94" s="48"/>
-      <c r="K94" s="48"/>
+      <c r="E94" s="42"/>
+      <c r="F94" s="42"/>
+      <c r="G94" s="42"/>
+      <c r="H94" s="42"/>
+      <c r="I94" s="42"/>
+      <c r="J94" s="42"/>
+      <c r="K94" s="42"/>
       <c r="L94" s="11" t="s">
         <v>60</v>
       </c>
@@ -3891,13 +3903,13 @@
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
-      <c r="H95" s="48"/>
-      <c r="I95" s="48"/>
-      <c r="J95" s="48"/>
-      <c r="K95" s="48"/>
+      <c r="E95" s="42"/>
+      <c r="F95" s="42"/>
+      <c r="G95" s="42"/>
+      <c r="H95" s="42"/>
+      <c r="I95" s="42"/>
+      <c r="J95" s="42"/>
+      <c r="K95" s="42"/>
       <c r="L95" s="11" t="s">
         <v>60</v>
       </c>
@@ -3910,13 +3922,13 @@
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="48"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="48"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="48"/>
-      <c r="J96" s="48"/>
-      <c r="K96" s="48"/>
+      <c r="E96" s="42"/>
+      <c r="F96" s="42"/>
+      <c r="G96" s="42"/>
+      <c r="H96" s="42"/>
+      <c r="I96" s="42"/>
+      <c r="J96" s="42"/>
+      <c r="K96" s="42"/>
       <c r="L96" s="11" t="s">
         <v>60</v>
       </c>
@@ -3929,13 +3941,13 @@
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="48"/>
-      <c r="J97" s="48"/>
-      <c r="K97" s="48"/>
+      <c r="E97" s="42"/>
+      <c r="F97" s="42"/>
+      <c r="G97" s="42"/>
+      <c r="H97" s="42"/>
+      <c r="I97" s="42"/>
+      <c r="J97" s="42"/>
+      <c r="K97" s="42"/>
       <c r="L97" s="11" t="s">
         <v>60</v>
       </c>
@@ -3948,13 +3960,13 @@
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
+      <c r="E98" s="42"/>
+      <c r="F98" s="42"/>
+      <c r="G98" s="42"/>
+      <c r="H98" s="42"/>
+      <c r="I98" s="42"/>
+      <c r="J98" s="42"/>
+      <c r="K98" s="42"/>
       <c r="L98" s="11" t="s">
         <v>60</v>
       </c>
@@ -3967,13 +3979,13 @@
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
-      <c r="J99" s="48"/>
-      <c r="K99" s="48"/>
+      <c r="E99" s="42"/>
+      <c r="F99" s="42"/>
+      <c r="G99" s="42"/>
+      <c r="H99" s="42"/>
+      <c r="I99" s="42"/>
+      <c r="J99" s="42"/>
+      <c r="K99" s="42"/>
       <c r="L99" s="11" t="s">
         <v>60</v>
       </c>
@@ -3986,63 +3998,148 @@
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
-      <c r="J100" s="48"/>
-      <c r="K100" s="48"/>
+      <c r="E100" s="42"/>
+      <c r="F100" s="42"/>
+      <c r="G100" s="42"/>
+      <c r="H100" s="42"/>
+      <c r="I100" s="42"/>
+      <c r="J100" s="42"/>
+      <c r="K100" s="42"/>
       <c r="L100" s="11" t="s">
         <v>60</v>
       </c>
       <c r="M100" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="195">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
+  <mergeCells count="196">
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -4067,134 +4164,50 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -5317,148 +5330,140 @@
   <sheetData>
     <row r="1" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
       <c r="E2" s="24"/>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="65" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="63"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="67"/>
       <c r="M2" s="24"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="59" t="e" vm="1">
+      <c r="B3" s="63" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
       <c r="E3" s="23"/>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="23"/>
-      <c r="J3" s="67" t="s">
+      <c r="J3" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="59" t="e" vm="2">
+      <c r="N3" s="63" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="67" t="s">
+      <c r="J4" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="66"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="69"/>
       <c r="M5" s="23"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
     </row>
     <row r="6" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="59" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="65" t="s">
+      <c r="C9" s="60"/>
+      <c r="D9" s="61" t="s">
         <v>184</v>
       </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="61" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65" t="s">
+      <c r="C10" s="61"/>
+      <c r="D10" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="70" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -5469,6 +5474,14 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305F9200-A857-463B-BCAA-81F230598A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8561979E-98D0-4753-A196-4D134FEC99B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView minimized="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
@@ -19,42 +19,31 @@
     <sheet name="버그" sheetId="4" r:id="rId4"/>
     <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -72,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="204">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -856,6 +845,10 @@
   </si>
   <si>
     <t>2주차</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기존 콜리전 방식에서 1초를 기다리는 방식으로 변경</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1247,57 +1240,69 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1316,23 +1321,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1877,36 +1870,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
@@ -1919,17 +1912,17 @@
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
       <c r="L3" s="5" t="s">
         <v>59</v>
       </c>
@@ -1948,17 +1941,17 @@
       <c r="D4" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
       <c r="L4" s="11" t="s">
         <v>172</v>
       </c>
@@ -1975,17 +1968,17 @@
       <c r="D5" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42" t="s">
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
       <c r="L5" s="11" t="s">
         <v>172</v>
       </c>
@@ -2002,17 +1995,17 @@
       <c r="D6" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42" t="s">
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
       <c r="L6" s="11" t="s">
         <v>172</v>
       </c>
@@ -2029,17 +2022,17 @@
       <c r="D7" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
       <c r="H7" s="30"/>
-      <c r="I7" s="42" t="s">
+      <c r="I7" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
       <c r="L7" s="11" t="s">
         <v>172</v>
       </c>
@@ -2056,17 +2049,17 @@
       <c r="D8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
       <c r="L8" s="11" t="s">
         <v>172</v>
       </c>
@@ -2083,17 +2076,17 @@
       <c r="D9" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
       <c r="H9" s="30"/>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
       <c r="L9" s="11" t="s">
         <v>172</v>
       </c>
@@ -2110,17 +2103,17 @@
       <c r="D10" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
       <c r="H10" s="30"/>
-      <c r="I10" s="42" t="s">
+      <c r="I10" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
       <c r="L10" s="11" t="s">
         <v>172</v>
       </c>
@@ -2137,17 +2130,17 @@
       <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42" t="s">
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
       <c r="L11" s="11" t="s">
         <v>172</v>
       </c>
@@ -2164,17 +2157,17 @@
       <c r="D12" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42" t="s">
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
       <c r="L12" s="11" t="s">
         <v>62</v>
       </c>
@@ -2191,17 +2184,17 @@
       <c r="D13" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42" t="s">
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
       <c r="L13" s="11" t="s">
         <v>60</v>
       </c>
@@ -2218,17 +2211,17 @@
       <c r="D14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42" t="s">
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
       <c r="L14" s="11" t="s">
         <v>62</v>
       </c>
@@ -2245,17 +2238,17 @@
       <c r="D15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42" t="s">
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
       <c r="L15" s="11" t="s">
         <v>172</v>
       </c>
@@ -2272,17 +2265,17 @@
       <c r="D16" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
       <c r="L16" s="11" t="s">
         <v>172</v>
       </c>
@@ -2299,17 +2292,17 @@
       <c r="D17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
       <c r="L17" s="11" t="s">
         <v>172</v>
       </c>
@@ -2326,17 +2319,17 @@
       <c r="D18" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42" t="s">
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
       <c r="L18" s="11" t="s">
         <v>172</v>
       </c>
@@ -2353,17 +2346,17 @@
       <c r="D19" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="45" t="s">
+      <c r="E19" s="51" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45" t="s">
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
       <c r="L19" s="11" t="s">
         <v>60</v>
       </c>
@@ -2380,17 +2373,17 @@
       <c r="D20" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45" t="s">
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
+      <c r="I20" s="51" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
+      <c r="J20" s="51"/>
+      <c r="K20" s="51"/>
       <c r="L20" s="11" t="s">
         <v>60</v>
       </c>
@@ -2407,17 +2400,17 @@
       <c r="D21" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45" t="s">
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
       <c r="L21" s="11" t="s">
         <v>172</v>
       </c>
@@ -2434,17 +2427,17 @@
       <c r="D22" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45" t="s">
+      <c r="F22" s="51"/>
+      <c r="G22" s="51"/>
+      <c r="H22" s="51"/>
+      <c r="I22" s="51" t="s">
         <v>174</v>
       </c>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="51"/>
       <c r="L22" s="11" t="s">
         <v>172</v>
       </c>
@@ -2461,17 +2454,17 @@
       <c r="D23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="46" t="s">
+      <c r="E23" s="52" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="45" t="s">
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="51" t="s">
         <v>178</v>
       </c>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
+      <c r="J23" s="51"/>
+      <c r="K23" s="51"/>
       <c r="L23" s="11" t="s">
         <v>60</v>
       </c>
@@ -2488,17 +2481,17 @@
       <c r="D24" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="52" t="s">
         <v>179</v>
       </c>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="45" t="s">
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="51" t="s">
         <v>180</v>
       </c>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
+      <c r="J24" s="51"/>
+      <c r="K24" s="51"/>
       <c r="L24" s="11" t="s">
         <v>60</v>
       </c>
@@ -2515,17 +2508,17 @@
       <c r="D25" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="45" t="s">
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="51" t="s">
         <v>182</v>
       </c>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
+      <c r="J25" s="51"/>
+      <c r="K25" s="51"/>
       <c r="L25" s="11" t="s">
         <v>60</v>
       </c>
@@ -2542,21 +2535,23 @@
       <c r="D26" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="47" t="s">
+      <c r="E26" s="53" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47" t="s">
+      <c r="F26" s="53"/>
+      <c r="G26" s="53"/>
+      <c r="H26" s="53"/>
+      <c r="I26" s="53" t="s">
         <v>187</v>
       </c>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
+      <c r="J26" s="53"/>
+      <c r="K26" s="53"/>
       <c r="L26" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M26" s="20"/>
+        <v>172</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>203</v>
+      </c>
       <c r="P26" s="40" t="s">
         <v>201</v>
       </c>
@@ -2575,17 +2570,17 @@
       <c r="D27" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="F27" s="51"/>
-      <c r="G27" s="52"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="50"/>
       <c r="H27" s="38"/>
-      <c r="I27" s="54" t="s">
+      <c r="I27" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="J27" s="55"/>
-      <c r="K27" s="56"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
       <c r="L27" s="11" t="s">
         <v>60</v>
       </c>
@@ -2629,17 +2624,17 @@
       <c r="D29" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E29" s="50" t="s">
+      <c r="E29" s="48" t="s">
         <v>198</v>
       </c>
-      <c r="F29" s="51"/>
-      <c r="G29" s="52"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="50"/>
       <c r="H29" s="38"/>
-      <c r="I29" s="54" t="s">
+      <c r="I29" s="43" t="s">
         <v>199</v>
       </c>
-      <c r="J29" s="55"/>
-      <c r="K29" s="56"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="45"/>
       <c r="L29" s="11" t="s">
         <v>60</v>
       </c>
@@ -2656,13 +2651,13 @@
       <c r="D30" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E30" s="49"/>
-      <c r="F30" s="49"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="49"/>
-      <c r="J30" s="49"/>
-      <c r="K30" s="49"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
       <c r="L30" s="11" t="s">
         <v>60</v>
       </c>
@@ -2675,13 +2670,13 @@
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
       <c r="L31" s="11" t="s">
         <v>60</v>
       </c>
@@ -2694,13 +2689,13 @@
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
       <c r="L32" s="11" t="s">
         <v>60</v>
       </c>
@@ -2713,13 +2708,13 @@
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
       <c r="L33" s="11" t="s">
         <v>60</v>
       </c>
@@ -2732,13 +2727,13 @@
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
       <c r="L34" s="11" t="s">
         <v>60</v>
       </c>
@@ -2751,13 +2746,13 @@
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
       <c r="L35" s="11" t="s">
         <v>60</v>
       </c>
@@ -2770,13 +2765,13 @@
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
       <c r="L36" s="11" t="s">
         <v>60</v>
       </c>
@@ -2789,13 +2784,13 @@
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
       <c r="L37" s="11" t="s">
         <v>60</v>
       </c>
@@ -2808,13 +2803,13 @@
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
       <c r="L38" s="11" t="s">
         <v>60</v>
       </c>
@@ -2827,13 +2822,13 @@
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42"/>
       <c r="L39" s="11" t="s">
         <v>60</v>
       </c>
@@ -2846,13 +2841,13 @@
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
       <c r="L40" s="11" t="s">
         <v>60</v>
       </c>
@@ -2865,13 +2860,13 @@
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
       <c r="L41" s="11" t="s">
         <v>60</v>
       </c>
@@ -2884,13 +2879,13 @@
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
       <c r="L42" s="11" t="s">
         <v>60</v>
       </c>
@@ -2903,13 +2898,13 @@
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
       <c r="L43" s="11" t="s">
         <v>60</v>
       </c>
@@ -2922,13 +2917,13 @@
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
       <c r="L44" s="11" t="s">
         <v>60</v>
       </c>
@@ -2941,13 +2936,13 @@
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
       <c r="L45" s="11" t="s">
         <v>60</v>
       </c>
@@ -2960,13 +2955,13 @@
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
       <c r="L46" s="11" t="s">
         <v>60</v>
       </c>
@@ -2979,13 +2974,13 @@
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
       <c r="L47" s="11" t="s">
         <v>60</v>
       </c>
@@ -2998,13 +2993,13 @@
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
       <c r="L48" s="11" t="s">
         <v>60</v>
       </c>
@@ -3017,13 +3012,13 @@
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
       <c r="L49" s="11" t="s">
         <v>60</v>
       </c>
@@ -3036,13 +3031,13 @@
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="48"/>
-      <c r="K50" s="48"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
       <c r="L50" s="11" t="s">
         <v>60</v>
       </c>
@@ -3055,13 +3050,13 @@
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
       <c r="L51" s="11" t="s">
         <v>60</v>
       </c>
@@ -3074,13 +3069,13 @@
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="48"/>
-      <c r="K52" s="48"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
       <c r="L52" s="11" t="s">
         <v>60</v>
       </c>
@@ -3093,13 +3088,13 @@
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
       <c r="L53" s="11" t="s">
         <v>60</v>
       </c>
@@ -3112,13 +3107,13 @@
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="J54" s="48"/>
-      <c r="K54" s="48"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
       <c r="L54" s="11" t="s">
         <v>60</v>
       </c>
@@ -3131,13 +3126,13 @@
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="48"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
       <c r="L55" s="11" t="s">
         <v>60</v>
       </c>
@@ -3150,13 +3145,13 @@
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="48"/>
-      <c r="J56" s="48"/>
-      <c r="K56" s="48"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="42"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
       <c r="L56" s="11" t="s">
         <v>60</v>
       </c>
@@ -3169,13 +3164,13 @@
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48"/>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="42"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="42"/>
+      <c r="K57" s="42"/>
       <c r="L57" s="11" t="s">
         <v>60</v>
       </c>
@@ -3188,13 +3183,13 @@
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="42"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="42"/>
+      <c r="K58" s="42"/>
       <c r="L58" s="11" t="s">
         <v>60</v>
       </c>
@@ -3207,13 +3202,13 @@
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="42"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
       <c r="L59" s="11" t="s">
         <v>60</v>
       </c>
@@ -3226,13 +3221,13 @@
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
       <c r="L60" s="11" t="s">
         <v>60</v>
       </c>
@@ -3245,13 +3240,13 @@
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48"/>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="42"/>
+      <c r="H61" s="42"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
       <c r="L61" s="11" t="s">
         <v>60</v>
       </c>
@@ -3264,13 +3259,13 @@
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="42"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
       <c r="L62" s="11" t="s">
         <v>60</v>
       </c>
@@ -3283,13 +3278,13 @@
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
       <c r="L63" s="11" t="s">
         <v>60</v>
       </c>
@@ -3302,13 +3297,13 @@
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48"/>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
       <c r="L64" s="11" t="s">
         <v>60</v>
       </c>
@@ -3321,13 +3316,13 @@
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48"/>
-      <c r="J65" s="48"/>
-      <c r="K65" s="48"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="42"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
       <c r="L65" s="11" t="s">
         <v>60</v>
       </c>
@@ -3340,13 +3335,13 @@
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
       <c r="L66" s="11" t="s">
         <v>60</v>
       </c>
@@ -3359,13 +3354,13 @@
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="53"/>
-      <c r="F67" s="53"/>
-      <c r="G67" s="53"/>
-      <c r="H67" s="53"/>
-      <c r="I67" s="48"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
       <c r="L67" s="11" t="s">
         <v>60</v>
       </c>
@@ -3378,13 +3373,13 @@
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
-      <c r="I68" s="48"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="48"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
       <c r="L68" s="11" t="s">
         <v>60</v>
       </c>
@@ -3397,13 +3392,13 @@
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48"/>
-      <c r="J69" s="48"/>
-      <c r="K69" s="48"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
       <c r="L69" s="11" t="s">
         <v>60</v>
       </c>
@@ -3416,13 +3411,13 @@
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="48"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
       <c r="L70" s="11" t="s">
         <v>60</v>
       </c>
@@ -3435,13 +3430,13 @@
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="48"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="42"/>
+      <c r="I71" s="42"/>
+      <c r="J71" s="42"/>
+      <c r="K71" s="42"/>
       <c r="L71" s="11" t="s">
         <v>60</v>
       </c>
@@ -3454,13 +3449,13 @@
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
-      <c r="J72" s="48"/>
-      <c r="K72" s="48"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="42"/>
+      <c r="K72" s="42"/>
       <c r="L72" s="11" t="s">
         <v>60</v>
       </c>
@@ -3473,13 +3468,13 @@
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
-      <c r="H73" s="48"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="48"/>
-      <c r="K73" s="48"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="42"/>
+      <c r="I73" s="42"/>
+      <c r="J73" s="42"/>
+      <c r="K73" s="42"/>
       <c r="L73" s="11" t="s">
         <v>60</v>
       </c>
@@ -3492,13 +3487,13 @@
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
-      <c r="J74" s="48"/>
-      <c r="K74" s="48"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="42"/>
+      <c r="I74" s="42"/>
+      <c r="J74" s="42"/>
+      <c r="K74" s="42"/>
       <c r="L74" s="11" t="s">
         <v>60</v>
       </c>
@@ -3511,13 +3506,13 @@
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="42"/>
+      <c r="H75" s="42"/>
+      <c r="I75" s="42"/>
+      <c r="J75" s="42"/>
+      <c r="K75" s="42"/>
       <c r="L75" s="11" t="s">
         <v>60</v>
       </c>
@@ -3530,13 +3525,13 @@
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
-      <c r="J76" s="48"/>
-      <c r="K76" s="48"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="42"/>
+      <c r="I76" s="42"/>
+      <c r="J76" s="42"/>
+      <c r="K76" s="42"/>
       <c r="L76" s="11" t="s">
         <v>60</v>
       </c>
@@ -3549,13 +3544,13 @@
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="48"/>
-      <c r="H77" s="48"/>
-      <c r="I77" s="48"/>
-      <c r="J77" s="48"/>
-      <c r="K77" s="48"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="42"/>
+      <c r="H77" s="42"/>
+      <c r="I77" s="42"/>
+      <c r="J77" s="42"/>
+      <c r="K77" s="42"/>
       <c r="L77" s="11" t="s">
         <v>60</v>
       </c>
@@ -3568,13 +3563,13 @@
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
+      <c r="E78" s="42"/>
+      <c r="F78" s="42"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="42"/>
+      <c r="I78" s="42"/>
+      <c r="J78" s="42"/>
+      <c r="K78" s="42"/>
       <c r="L78" s="11" t="s">
         <v>60</v>
       </c>
@@ -3587,13 +3582,13 @@
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="48"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="42"/>
+      <c r="I79" s="42"/>
+      <c r="J79" s="42"/>
+      <c r="K79" s="42"/>
       <c r="L79" s="11" t="s">
         <v>60</v>
       </c>
@@ -3606,13 +3601,13 @@
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
-      <c r="J80" s="48"/>
-      <c r="K80" s="48"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="42"/>
+      <c r="K80" s="42"/>
       <c r="L80" s="11" t="s">
         <v>60</v>
       </c>
@@ -3625,13 +3620,13 @@
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48"/>
-      <c r="J81" s="48"/>
-      <c r="K81" s="48"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="42"/>
+      <c r="I81" s="42"/>
+      <c r="J81" s="42"/>
+      <c r="K81" s="42"/>
       <c r="L81" s="11" t="s">
         <v>60</v>
       </c>
@@ -3644,13 +3639,13 @@
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48"/>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="42"/>
+      <c r="I82" s="42"/>
+      <c r="J82" s="42"/>
+      <c r="K82" s="42"/>
       <c r="L82" s="11" t="s">
         <v>60</v>
       </c>
@@ -3663,13 +3658,13 @@
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48"/>
-      <c r="J83" s="48"/>
-      <c r="K83" s="48"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="42"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="42"/>
+      <c r="I83" s="42"/>
+      <c r="J83" s="42"/>
+      <c r="K83" s="42"/>
       <c r="L83" s="11" t="s">
         <v>60</v>
       </c>
@@ -3682,13 +3677,13 @@
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48"/>
-      <c r="J84" s="48"/>
-      <c r="K84" s="48"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="42"/>
+      <c r="H84" s="42"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="42"/>
+      <c r="K84" s="42"/>
       <c r="L84" s="11" t="s">
         <v>60</v>
       </c>
@@ -3701,13 +3696,13 @@
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48"/>
-      <c r="J85" s="48"/>
-      <c r="K85" s="48"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="42"/>
+      <c r="J85" s="42"/>
+      <c r="K85" s="42"/>
       <c r="L85" s="11" t="s">
         <v>60</v>
       </c>
@@ -3720,13 +3715,13 @@
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
-      <c r="J86" s="48"/>
-      <c r="K86" s="48"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="42"/>
+      <c r="K86" s="42"/>
       <c r="L86" s="11" t="s">
         <v>60</v>
       </c>
@@ -3739,13 +3734,13 @@
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="42"/>
+      <c r="G87" s="42"/>
+      <c r="H87" s="42"/>
+      <c r="I87" s="42"/>
+      <c r="J87" s="42"/>
+      <c r="K87" s="42"/>
       <c r="L87" s="11" t="s">
         <v>60</v>
       </c>
@@ -3758,13 +3753,13 @@
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
-      <c r="J88" s="48"/>
-      <c r="K88" s="48"/>
+      <c r="E88" s="42"/>
+      <c r="F88" s="42"/>
+      <c r="G88" s="42"/>
+      <c r="H88" s="42"/>
+      <c r="I88" s="42"/>
+      <c r="J88" s="42"/>
+      <c r="K88" s="42"/>
       <c r="L88" s="11" t="s">
         <v>60</v>
       </c>
@@ -3777,13 +3772,13 @@
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="48"/>
-      <c r="F89" s="48"/>
-      <c r="G89" s="48"/>
-      <c r="H89" s="48"/>
-      <c r="I89" s="48"/>
-      <c r="J89" s="48"/>
-      <c r="K89" s="48"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="42"/>
+      <c r="H89" s="42"/>
+      <c r="I89" s="42"/>
+      <c r="J89" s="42"/>
+      <c r="K89" s="42"/>
       <c r="L89" s="11" t="s">
         <v>60</v>
       </c>
@@ -3796,13 +3791,13 @@
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="48"/>
-      <c r="F90" s="48"/>
-      <c r="G90" s="48"/>
-      <c r="H90" s="48"/>
-      <c r="I90" s="48"/>
-      <c r="J90" s="48"/>
-      <c r="K90" s="48"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="42"/>
+      <c r="H90" s="42"/>
+      <c r="I90" s="42"/>
+      <c r="J90" s="42"/>
+      <c r="K90" s="42"/>
       <c r="L90" s="11" t="s">
         <v>60</v>
       </c>
@@ -3815,13 +3810,13 @@
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="48"/>
-      <c r="I91" s="48"/>
-      <c r="J91" s="48"/>
-      <c r="K91" s="48"/>
+      <c r="E91" s="42"/>
+      <c r="F91" s="42"/>
+      <c r="G91" s="42"/>
+      <c r="H91" s="42"/>
+      <c r="I91" s="42"/>
+      <c r="J91" s="42"/>
+      <c r="K91" s="42"/>
       <c r="L91" s="11" t="s">
         <v>60</v>
       </c>
@@ -3834,13 +3829,13 @@
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="48"/>
-      <c r="J92" s="48"/>
-      <c r="K92" s="48"/>
+      <c r="E92" s="42"/>
+      <c r="F92" s="42"/>
+      <c r="G92" s="42"/>
+      <c r="H92" s="42"/>
+      <c r="I92" s="42"/>
+      <c r="J92" s="42"/>
+      <c r="K92" s="42"/>
       <c r="L92" s="11" t="s">
         <v>60</v>
       </c>
@@ -3853,13 +3848,13 @@
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="48"/>
-      <c r="H93" s="48"/>
-      <c r="I93" s="48"/>
-      <c r="J93" s="48"/>
-      <c r="K93" s="48"/>
+      <c r="E93" s="42"/>
+      <c r="F93" s="42"/>
+      <c r="G93" s="42"/>
+      <c r="H93" s="42"/>
+      <c r="I93" s="42"/>
+      <c r="J93" s="42"/>
+      <c r="K93" s="42"/>
       <c r="L93" s="11" t="s">
         <v>60</v>
       </c>
@@ -3872,13 +3867,13 @@
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="48"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="48"/>
-      <c r="H94" s="48"/>
-      <c r="I94" s="48"/>
-      <c r="J94" s="48"/>
-      <c r="K94" s="48"/>
+      <c r="E94" s="42"/>
+      <c r="F94" s="42"/>
+      <c r="G94" s="42"/>
+      <c r="H94" s="42"/>
+      <c r="I94" s="42"/>
+      <c r="J94" s="42"/>
+      <c r="K94" s="42"/>
       <c r="L94" s="11" t="s">
         <v>60</v>
       </c>
@@ -3891,13 +3886,13 @@
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
-      <c r="H95" s="48"/>
-      <c r="I95" s="48"/>
-      <c r="J95" s="48"/>
-      <c r="K95" s="48"/>
+      <c r="E95" s="42"/>
+      <c r="F95" s="42"/>
+      <c r="G95" s="42"/>
+      <c r="H95" s="42"/>
+      <c r="I95" s="42"/>
+      <c r="J95" s="42"/>
+      <c r="K95" s="42"/>
       <c r="L95" s="11" t="s">
         <v>60</v>
       </c>
@@ -3910,13 +3905,13 @@
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="48"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="48"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="48"/>
-      <c r="J96" s="48"/>
-      <c r="K96" s="48"/>
+      <c r="E96" s="42"/>
+      <c r="F96" s="42"/>
+      <c r="G96" s="42"/>
+      <c r="H96" s="42"/>
+      <c r="I96" s="42"/>
+      <c r="J96" s="42"/>
+      <c r="K96" s="42"/>
       <c r="L96" s="11" t="s">
         <v>60</v>
       </c>
@@ -3929,13 +3924,13 @@
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="48"/>
-      <c r="J97" s="48"/>
-      <c r="K97" s="48"/>
+      <c r="E97" s="42"/>
+      <c r="F97" s="42"/>
+      <c r="G97" s="42"/>
+      <c r="H97" s="42"/>
+      <c r="I97" s="42"/>
+      <c r="J97" s="42"/>
+      <c r="K97" s="42"/>
       <c r="L97" s="11" t="s">
         <v>60</v>
       </c>
@@ -3948,13 +3943,13 @@
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
+      <c r="E98" s="42"/>
+      <c r="F98" s="42"/>
+      <c r="G98" s="42"/>
+      <c r="H98" s="42"/>
+      <c r="I98" s="42"/>
+      <c r="J98" s="42"/>
+      <c r="K98" s="42"/>
       <c r="L98" s="11" t="s">
         <v>60</v>
       </c>
@@ -3967,13 +3962,13 @@
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
-      <c r="J99" s="48"/>
-      <c r="K99" s="48"/>
+      <c r="E99" s="42"/>
+      <c r="F99" s="42"/>
+      <c r="G99" s="42"/>
+      <c r="H99" s="42"/>
+      <c r="I99" s="42"/>
+      <c r="J99" s="42"/>
+      <c r="K99" s="42"/>
       <c r="L99" s="11" t="s">
         <v>60</v>
       </c>
@@ -3986,13 +3981,13 @@
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
-      <c r="J100" s="48"/>
-      <c r="K100" s="48"/>
+      <c r="E100" s="42"/>
+      <c r="F100" s="42"/>
+      <c r="G100" s="42"/>
+      <c r="H100" s="42"/>
+      <c r="I100" s="42"/>
+      <c r="J100" s="42"/>
+      <c r="K100" s="42"/>
       <c r="L100" s="11" t="s">
         <v>60</v>
       </c>
@@ -4000,49 +3995,134 @@
     </row>
   </sheetData>
   <mergeCells count="195">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -4067,134 +4147,49 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -5317,148 +5312,140 @@
   <sheetData>
     <row r="1" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
       <c r="E2" s="24"/>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="65" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="63"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="67"/>
       <c r="M2" s="24"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="59" t="e" vm="1">
+      <c r="B3" s="63" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
       <c r="E3" s="23"/>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="23"/>
-      <c r="J3" s="67" t="s">
+      <c r="J3" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="59" t="e" vm="2">
+      <c r="N3" s="63" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="67" t="s">
+      <c r="J4" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="66"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="69"/>
       <c r="M5" s="23"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
     </row>
     <row r="6" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="59" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="65" t="s">
+      <c r="C9" s="60"/>
+      <c r="D9" s="61" t="s">
         <v>184</v>
       </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="61" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65" t="s">
+      <c r="C10" s="61"/>
+      <c r="D10" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="70" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -5469,6 +5456,14 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8561979E-98D0-4753-A196-4D134FEC99B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE079306-8DF1-4F45-A7D1-ABAC11630107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
@@ -19,31 +19,42 @@
     <sheet name="버그" sheetId="4" r:id="rId4"/>
     <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -61,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="205">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -848,7 +859,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기존 콜리전 방식에서 1초를 기다리는 방식으로 변경</t>
+    <t>싱크대에서 물통에 물을 채운 뒤 열쇠를 가져갈 때 질문이 2번 나오는 현상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>싱크대에서 열쇠를 가져갈 때 질문이 한번만 나오도록 수정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2547,11 +2562,9 @@
       <c r="J26" s="53"/>
       <c r="K26" s="53"/>
       <c r="L26" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="M26" s="20" t="s">
-        <v>203</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="M26" s="20"/>
       <c r="P26" s="40" t="s">
         <v>201</v>
       </c>
@@ -2603,11 +2616,11 @@
       <c r="F28" s="39"/>
       <c r="G28" s="39"/>
       <c r="H28" s="39"/>
-      <c r="I28" s="39" t="s">
+      <c r="I28" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="J28" s="39"/>
-      <c r="K28" s="39"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="45"/>
       <c r="L28" s="11" t="s">
         <v>60</v>
       </c>
@@ -2646,16 +2659,20 @@
         <v>85</v>
       </c>
       <c r="C30" s="36">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="D30" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
+      <c r="E30" s="53" t="s">
+        <v>203</v>
+      </c>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="46" t="s">
+        <v>204</v>
+      </c>
       <c r="J30" s="46"/>
       <c r="K30" s="46"/>
       <c r="L30" s="11" t="s">
@@ -3994,7 +4011,7 @@
       <c r="M100" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="195">
+  <mergeCells count="196">
     <mergeCell ref="E18:H18"/>
     <mergeCell ref="I18:K18"/>
     <mergeCell ref="E14:H14"/>
@@ -4160,6 +4177,7 @@
     <mergeCell ref="I39:K39"/>
     <mergeCell ref="I40:K40"/>
     <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
     <mergeCell ref="I62:K62"/>
     <mergeCell ref="I63:K63"/>
     <mergeCell ref="I64:K64"/>

--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eoons\Desktop\Capstone\파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE079306-8DF1-4F45-A7D1-ABAC11630107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BC16C8-E9A2-485F-9A0B-78EC65FE5BBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12765" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
   <sheets>
     <sheet name="피드백" sheetId="7" r:id="rId1"/>
@@ -19,42 +19,31 @@
     <sheet name="버그" sheetId="4" r:id="rId4"/>
     <sheet name="서재 미니게임 구상" sheetId="8" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+        <ext xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="1"/>
         </ext>
       </extLst>
@@ -72,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="210">
   <si>
     <t>설명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -864,6 +853,32 @@
   </si>
   <si>
     <t>싱크대에서 열쇠를 가져갈 때 질문이 한번만 나오도록 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">열쇠 오브젝트가 2개가 나와서 질문이 2번 나오는 거
+수정 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지도 자물쇠 맵핑이 잘못되어 있었음 수정 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책 속에서 힌트를 넣기 + 주방의 체셔가 플레이어가 
+책의 페이지에 주목 할 수 있도록 프롬프트 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물병에 물을 부을 때 어색하던 콜리전 방식에서 2초를
+기다리는 방식과 물병의 입구와 물 줄기의 넓이를 맞춰서
+어색하던 연출 수정완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1층의 메이드 방과 서제만 적용 2층은 추후 적용 예정
+메이드 방과 서재의 입구의 문이 열려있는 스프라이트
+마련 완료 후 열쇠를 드래그 앤 드롭 했을 때 열린 문이 set active == true가 되도록 수정</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1255,10 +1270,40 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1270,42 +1315,39 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1313,34 +1355,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1885,36 +1900,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="43" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
@@ -1927,17 +1942,17 @@
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="56" t="s">
+      <c r="E3" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56" t="s">
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="44"/>
+      <c r="I3" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="56"/>
-      <c r="K3" s="56"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="44"/>
       <c r="L3" s="5" t="s">
         <v>59</v>
       </c>
@@ -1956,17 +1971,17 @@
       <c r="D4" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55" t="s">
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
       <c r="L4" s="11" t="s">
         <v>172</v>
       </c>
@@ -1983,17 +1998,17 @@
       <c r="D5" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="55" t="s">
+      <c r="E5" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55" t="s">
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="55"/>
-      <c r="K5" s="55"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
       <c r="L5" s="11" t="s">
         <v>172</v>
       </c>
@@ -2010,17 +2025,17 @@
       <c r="D6" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55" t="s">
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
       <c r="L6" s="11" t="s">
         <v>172</v>
       </c>
@@ -2037,17 +2052,17 @@
       <c r="D7" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E7" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
       <c r="H7" s="30"/>
-      <c r="I7" s="55" t="s">
+      <c r="I7" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
       <c r="L7" s="11" t="s">
         <v>172</v>
       </c>
@@ -2064,17 +2079,17 @@
       <c r="D8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="55" t="s">
+      <c r="E8" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="55" t="s">
+      <c r="I8" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="55"/>
-      <c r="K8" s="55"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
       <c r="L8" s="11" t="s">
         <v>172</v>
       </c>
@@ -2091,17 +2106,17 @@
       <c r="D9" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="55" t="s">
+      <c r="E9" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
       <c r="H9" s="30"/>
-      <c r="I9" s="55" t="s">
+      <c r="I9" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="55"/>
-      <c r="K9" s="55"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
       <c r="L9" s="11" t="s">
         <v>172</v>
       </c>
@@ -2118,17 +2133,17 @@
       <c r="D10" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="55" t="s">
+      <c r="E10" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="30"/>
-      <c r="I10" s="55" t="s">
+      <c r="I10" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="55"/>
-      <c r="K10" s="55"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
       <c r="L10" s="11" t="s">
         <v>172</v>
       </c>
@@ -2145,17 +2160,17 @@
       <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="55" t="s">
+      <c r="E11" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55" t="s">
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="55"/>
-      <c r="K11" s="55"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
       <c r="L11" s="11" t="s">
         <v>172</v>
       </c>
@@ -2172,17 +2187,17 @@
       <c r="D12" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="55" t="s">
+      <c r="E12" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55" t="s">
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
       <c r="L12" s="11" t="s">
         <v>62</v>
       </c>
@@ -2199,17 +2214,17 @@
       <c r="D13" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="55" t="s">
+      <c r="E13" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55" t="s">
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
       <c r="L13" s="11" t="s">
         <v>60</v>
       </c>
@@ -2226,17 +2241,17 @@
       <c r="D14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="55" t="s">
+      <c r="E14" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55" t="s">
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="55"/>
-      <c r="K14" s="55"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
       <c r="L14" s="11" t="s">
         <v>62</v>
       </c>
@@ -2253,17 +2268,17 @@
       <c r="D15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="55" t="s">
+      <c r="E15" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55" t="s">
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
       <c r="L15" s="11" t="s">
         <v>172</v>
       </c>
@@ -2280,17 +2295,17 @@
       <c r="D16" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="55" t="s">
+      <c r="E16" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="55" t="s">
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="55"/>
-      <c r="K16" s="55"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
       <c r="L16" s="11" t="s">
         <v>172</v>
       </c>
@@ -2307,17 +2322,17 @@
       <c r="D17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="55" t="s">
+      <c r="E17" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55" t="s">
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
       <c r="L17" s="11" t="s">
         <v>172</v>
       </c>
@@ -2334,17 +2349,17 @@
       <c r="D18" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="55" t="s">
+      <c r="E18" s="42" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="55"/>
-      <c r="G18" s="55"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="55" t="s">
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="55"/>
-      <c r="K18" s="55"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
       <c r="L18" s="11" t="s">
         <v>172</v>
       </c>
@@ -2361,17 +2376,17 @@
       <c r="D19" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="E19" s="45" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="51"/>
-      <c r="I19" s="51" t="s">
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="51"/>
-      <c r="K19" s="51"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
       <c r="L19" s="11" t="s">
         <v>60</v>
       </c>
@@ -2388,17 +2403,17 @@
       <c r="D20" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="E20" s="45" t="s">
         <v>160</v>
       </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="51"/>
-      <c r="H20" s="51"/>
-      <c r="I20" s="51" t="s">
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
       <c r="L20" s="11" t="s">
         <v>60</v>
       </c>
@@ -2415,17 +2430,17 @@
       <c r="D21" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="51" t="s">
+      <c r="E21" s="45" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="51"/>
-      <c r="G21" s="51"/>
-      <c r="H21" s="51"/>
-      <c r="I21" s="51" t="s">
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="51"/>
-      <c r="K21" s="51"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
       <c r="L21" s="11" t="s">
         <v>172</v>
       </c>
@@ -2442,17 +2457,17 @@
       <c r="D22" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="51" t="s">
+      <c r="E22" s="45" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="51"/>
-      <c r="G22" s="51"/>
-      <c r="H22" s="51"/>
-      <c r="I22" s="51" t="s">
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="J22" s="51"/>
-      <c r="K22" s="51"/>
+      <c r="J22" s="45"/>
+      <c r="K22" s="45"/>
       <c r="L22" s="11" t="s">
         <v>172</v>
       </c>
@@ -2469,17 +2484,17 @@
       <c r="D23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="52" t="s">
+      <c r="E23" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="51" t="s">
+      <c r="F23" s="46"/>
+      <c r="G23" s="46"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="45" t="s">
         <v>178</v>
       </c>
-      <c r="J23" s="51"/>
-      <c r="K23" s="51"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
       <c r="L23" s="11" t="s">
         <v>60</v>
       </c>
@@ -2496,17 +2511,17 @@
       <c r="D24" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="52" t="s">
+      <c r="E24" s="46" t="s">
         <v>179</v>
       </c>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="51" t="s">
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
       <c r="L24" s="11" t="s">
         <v>60</v>
       </c>
@@ -2523,17 +2538,17 @@
       <c r="D25" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="52" t="s">
+      <c r="E25" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="51" t="s">
+      <c r="F25" s="46"/>
+      <c r="G25" s="46"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="J25" s="51"/>
-      <c r="K25" s="51"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
       <c r="L25" s="11" t="s">
         <v>60</v>
       </c>
@@ -2550,21 +2565,23 @@
       <c r="D26" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="53" t="s">
+      <c r="E26" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="53"/>
-      <c r="G26" s="53"/>
-      <c r="H26" s="53"/>
-      <c r="I26" s="53" t="s">
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+      <c r="H26" s="47"/>
+      <c r="I26" s="47" t="s">
         <v>187</v>
       </c>
-      <c r="J26" s="53"/>
-      <c r="K26" s="53"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="47"/>
       <c r="L26" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M26" s="20"/>
+        <v>172</v>
+      </c>
+      <c r="M26" s="12" t="s">
+        <v>208</v>
+      </c>
       <c r="P26" s="40" t="s">
         <v>201</v>
       </c>
@@ -2583,21 +2600,23 @@
       <c r="D27" s="37" t="s">
         <v>190</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="F27" s="49"/>
-      <c r="G27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="51"/>
       <c r="H27" s="38"/>
-      <c r="I27" s="43" t="s">
+      <c r="I27" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="J27" s="44"/>
-      <c r="K27" s="45"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="55"/>
       <c r="L27" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M27" s="20"/>
+        <v>62</v>
+      </c>
+      <c r="M27" s="12" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="28" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20"/>
@@ -2616,15 +2635,17 @@
       <c r="F28" s="39"/>
       <c r="G28" s="39"/>
       <c r="H28" s="39"/>
-      <c r="I28" s="43" t="s">
+      <c r="I28" s="53" t="s">
         <v>196</v>
       </c>
-      <c r="J28" s="44"/>
-      <c r="K28" s="45"/>
+      <c r="J28" s="54"/>
+      <c r="K28" s="55"/>
       <c r="L28" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M28" s="20"/>
+        <v>172</v>
+      </c>
+      <c r="M28" s="12" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="29" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20"/>
@@ -2637,21 +2658,23 @@
       <c r="D29" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E29" s="48" t="s">
+      <c r="E29" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="F29" s="49"/>
-      <c r="G29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="51"/>
       <c r="H29" s="38"/>
-      <c r="I29" s="43" t="s">
+      <c r="I29" s="53" t="s">
         <v>199</v>
       </c>
-      <c r="J29" s="44"/>
-      <c r="K29" s="45"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="55"/>
       <c r="L29" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M29" s="20"/>
+        <v>172</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="30" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20"/>
@@ -2664,21 +2687,23 @@
       <c r="D30" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E30" s="53" t="s">
+      <c r="E30" s="47" t="s">
         <v>203</v>
       </c>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="46" t="s">
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+      <c r="H30" s="47"/>
+      <c r="I30" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
       <c r="L30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M30" s="20"/>
+        <v>172</v>
+      </c>
+      <c r="M30" s="12" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="31" spans="1:17" s="19" customFormat="1" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20"/>
@@ -2687,13 +2712,13 @@
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
+      <c r="H31" s="48"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
       <c r="L31" s="11" t="s">
         <v>60</v>
       </c>
@@ -2706,13 +2731,13 @@
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
+      <c r="E32" s="48"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="48"/>
+      <c r="H32" s="48"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="48"/>
+      <c r="K32" s="48"/>
       <c r="L32" s="11" t="s">
         <v>60</v>
       </c>
@@ -2725,13 +2750,13 @@
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
       <c r="L33" s="11" t="s">
         <v>60</v>
       </c>
@@ -2744,13 +2769,13 @@
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="48"/>
+      <c r="G34" s="48"/>
+      <c r="H34" s="48"/>
+      <c r="I34" s="48"/>
+      <c r="J34" s="48"/>
+      <c r="K34" s="48"/>
       <c r="L34" s="11" t="s">
         <v>60</v>
       </c>
@@ -2763,13 +2788,13 @@
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="42"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
       <c r="L35" s="11" t="s">
         <v>60</v>
       </c>
@@ -2782,13 +2807,13 @@
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="48"/>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
       <c r="L36" s="11" t="s">
         <v>60</v>
       </c>
@@ -2801,13 +2826,13 @@
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="42"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
+      <c r="H37" s="48"/>
+      <c r="I37" s="48"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
       <c r="L37" s="11" t="s">
         <v>60</v>
       </c>
@@ -2820,13 +2845,13 @@
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="42"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="42"/>
-      <c r="J38" s="42"/>
-      <c r="K38" s="42"/>
+      <c r="E38" s="48"/>
+      <c r="F38" s="48"/>
+      <c r="G38" s="48"/>
+      <c r="H38" s="48"/>
+      <c r="I38" s="48"/>
+      <c r="J38" s="48"/>
+      <c r="K38" s="48"/>
       <c r="L38" s="11" t="s">
         <v>60</v>
       </c>
@@ -2839,13 +2864,13 @@
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="42"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42"/>
-      <c r="K39" s="42"/>
+      <c r="E39" s="48"/>
+      <c r="F39" s="48"/>
+      <c r="G39" s="48"/>
+      <c r="H39" s="48"/>
+      <c r="I39" s="48"/>
+      <c r="J39" s="48"/>
+      <c r="K39" s="48"/>
       <c r="L39" s="11" t="s">
         <v>60</v>
       </c>
@@ -2858,13 +2883,13 @@
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="42"/>
-      <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
-      <c r="K40" s="42"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
       <c r="L40" s="11" t="s">
         <v>60</v>
       </c>
@@ -2877,13 +2902,13 @@
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
-      <c r="K41" s="42"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="48"/>
+      <c r="H41" s="48"/>
+      <c r="I41" s="48"/>
+      <c r="J41" s="48"/>
+      <c r="K41" s="48"/>
       <c r="L41" s="11" t="s">
         <v>60</v>
       </c>
@@ -2896,13 +2921,13 @@
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48"/>
+      <c r="J42" s="48"/>
+      <c r="K42" s="48"/>
       <c r="L42" s="11" t="s">
         <v>60</v>
       </c>
@@ -2915,13 +2940,13 @@
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="42"/>
-      <c r="I43" s="42"/>
-      <c r="J43" s="42"/>
-      <c r="K43" s="42"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
       <c r="L43" s="11" t="s">
         <v>60</v>
       </c>
@@ -2934,13 +2959,13 @@
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="42"/>
-      <c r="H44" s="42"/>
-      <c r="I44" s="42"/>
-      <c r="J44" s="42"/>
-      <c r="K44" s="42"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
       <c r="L44" s="11" t="s">
         <v>60</v>
       </c>
@@ -2953,13 +2978,13 @@
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="42"/>
-      <c r="F45" s="42"/>
-      <c r="G45" s="42"/>
-      <c r="H45" s="42"/>
-      <c r="I45" s="42"/>
-      <c r="J45" s="42"/>
-      <c r="K45" s="42"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48"/>
+      <c r="I45" s="48"/>
+      <c r="J45" s="48"/>
+      <c r="K45" s="48"/>
       <c r="L45" s="11" t="s">
         <v>60</v>
       </c>
@@ -2972,13 +2997,13 @@
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="42"/>
-      <c r="J46" s="42"/>
-      <c r="K46" s="42"/>
+      <c r="E46" s="48"/>
+      <c r="F46" s="48"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="48"/>
+      <c r="I46" s="48"/>
+      <c r="J46" s="48"/>
+      <c r="K46" s="48"/>
       <c r="L46" s="11" t="s">
         <v>60</v>
       </c>
@@ -2991,13 +3016,13 @@
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
-      <c r="J47" s="42"/>
-      <c r="K47" s="42"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
+      <c r="H47" s="48"/>
+      <c r="I47" s="48"/>
+      <c r="J47" s="48"/>
+      <c r="K47" s="48"/>
       <c r="L47" s="11" t="s">
         <v>60</v>
       </c>
@@ -3010,13 +3035,13 @@
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="42"/>
-      <c r="F48" s="42"/>
-      <c r="G48" s="42"/>
-      <c r="H48" s="42"/>
-      <c r="I48" s="42"/>
-      <c r="J48" s="42"/>
-      <c r="K48" s="42"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="G48" s="48"/>
+      <c r="H48" s="48"/>
+      <c r="I48" s="48"/>
+      <c r="J48" s="48"/>
+      <c r="K48" s="48"/>
       <c r="L48" s="11" t="s">
         <v>60</v>
       </c>
@@ -3029,13 +3054,13 @@
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="42"/>
-      <c r="H49" s="42"/>
-      <c r="I49" s="42"/>
-      <c r="J49" s="42"/>
-      <c r="K49" s="42"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
       <c r="L49" s="11" t="s">
         <v>60</v>
       </c>
@@ -3048,13 +3073,13 @@
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="42"/>
-      <c r="I50" s="42"/>
-      <c r="J50" s="42"/>
-      <c r="K50" s="42"/>
+      <c r="E50" s="48"/>
+      <c r="F50" s="48"/>
+      <c r="G50" s="48"/>
+      <c r="H50" s="48"/>
+      <c r="I50" s="48"/>
+      <c r="J50" s="48"/>
+      <c r="K50" s="48"/>
       <c r="L50" s="11" t="s">
         <v>60</v>
       </c>
@@ -3067,13 +3092,13 @@
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="42"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="42"/>
-      <c r="J51" s="42"/>
-      <c r="K51" s="42"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+      <c r="I51" s="48"/>
+      <c r="J51" s="48"/>
+      <c r="K51" s="48"/>
       <c r="L51" s="11" t="s">
         <v>60</v>
       </c>
@@ -3086,13 +3111,13 @@
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="42"/>
-      <c r="H52" s="42"/>
-      <c r="I52" s="42"/>
-      <c r="J52" s="42"/>
-      <c r="K52" s="42"/>
+      <c r="E52" s="48"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="48"/>
+      <c r="H52" s="48"/>
+      <c r="I52" s="48"/>
+      <c r="J52" s="48"/>
+      <c r="K52" s="48"/>
       <c r="L52" s="11" t="s">
         <v>60</v>
       </c>
@@ -3105,13 +3130,13 @@
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
-      <c r="H53" s="42"/>
-      <c r="I53" s="42"/>
-      <c r="J53" s="42"/>
-      <c r="K53" s="42"/>
+      <c r="E53" s="48"/>
+      <c r="F53" s="48"/>
+      <c r="G53" s="48"/>
+      <c r="H53" s="48"/>
+      <c r="I53" s="48"/>
+      <c r="J53" s="48"/>
+      <c r="K53" s="48"/>
       <c r="L53" s="11" t="s">
         <v>60</v>
       </c>
@@ -3124,13 +3149,13 @@
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="42"/>
-      <c r="I54" s="42"/>
-      <c r="J54" s="42"/>
-      <c r="K54" s="42"/>
+      <c r="E54" s="48"/>
+      <c r="F54" s="48"/>
+      <c r="G54" s="48"/>
+      <c r="H54" s="48"/>
+      <c r="I54" s="48"/>
+      <c r="J54" s="48"/>
+      <c r="K54" s="48"/>
       <c r="L54" s="11" t="s">
         <v>60</v>
       </c>
@@ -3143,13 +3168,13 @@
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="42"/>
-      <c r="I55" s="42"/>
-      <c r="J55" s="42"/>
-      <c r="K55" s="42"/>
+      <c r="E55" s="48"/>
+      <c r="F55" s="48"/>
+      <c r="G55" s="48"/>
+      <c r="H55" s="48"/>
+      <c r="I55" s="48"/>
+      <c r="J55" s="48"/>
+      <c r="K55" s="48"/>
       <c r="L55" s="11" t="s">
         <v>60</v>
       </c>
@@ -3162,13 +3187,13 @@
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="42"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="42"/>
-      <c r="K56" s="42"/>
+      <c r="E56" s="48"/>
+      <c r="F56" s="48"/>
+      <c r="G56" s="48"/>
+      <c r="H56" s="48"/>
+      <c r="I56" s="48"/>
+      <c r="J56" s="48"/>
+      <c r="K56" s="48"/>
       <c r="L56" s="11" t="s">
         <v>60</v>
       </c>
@@ -3181,13 +3206,13 @@
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="42"/>
-      <c r="K57" s="42"/>
+      <c r="E57" s="48"/>
+      <c r="F57" s="48"/>
+      <c r="G57" s="48"/>
+      <c r="H57" s="48"/>
+      <c r="I57" s="48"/>
+      <c r="J57" s="48"/>
+      <c r="K57" s="48"/>
       <c r="L57" s="11" t="s">
         <v>60</v>
       </c>
@@ -3200,13 +3225,13 @@
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
-      <c r="J58" s="42"/>
-      <c r="K58" s="42"/>
+      <c r="E58" s="48"/>
+      <c r="F58" s="48"/>
+      <c r="G58" s="48"/>
+      <c r="H58" s="48"/>
+      <c r="I58" s="48"/>
+      <c r="J58" s="48"/>
+      <c r="K58" s="48"/>
       <c r="L58" s="11" t="s">
         <v>60</v>
       </c>
@@ -3219,13 +3244,13 @@
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="42"/>
-      <c r="J59" s="42"/>
-      <c r="K59" s="42"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
       <c r="L59" s="11" t="s">
         <v>60</v>
       </c>
@@ -3238,13 +3263,13 @@
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="42"/>
-      <c r="I60" s="42"/>
-      <c r="J60" s="42"/>
-      <c r="K60" s="42"/>
+      <c r="E60" s="48"/>
+      <c r="F60" s="48"/>
+      <c r="G60" s="48"/>
+      <c r="H60" s="48"/>
+      <c r="I60" s="48"/>
+      <c r="J60" s="48"/>
+      <c r="K60" s="48"/>
       <c r="L60" s="11" t="s">
         <v>60</v>
       </c>
@@ -3257,13 +3282,13 @@
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="42"/>
-      <c r="H61" s="42"/>
-      <c r="I61" s="42"/>
-      <c r="J61" s="42"/>
-      <c r="K61" s="42"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="48"/>
+      <c r="G61" s="48"/>
+      <c r="H61" s="48"/>
+      <c r="I61" s="48"/>
+      <c r="J61" s="48"/>
+      <c r="K61" s="48"/>
       <c r="L61" s="11" t="s">
         <v>60</v>
       </c>
@@ -3276,13 +3301,13 @@
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="42"/>
-      <c r="H62" s="42"/>
-      <c r="I62" s="42"/>
-      <c r="J62" s="42"/>
-      <c r="K62" s="42"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="48"/>
+      <c r="G62" s="48"/>
+      <c r="H62" s="48"/>
+      <c r="I62" s="48"/>
+      <c r="J62" s="48"/>
+      <c r="K62" s="48"/>
       <c r="L62" s="11" t="s">
         <v>60</v>
       </c>
@@ -3295,13 +3320,13 @@
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="42"/>
-      <c r="G63" s="42"/>
-      <c r="H63" s="42"/>
-      <c r="I63" s="42"/>
-      <c r="J63" s="42"/>
-      <c r="K63" s="42"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="48"/>
+      <c r="G63" s="48"/>
+      <c r="H63" s="48"/>
+      <c r="I63" s="48"/>
+      <c r="J63" s="48"/>
+      <c r="K63" s="48"/>
       <c r="L63" s="11" t="s">
         <v>60</v>
       </c>
@@ -3314,13 +3339,13 @@
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="42"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="42"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="42"/>
-      <c r="K64" s="42"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="48"/>
+      <c r="G64" s="48"/>
+      <c r="H64" s="48"/>
+      <c r="I64" s="48"/>
+      <c r="J64" s="48"/>
+      <c r="K64" s="48"/>
       <c r="L64" s="11" t="s">
         <v>60</v>
       </c>
@@ -3333,13 +3358,13 @@
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="42"/>
-      <c r="H65" s="42"/>
-      <c r="I65" s="42"/>
-      <c r="J65" s="42"/>
-      <c r="K65" s="42"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="48"/>
+      <c r="G65" s="48"/>
+      <c r="H65" s="48"/>
+      <c r="I65" s="48"/>
+      <c r="J65" s="48"/>
+      <c r="K65" s="48"/>
       <c r="L65" s="11" t="s">
         <v>60</v>
       </c>
@@ -3352,13 +3377,13 @@
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="42"/>
-      <c r="G66" s="42"/>
-      <c r="H66" s="42"/>
-      <c r="I66" s="42"/>
-      <c r="J66" s="42"/>
-      <c r="K66" s="42"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="48"/>
+      <c r="G66" s="48"/>
+      <c r="H66" s="48"/>
+      <c r="I66" s="48"/>
+      <c r="J66" s="48"/>
+      <c r="K66" s="48"/>
       <c r="L66" s="11" t="s">
         <v>60</v>
       </c>
@@ -3371,13 +3396,13 @@
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="47"/>
-      <c r="F67" s="47"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="47"/>
-      <c r="I67" s="42"/>
-      <c r="J67" s="42"/>
-      <c r="K67" s="42"/>
+      <c r="E67" s="52"/>
+      <c r="F67" s="52"/>
+      <c r="G67" s="52"/>
+      <c r="H67" s="52"/>
+      <c r="I67" s="48"/>
+      <c r="J67" s="48"/>
+      <c r="K67" s="48"/>
       <c r="L67" s="11" t="s">
         <v>60</v>
       </c>
@@ -3390,13 +3415,13 @@
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="42"/>
-      <c r="I68" s="42"/>
-      <c r="J68" s="42"/>
-      <c r="K68" s="42"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="48"/>
       <c r="L68" s="11" t="s">
         <v>60</v>
       </c>
@@ -3409,13 +3434,13 @@
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="42"/>
-      <c r="F69" s="42"/>
-      <c r="G69" s="42"/>
-      <c r="H69" s="42"/>
-      <c r="I69" s="42"/>
-      <c r="J69" s="42"/>
-      <c r="K69" s="42"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="48"/>
+      <c r="G69" s="48"/>
+      <c r="H69" s="48"/>
+      <c r="I69" s="48"/>
+      <c r="J69" s="48"/>
+      <c r="K69" s="48"/>
       <c r="L69" s="11" t="s">
         <v>60</v>
       </c>
@@ -3428,13 +3453,13 @@
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="42"/>
-      <c r="F70" s="42"/>
-      <c r="G70" s="42"/>
-      <c r="H70" s="42"/>
-      <c r="I70" s="42"/>
-      <c r="J70" s="42"/>
-      <c r="K70" s="42"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="48"/>
+      <c r="G70" s="48"/>
+      <c r="H70" s="48"/>
+      <c r="I70" s="48"/>
+      <c r="J70" s="48"/>
+      <c r="K70" s="48"/>
       <c r="L70" s="11" t="s">
         <v>60</v>
       </c>
@@ -3447,13 +3472,13 @@
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="42"/>
-      <c r="G71" s="42"/>
-      <c r="H71" s="42"/>
-      <c r="I71" s="42"/>
-      <c r="J71" s="42"/>
-      <c r="K71" s="42"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
       <c r="L71" s="11" t="s">
         <v>60</v>
       </c>
@@ -3466,13 +3491,13 @@
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-      <c r="E72" s="42"/>
-      <c r="F72" s="42"/>
-      <c r="G72" s="42"/>
-      <c r="H72" s="42"/>
-      <c r="I72" s="42"/>
-      <c r="J72" s="42"/>
-      <c r="K72" s="42"/>
+      <c r="E72" s="48"/>
+      <c r="F72" s="48"/>
+      <c r="G72" s="48"/>
+      <c r="H72" s="48"/>
+      <c r="I72" s="48"/>
+      <c r="J72" s="48"/>
+      <c r="K72" s="48"/>
       <c r="L72" s="11" t="s">
         <v>60</v>
       </c>
@@ -3485,13 +3510,13 @@
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="42"/>
-      <c r="F73" s="42"/>
-      <c r="G73" s="42"/>
-      <c r="H73" s="42"/>
-      <c r="I73" s="42"/>
-      <c r="J73" s="42"/>
-      <c r="K73" s="42"/>
+      <c r="E73" s="48"/>
+      <c r="F73" s="48"/>
+      <c r="G73" s="48"/>
+      <c r="H73" s="48"/>
+      <c r="I73" s="48"/>
+      <c r="J73" s="48"/>
+      <c r="K73" s="48"/>
       <c r="L73" s="11" t="s">
         <v>60</v>
       </c>
@@ -3504,13 +3529,13 @@
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-      <c r="E74" s="42"/>
-      <c r="F74" s="42"/>
-      <c r="G74" s="42"/>
-      <c r="H74" s="42"/>
-      <c r="I74" s="42"/>
-      <c r="J74" s="42"/>
-      <c r="K74" s="42"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="48"/>
+      <c r="G74" s="48"/>
+      <c r="H74" s="48"/>
+      <c r="I74" s="48"/>
+      <c r="J74" s="48"/>
+      <c r="K74" s="48"/>
       <c r="L74" s="11" t="s">
         <v>60</v>
       </c>
@@ -3523,13 +3548,13 @@
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-      <c r="E75" s="42"/>
-      <c r="F75" s="42"/>
-      <c r="G75" s="42"/>
-      <c r="H75" s="42"/>
-      <c r="I75" s="42"/>
-      <c r="J75" s="42"/>
-      <c r="K75" s="42"/>
+      <c r="E75" s="48"/>
+      <c r="F75" s="48"/>
+      <c r="G75" s="48"/>
+      <c r="H75" s="48"/>
+      <c r="I75" s="48"/>
+      <c r="J75" s="48"/>
+      <c r="K75" s="48"/>
       <c r="L75" s="11" t="s">
         <v>60</v>
       </c>
@@ -3542,13 +3567,13 @@
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-      <c r="E76" s="42"/>
-      <c r="F76" s="42"/>
-      <c r="G76" s="42"/>
-      <c r="H76" s="42"/>
-      <c r="I76" s="42"/>
-      <c r="J76" s="42"/>
-      <c r="K76" s="42"/>
+      <c r="E76" s="48"/>
+      <c r="F76" s="48"/>
+      <c r="G76" s="48"/>
+      <c r="H76" s="48"/>
+      <c r="I76" s="48"/>
+      <c r="J76" s="48"/>
+      <c r="K76" s="48"/>
       <c r="L76" s="11" t="s">
         <v>60</v>
       </c>
@@ -3561,13 +3586,13 @@
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="42"/>
-      <c r="H77" s="42"/>
-      <c r="I77" s="42"/>
-      <c r="J77" s="42"/>
-      <c r="K77" s="42"/>
+      <c r="E77" s="48"/>
+      <c r="F77" s="48"/>
+      <c r="G77" s="48"/>
+      <c r="H77" s="48"/>
+      <c r="I77" s="48"/>
+      <c r="J77" s="48"/>
+      <c r="K77" s="48"/>
       <c r="L77" s="11" t="s">
         <v>60</v>
       </c>
@@ -3580,13 +3605,13 @@
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-      <c r="E78" s="42"/>
-      <c r="F78" s="42"/>
-      <c r="G78" s="42"/>
-      <c r="H78" s="42"/>
-      <c r="I78" s="42"/>
-      <c r="J78" s="42"/>
-      <c r="K78" s="42"/>
+      <c r="E78" s="48"/>
+      <c r="F78" s="48"/>
+      <c r="G78" s="48"/>
+      <c r="H78" s="48"/>
+      <c r="I78" s="48"/>
+      <c r="J78" s="48"/>
+      <c r="K78" s="48"/>
       <c r="L78" s="11" t="s">
         <v>60</v>
       </c>
@@ -3599,13 +3624,13 @@
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="42"/>
-      <c r="G79" s="42"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-      <c r="J79" s="42"/>
-      <c r="K79" s="42"/>
+      <c r="E79" s="48"/>
+      <c r="F79" s="48"/>
+      <c r="G79" s="48"/>
+      <c r="H79" s="48"/>
+      <c r="I79" s="48"/>
+      <c r="J79" s="48"/>
+      <c r="K79" s="48"/>
       <c r="L79" s="11" t="s">
         <v>60</v>
       </c>
@@ -3618,13 +3643,13 @@
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-      <c r="E80" s="42"/>
-      <c r="F80" s="42"/>
-      <c r="G80" s="42"/>
-      <c r="H80" s="42"/>
-      <c r="I80" s="42"/>
-      <c r="J80" s="42"/>
-      <c r="K80" s="42"/>
+      <c r="E80" s="48"/>
+      <c r="F80" s="48"/>
+      <c r="G80" s="48"/>
+      <c r="H80" s="48"/>
+      <c r="I80" s="48"/>
+      <c r="J80" s="48"/>
+      <c r="K80" s="48"/>
       <c r="L80" s="11" t="s">
         <v>60</v>
       </c>
@@ -3637,13 +3662,13 @@
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-      <c r="E81" s="42"/>
-      <c r="F81" s="42"/>
-      <c r="G81" s="42"/>
-      <c r="H81" s="42"/>
-      <c r="I81" s="42"/>
-      <c r="J81" s="42"/>
-      <c r="K81" s="42"/>
+      <c r="E81" s="48"/>
+      <c r="F81" s="48"/>
+      <c r="G81" s="48"/>
+      <c r="H81" s="48"/>
+      <c r="I81" s="48"/>
+      <c r="J81" s="48"/>
+      <c r="K81" s="48"/>
       <c r="L81" s="11" t="s">
         <v>60</v>
       </c>
@@ -3656,13 +3681,13 @@
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="42"/>
-      <c r="F82" s="42"/>
-      <c r="G82" s="42"/>
-      <c r="H82" s="42"/>
-      <c r="I82" s="42"/>
-      <c r="J82" s="42"/>
-      <c r="K82" s="42"/>
+      <c r="E82" s="48"/>
+      <c r="F82" s="48"/>
+      <c r="G82" s="48"/>
+      <c r="H82" s="48"/>
+      <c r="I82" s="48"/>
+      <c r="J82" s="48"/>
+      <c r="K82" s="48"/>
       <c r="L82" s="11" t="s">
         <v>60</v>
       </c>
@@ -3675,13 +3700,13 @@
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-      <c r="E83" s="42"/>
-      <c r="F83" s="42"/>
-      <c r="G83" s="42"/>
-      <c r="H83" s="42"/>
-      <c r="I83" s="42"/>
-      <c r="J83" s="42"/>
-      <c r="K83" s="42"/>
+      <c r="E83" s="48"/>
+      <c r="F83" s="48"/>
+      <c r="G83" s="48"/>
+      <c r="H83" s="48"/>
+      <c r="I83" s="48"/>
+      <c r="J83" s="48"/>
+      <c r="K83" s="48"/>
       <c r="L83" s="11" t="s">
         <v>60</v>
       </c>
@@ -3694,13 +3719,13 @@
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="42"/>
-      <c r="F84" s="42"/>
-      <c r="G84" s="42"/>
-      <c r="H84" s="42"/>
-      <c r="I84" s="42"/>
-      <c r="J84" s="42"/>
-      <c r="K84" s="42"/>
+      <c r="E84" s="48"/>
+      <c r="F84" s="48"/>
+      <c r="G84" s="48"/>
+      <c r="H84" s="48"/>
+      <c r="I84" s="48"/>
+      <c r="J84" s="48"/>
+      <c r="K84" s="48"/>
       <c r="L84" s="11" t="s">
         <v>60</v>
       </c>
@@ -3713,13 +3738,13 @@
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="42"/>
-      <c r="F85" s="42"/>
-      <c r="G85" s="42"/>
-      <c r="H85" s="42"/>
-      <c r="I85" s="42"/>
-      <c r="J85" s="42"/>
-      <c r="K85" s="42"/>
+      <c r="E85" s="48"/>
+      <c r="F85" s="48"/>
+      <c r="G85" s="48"/>
+      <c r="H85" s="48"/>
+      <c r="I85" s="48"/>
+      <c r="J85" s="48"/>
+      <c r="K85" s="48"/>
       <c r="L85" s="11" t="s">
         <v>60</v>
       </c>
@@ -3732,13 +3757,13 @@
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="42"/>
-      <c r="F86" s="42"/>
-      <c r="G86" s="42"/>
-      <c r="H86" s="42"/>
-      <c r="I86" s="42"/>
-      <c r="J86" s="42"/>
-      <c r="K86" s="42"/>
+      <c r="E86" s="48"/>
+      <c r="F86" s="48"/>
+      <c r="G86" s="48"/>
+      <c r="H86" s="48"/>
+      <c r="I86" s="48"/>
+      <c r="J86" s="48"/>
+      <c r="K86" s="48"/>
       <c r="L86" s="11" t="s">
         <v>60</v>
       </c>
@@ -3751,13 +3776,13 @@
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="42"/>
-      <c r="F87" s="42"/>
-      <c r="G87" s="42"/>
-      <c r="H87" s="42"/>
-      <c r="I87" s="42"/>
-      <c r="J87" s="42"/>
-      <c r="K87" s="42"/>
+      <c r="E87" s="48"/>
+      <c r="F87" s="48"/>
+      <c r="G87" s="48"/>
+      <c r="H87" s="48"/>
+      <c r="I87" s="48"/>
+      <c r="J87" s="48"/>
+      <c r="K87" s="48"/>
       <c r="L87" s="11" t="s">
         <v>60</v>
       </c>
@@ -3770,13 +3795,13 @@
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="42"/>
-      <c r="F88" s="42"/>
-      <c r="G88" s="42"/>
-      <c r="H88" s="42"/>
-      <c r="I88" s="42"/>
-      <c r="J88" s="42"/>
-      <c r="K88" s="42"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
+      <c r="J88" s="48"/>
+      <c r="K88" s="48"/>
       <c r="L88" s="11" t="s">
         <v>60</v>
       </c>
@@ -3789,13 +3814,13 @@
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="42"/>
-      <c r="F89" s="42"/>
-      <c r="G89" s="42"/>
-      <c r="H89" s="42"/>
-      <c r="I89" s="42"/>
-      <c r="J89" s="42"/>
-      <c r="K89" s="42"/>
+      <c r="E89" s="48"/>
+      <c r="F89" s="48"/>
+      <c r="G89" s="48"/>
+      <c r="H89" s="48"/>
+      <c r="I89" s="48"/>
+      <c r="J89" s="48"/>
+      <c r="K89" s="48"/>
       <c r="L89" s="11" t="s">
         <v>60</v>
       </c>
@@ -3808,13 +3833,13 @@
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="42"/>
-      <c r="F90" s="42"/>
-      <c r="G90" s="42"/>
-      <c r="H90" s="42"/>
-      <c r="I90" s="42"/>
-      <c r="J90" s="42"/>
-      <c r="K90" s="42"/>
+      <c r="E90" s="48"/>
+      <c r="F90" s="48"/>
+      <c r="G90" s="48"/>
+      <c r="H90" s="48"/>
+      <c r="I90" s="48"/>
+      <c r="J90" s="48"/>
+      <c r="K90" s="48"/>
       <c r="L90" s="11" t="s">
         <v>60</v>
       </c>
@@ -3827,13 +3852,13 @@
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="42"/>
-      <c r="F91" s="42"/>
-      <c r="G91" s="42"/>
-      <c r="H91" s="42"/>
-      <c r="I91" s="42"/>
-      <c r="J91" s="42"/>
-      <c r="K91" s="42"/>
+      <c r="E91" s="48"/>
+      <c r="F91" s="48"/>
+      <c r="G91" s="48"/>
+      <c r="H91" s="48"/>
+      <c r="I91" s="48"/>
+      <c r="J91" s="48"/>
+      <c r="K91" s="48"/>
       <c r="L91" s="11" t="s">
         <v>60</v>
       </c>
@@ -3846,13 +3871,13 @@
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="42"/>
-      <c r="F92" s="42"/>
-      <c r="G92" s="42"/>
-      <c r="H92" s="42"/>
-      <c r="I92" s="42"/>
-      <c r="J92" s="42"/>
-      <c r="K92" s="42"/>
+      <c r="E92" s="48"/>
+      <c r="F92" s="48"/>
+      <c r="G92" s="48"/>
+      <c r="H92" s="48"/>
+      <c r="I92" s="48"/>
+      <c r="J92" s="48"/>
+      <c r="K92" s="48"/>
       <c r="L92" s="11" t="s">
         <v>60</v>
       </c>
@@ -3865,13 +3890,13 @@
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="42"/>
-      <c r="F93" s="42"/>
-      <c r="G93" s="42"/>
-      <c r="H93" s="42"/>
-      <c r="I93" s="42"/>
-      <c r="J93" s="42"/>
-      <c r="K93" s="42"/>
+      <c r="E93" s="48"/>
+      <c r="F93" s="48"/>
+      <c r="G93" s="48"/>
+      <c r="H93" s="48"/>
+      <c r="I93" s="48"/>
+      <c r="J93" s="48"/>
+      <c r="K93" s="48"/>
       <c r="L93" s="11" t="s">
         <v>60</v>
       </c>
@@ -3884,13 +3909,13 @@
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="42"/>
-      <c r="F94" s="42"/>
-      <c r="G94" s="42"/>
-      <c r="H94" s="42"/>
-      <c r="I94" s="42"/>
-      <c r="J94" s="42"/>
-      <c r="K94" s="42"/>
+      <c r="E94" s="48"/>
+      <c r="F94" s="48"/>
+      <c r="G94" s="48"/>
+      <c r="H94" s="48"/>
+      <c r="I94" s="48"/>
+      <c r="J94" s="48"/>
+      <c r="K94" s="48"/>
       <c r="L94" s="11" t="s">
         <v>60</v>
       </c>
@@ -3903,13 +3928,13 @@
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="42"/>
-      <c r="F95" s="42"/>
-      <c r="G95" s="42"/>
-      <c r="H95" s="42"/>
-      <c r="I95" s="42"/>
-      <c r="J95" s="42"/>
-      <c r="K95" s="42"/>
+      <c r="E95" s="48"/>
+      <c r="F95" s="48"/>
+      <c r="G95" s="48"/>
+      <c r="H95" s="48"/>
+      <c r="I95" s="48"/>
+      <c r="J95" s="48"/>
+      <c r="K95" s="48"/>
       <c r="L95" s="11" t="s">
         <v>60</v>
       </c>
@@ -3922,13 +3947,13 @@
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="42"/>
-      <c r="F96" s="42"/>
-      <c r="G96" s="42"/>
-      <c r="H96" s="42"/>
-      <c r="I96" s="42"/>
-      <c r="J96" s="42"/>
-      <c r="K96" s="42"/>
+      <c r="E96" s="48"/>
+      <c r="F96" s="48"/>
+      <c r="G96" s="48"/>
+      <c r="H96" s="48"/>
+      <c r="I96" s="48"/>
+      <c r="J96" s="48"/>
+      <c r="K96" s="48"/>
       <c r="L96" s="11" t="s">
         <v>60</v>
       </c>
@@ -3941,13 +3966,13 @@
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="42"/>
-      <c r="F97" s="42"/>
-      <c r="G97" s="42"/>
-      <c r="H97" s="42"/>
-      <c r="I97" s="42"/>
-      <c r="J97" s="42"/>
-      <c r="K97" s="42"/>
+      <c r="E97" s="48"/>
+      <c r="F97" s="48"/>
+      <c r="G97" s="48"/>
+      <c r="H97" s="48"/>
+      <c r="I97" s="48"/>
+      <c r="J97" s="48"/>
+      <c r="K97" s="48"/>
       <c r="L97" s="11" t="s">
         <v>60</v>
       </c>
@@ -3960,13 +3985,13 @@
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="42"/>
-      <c r="F98" s="42"/>
-      <c r="G98" s="42"/>
-      <c r="H98" s="42"/>
-      <c r="I98" s="42"/>
-      <c r="J98" s="42"/>
-      <c r="K98" s="42"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
       <c r="L98" s="11" t="s">
         <v>60</v>
       </c>
@@ -3979,13 +4004,13 @@
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="42"/>
-      <c r="F99" s="42"/>
-      <c r="G99" s="42"/>
-      <c r="H99" s="42"/>
-      <c r="I99" s="42"/>
-      <c r="J99" s="42"/>
-      <c r="K99" s="42"/>
+      <c r="E99" s="48"/>
+      <c r="F99" s="48"/>
+      <c r="G99" s="48"/>
+      <c r="H99" s="48"/>
+      <c r="I99" s="48"/>
+      <c r="J99" s="48"/>
+      <c r="K99" s="48"/>
       <c r="L99" s="11" t="s">
         <v>60</v>
       </c>
@@ -3998,13 +4023,13 @@
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="42"/>
-      <c r="F100" s="42"/>
-      <c r="G100" s="42"/>
-      <c r="H100" s="42"/>
-      <c r="I100" s="42"/>
-      <c r="J100" s="42"/>
-      <c r="K100" s="42"/>
+      <c r="E100" s="48"/>
+      <c r="F100" s="48"/>
+      <c r="G100" s="48"/>
+      <c r="H100" s="48"/>
+      <c r="I100" s="48"/>
+      <c r="J100" s="48"/>
+      <c r="K100" s="48"/>
       <c r="L100" s="11" t="s">
         <v>60</v>
       </c>
@@ -4012,134 +4037,50 @@
     </row>
   </sheetData>
   <mergeCells count="196">
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -4164,50 +4105,134 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E5:H5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -5330,140 +5355,148 @@
   <sheetData>
     <row r="1" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="64" t="s">
+      <c r="B2" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
       <c r="E2" s="24"/>
-      <c r="F2" s="65" t="s">
+      <c r="F2" s="61" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="67"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="63"/>
       <c r="M2" s="24"/>
-      <c r="N2" s="64" t="s">
+      <c r="N2" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="64"/>
-      <c r="P2" s="64"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="63" t="e" vm="1">
+      <c r="B3" s="59" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
       <c r="E3" s="23"/>
-      <c r="F3" s="70" t="s">
+      <c r="F3" s="67" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
       <c r="I3" s="23"/>
-      <c r="J3" s="70" t="s">
+      <c r="J3" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="K3" s="70"/>
-      <c r="L3" s="70"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="63" t="e" vm="2">
+      <c r="N3" s="59" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="67" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="70" t="s">
+      <c r="J4" s="67" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
+      <c r="N4" s="59"/>
+      <c r="O4" s="59"/>
+      <c r="P4" s="59"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="64" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="61"/>
-      <c r="H5" s="61"/>
-      <c r="I5" s="61"/>
-      <c r="J5" s="61"/>
-      <c r="K5" s="61"/>
-      <c r="L5" s="69"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="66"/>
       <c r="M5" s="23"/>
-      <c r="N5" s="63"/>
-      <c r="O5" s="63"/>
-      <c r="P5" s="63"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
     </row>
     <row r="6" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="59"/>
-      <c r="D8" s="59" t="s">
+      <c r="C8" s="68"/>
+      <c r="D8" s="68" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="69" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="60"/>
-      <c r="D9" s="61" t="s">
+      <c r="C9" s="69"/>
+      <c r="D9" s="65" t="s">
         <v>184</v>
       </c>
-      <c r="E9" s="61"/>
-      <c r="F9" s="61"/>
+      <c r="E9" s="65"/>
+      <c r="F9" s="65"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="65" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61" t="s">
+      <c r="C10" s="65"/>
+      <c r="D10" s="65" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="61" t="s">
+      <c r="B11" s="65" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="62" t="s">
+      <c r="C11" s="65"/>
+      <c r="D11" s="70" t="s">
         <v>189</v>
       </c>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -5474,14 +5507,6 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/QA문서/QA.xlsx
+++ b/QA문서/QA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\newCapstone\QA문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BC16C8-E9A2-485F-9A0B-78EC65FE5BBB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDB7469-DC7C-4897-8CBE-EE37D8C63212}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12765" xr2:uid="{E8BC181F-28AA-4B30-BD92-43D69A4CDDA5}"/>
   </bookViews>
@@ -1270,57 +1270,69 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1339,23 +1351,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1900,36 +1900,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
     </row>
     <row r="2" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="M2" s="54"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
@@ -1942,17 +1942,17 @@
       <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="44"/>
-      <c r="K3" s="44"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
       <c r="L3" s="5" t="s">
         <v>59</v>
       </c>
@@ -1971,17 +1971,17 @@
       <c r="D4" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55" t="s">
         <v>53</v>
       </c>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
       <c r="L4" s="11" t="s">
         <v>172</v>
       </c>
@@ -1998,17 +1998,17 @@
       <c r="D5" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="55" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42" t="s">
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="55" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="55"/>
       <c r="L5" s="11" t="s">
         <v>172</v>
       </c>
@@ -2025,17 +2025,17 @@
       <c r="D6" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42" t="s">
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
       <c r="L6" s="11" t="s">
         <v>172</v>
       </c>
@@ -2052,17 +2052,17 @@
       <c r="D7" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
       <c r="H7" s="30"/>
-      <c r="I7" s="42" t="s">
+      <c r="I7" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
       <c r="L7" s="11" t="s">
         <v>172</v>
       </c>
@@ -2079,17 +2079,17 @@
       <c r="D8" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="55"/>
       <c r="L8" s="11" t="s">
         <v>172</v>
       </c>
@@ -2106,17 +2106,17 @@
       <c r="D9" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="55" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
       <c r="H9" s="30"/>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="55" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="55"/>
       <c r="L9" s="11" t="s">
         <v>172</v>
       </c>
@@ -2133,17 +2133,17 @@
       <c r="D10" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
       <c r="H10" s="30"/>
-      <c r="I10" s="42" t="s">
+      <c r="I10" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="55"/>
       <c r="L10" s="11" t="s">
         <v>172</v>
       </c>
@@ -2160,17 +2160,17 @@
       <c r="D11" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42" t="s">
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
       <c r="L11" s="11" t="s">
         <v>172</v>
       </c>
@@ -2187,17 +2187,17 @@
       <c r="D12" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42" t="s">
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
       <c r="L12" s="11" t="s">
         <v>62</v>
       </c>
@@ -2214,17 +2214,17 @@
       <c r="D13" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="55" t="s">
         <v>64</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42" t="s">
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55" t="s">
         <v>65</v>
       </c>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
+      <c r="J13" s="55"/>
+      <c r="K13" s="55"/>
       <c r="L13" s="11" t="s">
         <v>60</v>
       </c>
@@ -2241,17 +2241,17 @@
       <c r="D14" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42" t="s">
+      <c r="F14" s="55"/>
+      <c r="G14" s="55"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="55" t="s">
         <v>67</v>
       </c>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
+      <c r="J14" s="55"/>
+      <c r="K14" s="55"/>
       <c r="L14" s="11" t="s">
         <v>62</v>
       </c>
@@ -2268,17 +2268,17 @@
       <c r="D15" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="55" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42" t="s">
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55" t="s">
         <v>69</v>
       </c>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
       <c r="L15" s="11" t="s">
         <v>172</v>
       </c>
@@ -2295,17 +2295,17 @@
       <c r="D16" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="55" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
       <c r="L16" s="11" t="s">
         <v>172</v>
       </c>
@@ -2322,17 +2322,17 @@
       <c r="D17" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="55" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
       <c r="L17" s="11" t="s">
         <v>172</v>
       </c>
@@ -2349,17 +2349,17 @@
       <c r="D18" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="55" t="s">
         <v>156</v>
       </c>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42" t="s">
+      <c r="F18" s="55"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
+      <c r="J18" s="55"/>
+      <c r="K18" s="55"/>
       <c r="L18" s="11" t="s">
         <v>172</v>
       </c>
@@ -2376,17 +2376,17 @@
       <c r="D19" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="45" t="s">
+      <c r="E19" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45" t="s">
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52" t="s">
         <v>159</v>
       </c>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
       <c r="L19" s="11" t="s">
         <v>60</v>
       </c>
@@ -2403,17 +2403,17 @@
       <c r="D20" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="52" t="s">
         <v>160</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="45"/>
-      <c r="H20" s="45"/>
-      <c r="I20" s="45" t="s">
+      <c r="F20" s="52"/>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="45"/>
-      <c r="K20" s="45"/>
+      <c r="J20" s="52"/>
+      <c r="K20" s="52"/>
       <c r="L20" s="11" t="s">
         <v>60</v>
       </c>
@@ -2430,17 +2430,17 @@
       <c r="D21" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="52" t="s">
         <v>170</v>
       </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45" t="s">
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52" t="s">
         <v>171</v>
       </c>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
       <c r="L21" s="11" t="s">
         <v>172</v>
       </c>
@@ -2457,17 +2457,17 @@
       <c r="D22" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="52" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="45"/>
-      <c r="H22" s="45"/>
-      <c r="I22" s="45" t="s">
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52" t="s">
         <v>174</v>
       </c>
-      <c r="J22" s="45"/>
-      <c r="K22" s="45"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
       <c r="L22" s="11" t="s">
         <v>172</v>
       </c>
@@ -2484,17 +2484,17 @@
       <c r="D23" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="46" t="s">
+      <c r="E23" s="53" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="46"/>
-      <c r="G23" s="46"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="45" t="s">
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="J23" s="45"/>
-      <c r="K23" s="45"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
       <c r="L23" s="11" t="s">
         <v>60</v>
       </c>
@@ -2511,17 +2511,17 @@
       <c r="D24" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="53" t="s">
         <v>179</v>
       </c>
-      <c r="F24" s="46"/>
-      <c r="G24" s="46"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="45" t="s">
+      <c r="F24" s="53"/>
+      <c r="G24" s="53"/>
+      <c r="H24" s="53"/>
+      <c r="I24" s="52" t="s">
         <v>180</v>
       </c>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
       <c r="L24" s="11" t="s">
         <v>60</v>
       </c>
@@ -2538,17 +2538,17 @@
       <c r="D25" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="53" t="s">
         <v>181</v>
       </c>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="45" t="s">
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
       <c r="L25" s="11" t="s">
         <v>60</v>
       </c>
@@ -2565,17 +2565,17 @@
       <c r="D26" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="47" t="s">
+      <c r="E26" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47" t="s">
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
       <c r="L26" s="11" t="s">
         <v>172</v>
       </c>
@@ -2606,13 +2606,13 @@
       <c r="F27" s="50"/>
       <c r="G27" s="51"/>
       <c r="H27" s="38"/>
-      <c r="I27" s="53" t="s">
+      <c r="I27" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="J27" s="54"/>
-      <c r="K27" s="55"/>
+      <c r="J27" s="44"/>
+      <c r="K27" s="45"/>
       <c r="L27" s="11" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="M27" s="12" t="s">
         <v>209</v>
@@ -2635,11 +2635,11 @@
       <c r="F28" s="39"/>
       <c r="G28" s="39"/>
       <c r="H28" s="39"/>
-      <c r="I28" s="53" t="s">
+      <c r="I28" s="43" t="s">
         <v>196</v>
       </c>
-      <c r="J28" s="54"/>
-      <c r="K28" s="55"/>
+      <c r="J28" s="44"/>
+      <c r="K28" s="45"/>
       <c r="L28" s="11" t="s">
         <v>172</v>
       </c>
@@ -2664,11 +2664,11 @@
       <c r="F29" s="50"/>
       <c r="G29" s="51"/>
       <c r="H29" s="38"/>
-      <c r="I29" s="53" t="s">
+      <c r="I29" s="43" t="s">
         <v>199</v>
       </c>
-      <c r="J29" s="54"/>
-      <c r="K29" s="55"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="45"/>
       <c r="L29" s="11" t="s">
         <v>172</v>
       </c>
@@ -2687,17 +2687,17 @@
       <c r="D30" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="E30" s="47" t="s">
+      <c r="E30" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="56" t="s">
+      <c r="F30" s="48"/>
+      <c r="G30" s="48"/>
+      <c r="H30" s="48"/>
+      <c r="I30" s="46" t="s">
         <v>204</v>
       </c>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="46"/>
       <c r="L30" s="11" t="s">
         <v>172</v>
       </c>
@@ -2712,13 +2712,13 @@
       </c>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
-      <c r="K31" s="48"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
       <c r="L31" s="11" t="s">
         <v>60</v>
       </c>
@@ -2731,13 +2731,13 @@
       </c>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="48"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="48"/>
-      <c r="J32" s="48"/>
-      <c r="K32" s="48"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
       <c r="L32" s="11" t="s">
         <v>60</v>
       </c>
@@ -2750,13 +2750,13 @@
       </c>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="48"/>
-      <c r="K33" s="48"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
       <c r="L33" s="11" t="s">
         <v>60</v>
       </c>
@@ -2769,13 +2769,13 @@
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
-      <c r="G34" s="48"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="48"/>
-      <c r="J34" s="48"/>
-      <c r="K34" s="48"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
       <c r="L34" s="11" t="s">
         <v>60</v>
       </c>
@@ -2788,13 +2788,13 @@
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="48"/>
-      <c r="J35" s="48"/>
-      <c r="K35" s="48"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
       <c r="L35" s="11" t="s">
         <v>60</v>
       </c>
@@ -2807,13 +2807,13 @@
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
       <c r="L36" s="11" t="s">
         <v>60</v>
       </c>
@@ -2826,13 +2826,13 @@
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="48"/>
-      <c r="J37" s="48"/>
-      <c r="K37" s="48"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
       <c r="L37" s="11" t="s">
         <v>60</v>
       </c>
@@ -2845,13 +2845,13 @@
       </c>
       <c r="C38" s="11"/>
       <c r="D38" s="11"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="48"/>
-      <c r="J38" s="48"/>
-      <c r="K38" s="48"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
       <c r="L38" s="11" t="s">
         <v>60</v>
       </c>
@@ -2864,13 +2864,13 @@
       </c>
       <c r="C39" s="11"/>
       <c r="D39" s="11"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="48"/>
-      <c r="J39" s="48"/>
-      <c r="K39" s="48"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42"/>
       <c r="L39" s="11" t="s">
         <v>60</v>
       </c>
@@ -2883,13 +2883,13 @@
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="48"/>
-      <c r="J40" s="48"/>
-      <c r="K40" s="48"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
       <c r="L40" s="11" t="s">
         <v>60</v>
       </c>
@@ -2902,13 +2902,13 @@
       </c>
       <c r="C41" s="11"/>
       <c r="D41" s="11"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="48"/>
-      <c r="K41" s="48"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
       <c r="L41" s="11" t="s">
         <v>60</v>
       </c>
@@ -2921,13 +2921,13 @@
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="48"/>
-      <c r="K42" s="48"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
       <c r="L42" s="11" t="s">
         <v>60</v>
       </c>
@@ -2940,13 +2940,13 @@
       </c>
       <c r="C43" s="11"/>
       <c r="D43" s="11"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
       <c r="L43" s="11" t="s">
         <v>60</v>
       </c>
@@ -2959,13 +2959,13 @@
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="48"/>
-      <c r="K44" s="48"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
       <c r="L44" s="11" t="s">
         <v>60</v>
       </c>
@@ -2978,13 +2978,13 @@
       </c>
       <c r="C45" s="11"/>
       <c r="D45" s="11"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="48"/>
-      <c r="K45" s="48"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
       <c r="L45" s="11" t="s">
         <v>60</v>
       </c>
@@ -2997,13 +2997,13 @@
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="48"/>
-      <c r="K46" s="48"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
       <c r="L46" s="11" t="s">
         <v>60</v>
       </c>
@@ -3016,13 +3016,13 @@
       </c>
       <c r="C47" s="11"/>
       <c r="D47" s="11"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="48"/>
-      <c r="K47" s="48"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
       <c r="L47" s="11" t="s">
         <v>60</v>
       </c>
@@ -3035,13 +3035,13 @@
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="48"/>
-      <c r="K48" s="48"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
       <c r="L48" s="11" t="s">
         <v>60</v>
       </c>
@@ -3054,13 +3054,13 @@
       </c>
       <c r="C49" s="11"/>
       <c r="D49" s="11"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
       <c r="L49" s="11" t="s">
         <v>60</v>
       </c>
@@ -3073,13 +3073,13 @@
       </c>
       <c r="C50" s="11"/>
       <c r="D50" s="11"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="48"/>
-      <c r="K50" s="48"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
       <c r="L50" s="11" t="s">
         <v>60</v>
       </c>
@@ -3092,13 +3092,13 @@
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="48"/>
-      <c r="K51" s="48"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
       <c r="L51" s="11" t="s">
         <v>60</v>
       </c>
@@ -3111,13 +3111,13 @@
       </c>
       <c r="C52" s="11"/>
       <c r="D52" s="11"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="48"/>
-      <c r="K52" s="48"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
       <c r="L52" s="11" t="s">
         <v>60</v>
       </c>
@@ -3130,13 +3130,13 @@
       </c>
       <c r="C53" s="11"/>
       <c r="D53" s="11"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="48"/>
-      <c r="K53" s="48"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
       <c r="L53" s="11" t="s">
         <v>60</v>
       </c>
@@ -3149,13 +3149,13 @@
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="J54" s="48"/>
-      <c r="K54" s="48"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
       <c r="L54" s="11" t="s">
         <v>60</v>
       </c>
@@ -3168,13 +3168,13 @@
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
-      <c r="G55" s="48"/>
-      <c r="H55" s="48"/>
-      <c r="I55" s="48"/>
-      <c r="J55" s="48"/>
-      <c r="K55" s="48"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
       <c r="L55" s="11" t="s">
         <v>60</v>
       </c>
@@ -3187,13 +3187,13 @@
       </c>
       <c r="C56" s="11"/>
       <c r="D56" s="11"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
-      <c r="G56" s="48"/>
-      <c r="H56" s="48"/>
-      <c r="I56" s="48"/>
-      <c r="J56" s="48"/>
-      <c r="K56" s="48"/>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="42"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
       <c r="L56" s="11" t="s">
         <v>60</v>
       </c>
@@ -3206,13 +3206,13 @@
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
-      <c r="G57" s="48"/>
-      <c r="H57" s="48"/>
-      <c r="I57" s="48"/>
-      <c r="J57" s="48"/>
-      <c r="K57" s="48"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="42"/>
+      <c r="I57" s="42"/>
+      <c r="J57" s="42"/>
+      <c r="K57" s="42"/>
       <c r="L57" s="11" t="s">
         <v>60</v>
       </c>
@@ -3225,13 +3225,13 @@
       </c>
       <c r="C58" s="11"/>
       <c r="D58" s="11"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
-      <c r="G58" s="48"/>
-      <c r="H58" s="48"/>
-      <c r="I58" s="48"/>
-      <c r="J58" s="48"/>
-      <c r="K58" s="48"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="42"/>
+      <c r="I58" s="42"/>
+      <c r="J58" s="42"/>
+      <c r="K58" s="42"/>
       <c r="L58" s="11" t="s">
         <v>60</v>
       </c>
@@ -3244,13 +3244,13 @@
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="42"/>
+      <c r="I59" s="42"/>
+      <c r="J59" s="42"/>
+      <c r="K59" s="42"/>
       <c r="L59" s="11" t="s">
         <v>60</v>
       </c>
@@ -3263,13 +3263,13 @@
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11"/>
-      <c r="E60" s="48"/>
-      <c r="F60" s="48"/>
-      <c r="G60" s="48"/>
-      <c r="H60" s="48"/>
-      <c r="I60" s="48"/>
-      <c r="J60" s="48"/>
-      <c r="K60" s="48"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
+      <c r="I60" s="42"/>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
       <c r="L60" s="11" t="s">
         <v>60</v>
       </c>
@@ -3282,13 +3282,13 @@
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="48"/>
-      <c r="H61" s="48"/>
-      <c r="I61" s="48"/>
-      <c r="J61" s="48"/>
-      <c r="K61" s="48"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="42"/>
+      <c r="H61" s="42"/>
+      <c r="I61" s="42"/>
+      <c r="J61" s="42"/>
+      <c r="K61" s="42"/>
       <c r="L61" s="11" t="s">
         <v>60</v>
       </c>
@@ -3301,13 +3301,13 @@
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
-      <c r="E62" s="48"/>
-      <c r="F62" s="48"/>
-      <c r="G62" s="48"/>
-      <c r="H62" s="48"/>
-      <c r="I62" s="48"/>
-      <c r="J62" s="48"/>
-      <c r="K62" s="48"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="42"/>
+      <c r="I62" s="42"/>
+      <c r="J62" s="42"/>
+      <c r="K62" s="42"/>
       <c r="L62" s="11" t="s">
         <v>60</v>
       </c>
@@ -3320,13 +3320,13 @@
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
-      <c r="E63" s="48"/>
-      <c r="F63" s="48"/>
-      <c r="G63" s="48"/>
-      <c r="H63" s="48"/>
-      <c r="I63" s="48"/>
-      <c r="J63" s="48"/>
-      <c r="K63" s="48"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+      <c r="I63" s="42"/>
+      <c r="J63" s="42"/>
+      <c r="K63" s="42"/>
       <c r="L63" s="11" t="s">
         <v>60</v>
       </c>
@@ -3339,13 +3339,13 @@
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="48"/>
-      <c r="G64" s="48"/>
-      <c r="H64" s="48"/>
-      <c r="I64" s="48"/>
-      <c r="J64" s="48"/>
-      <c r="K64" s="48"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+      <c r="I64" s="42"/>
+      <c r="J64" s="42"/>
+      <c r="K64" s="42"/>
       <c r="L64" s="11" t="s">
         <v>60</v>
       </c>
@@ -3358,13 +3358,13 @@
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
-      <c r="E65" s="48"/>
-      <c r="F65" s="48"/>
-      <c r="G65" s="48"/>
-      <c r="H65" s="48"/>
-      <c r="I65" s="48"/>
-      <c r="J65" s="48"/>
-      <c r="K65" s="48"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="42"/>
+      <c r="I65" s="42"/>
+      <c r="J65" s="42"/>
+      <c r="K65" s="42"/>
       <c r="L65" s="11" t="s">
         <v>60</v>
       </c>
@@ -3377,13 +3377,13 @@
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
-      <c r="E66" s="48"/>
-      <c r="F66" s="48"/>
-      <c r="G66" s="48"/>
-      <c r="H66" s="48"/>
-      <c r="I66" s="48"/>
-      <c r="J66" s="48"/>
-      <c r="K66" s="48"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="42"/>
+      <c r="K66" s="42"/>
       <c r="L66" s="11" t="s">
         <v>60</v>
       </c>
@@ -3396,13 +3396,13 @@
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11"/>
-      <c r="E67" s="52"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="52"/>
-      <c r="H67" s="52"/>
-      <c r="I67" s="48"/>
-      <c r="J67" s="48"/>
-      <c r="K67" s="48"/>
+      <c r="E67" s="47"/>
+      <c r="F67" s="47"/>
+      <c r="G67" s="47"/>
+      <c r="H67" s="47"/>
+      <c r="I67" s="42"/>
+      <c r="J67" s="42"/>
+      <c r="K67" s="42"/>
       <c r="L67" s="11" t="s">
         <v>60</v>
       </c>
@@ -3415,13 +3415,13 @@
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
-      <c r="I68" s="48"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="48"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+      <c r="I68" s="42"/>
+      <c r="J68" s="42"/>
+      <c r="K68" s="42"/>
       <c r="L68" s="11" t="s">
         <v>60</v>
       </c>
@@ -3434,13 +3434,13 @@
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
-      <c r="E69" s="48"/>
-      <c r="F69" s="48"/>
-      <c r="G69" s="48"/>
-      <c r="H69" s="48"/>
-      <c r="I69" s="48"/>
-      <c r="J69" s="48"/>
-      <c r="K69" s="48"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+      <c r="I69" s="42"/>
+      <c r="J69" s="42"/>
+      <c r="K69" s="42"/>
       <c r="L69" s="11" t="s">
         <v>60</v>
       </c>
@@ -3453,13 +3453,13 @@
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
-      <c r="E70" s="48"/>
-      <c r="F70" s="48"/>
-      <c r="G70" s="48"/>
-      <c r="H70" s="48"/>
-      <c r="I70" s="48"/>
-      <c r="J70" s="48"/>
-      <c r="K70" s="48"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+      <c r="I70" s="42"/>
+      <c r="J70" s="42"/>
+      <c r="K70" s="42"/>
       <c r="L70" s="11" t="s">
         <v>60</v>
       </c>
@@ -3472,13 +3472,13 @@
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
-      <c r="E71" s="48"/>
-      <c r="F71" s="48"/>
-      <c r="G71" s="48"/>
-      <c r="H71" s="48"/>
-      <c r="I71" s="48"/>
-      <c r="J71" s="48"/>
-      <c r="K71" s="48"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="42"/>
+      <c r="I71" s="42"/>
+      <c r="J71" s="42"/>
+      <c r="K71" s="42"/>
       <c r="L71" s="11" t="s">
         <v>60</v>
       </c>
@@ -3491,13 +3491,13 @@
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
-      <c r="E72" s="48"/>
-      <c r="F72" s="48"/>
-      <c r="G72" s="48"/>
-      <c r="H72" s="48"/>
-      <c r="I72" s="48"/>
-      <c r="J72" s="48"/>
-      <c r="K72" s="48"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="42"/>
+      <c r="K72" s="42"/>
       <c r="L72" s="11" t="s">
         <v>60</v>
       </c>
@@ -3510,13 +3510,13 @@
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
-      <c r="E73" s="48"/>
-      <c r="F73" s="48"/>
-      <c r="G73" s="48"/>
-      <c r="H73" s="48"/>
-      <c r="I73" s="48"/>
-      <c r="J73" s="48"/>
-      <c r="K73" s="48"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="42"/>
+      <c r="I73" s="42"/>
+      <c r="J73" s="42"/>
+      <c r="K73" s="42"/>
       <c r="L73" s="11" t="s">
         <v>60</v>
       </c>
@@ -3529,13 +3529,13 @@
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="48"/>
-      <c r="G74" s="48"/>
-      <c r="H74" s="48"/>
-      <c r="I74" s="48"/>
-      <c r="J74" s="48"/>
-      <c r="K74" s="48"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="42"/>
+      <c r="I74" s="42"/>
+      <c r="J74" s="42"/>
+      <c r="K74" s="42"/>
       <c r="L74" s="11" t="s">
         <v>60</v>
       </c>
@@ -3548,13 +3548,13 @@
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11"/>
-      <c r="E75" s="48"/>
-      <c r="F75" s="48"/>
-      <c r="G75" s="48"/>
-      <c r="H75" s="48"/>
-      <c r="I75" s="48"/>
-      <c r="J75" s="48"/>
-      <c r="K75" s="48"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="42"/>
+      <c r="H75" s="42"/>
+      <c r="I75" s="42"/>
+      <c r="J75" s="42"/>
+      <c r="K75" s="42"/>
       <c r="L75" s="11" t="s">
         <v>60</v>
       </c>
@@ -3567,13 +3567,13 @@
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
-      <c r="E76" s="48"/>
-      <c r="F76" s="48"/>
-      <c r="G76" s="48"/>
-      <c r="H76" s="48"/>
-      <c r="I76" s="48"/>
-      <c r="J76" s="48"/>
-      <c r="K76" s="48"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="42"/>
+      <c r="I76" s="42"/>
+      <c r="J76" s="42"/>
+      <c r="K76" s="42"/>
       <c r="L76" s="11" t="s">
         <v>60</v>
       </c>
@@ -3586,13 +3586,13 @@
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11"/>
-      <c r="E77" s="48"/>
-      <c r="F77" s="48"/>
-      <c r="G77" s="48"/>
-      <c r="H77" s="48"/>
-      <c r="I77" s="48"/>
-      <c r="J77" s="48"/>
-      <c r="K77" s="48"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="42"/>
+      <c r="H77" s="42"/>
+      <c r="I77" s="42"/>
+      <c r="J77" s="42"/>
+      <c r="K77" s="42"/>
       <c r="L77" s="11" t="s">
         <v>60</v>
       </c>
@@ -3605,13 +3605,13 @@
       </c>
       <c r="C78" s="11"/>
       <c r="D78" s="11"/>
-      <c r="E78" s="48"/>
-      <c r="F78" s="48"/>
-      <c r="G78" s="48"/>
-      <c r="H78" s="48"/>
-      <c r="I78" s="48"/>
-      <c r="J78" s="48"/>
-      <c r="K78" s="48"/>
+      <c r="E78" s="42"/>
+      <c r="F78" s="42"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="42"/>
+      <c r="I78" s="42"/>
+      <c r="J78" s="42"/>
+      <c r="K78" s="42"/>
       <c r="L78" s="11" t="s">
         <v>60</v>
       </c>
@@ -3624,13 +3624,13 @@
       </c>
       <c r="C79" s="11"/>
       <c r="D79" s="11"/>
-      <c r="E79" s="48"/>
-      <c r="F79" s="48"/>
-      <c r="G79" s="48"/>
-      <c r="H79" s="48"/>
-      <c r="I79" s="48"/>
-      <c r="J79" s="48"/>
-      <c r="K79" s="48"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="42"/>
+      <c r="I79" s="42"/>
+      <c r="J79" s="42"/>
+      <c r="K79" s="42"/>
       <c r="L79" s="11" t="s">
         <v>60</v>
       </c>
@@ -3643,13 +3643,13 @@
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11"/>
-      <c r="E80" s="48"/>
-      <c r="F80" s="48"/>
-      <c r="G80" s="48"/>
-      <c r="H80" s="48"/>
-      <c r="I80" s="48"/>
-      <c r="J80" s="48"/>
-      <c r="K80" s="48"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="42"/>
+      <c r="K80" s="42"/>
       <c r="L80" s="11" t="s">
         <v>60</v>
       </c>
@@ -3662,13 +3662,13 @@
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11"/>
-      <c r="E81" s="48"/>
-      <c r="F81" s="48"/>
-      <c r="G81" s="48"/>
-      <c r="H81" s="48"/>
-      <c r="I81" s="48"/>
-      <c r="J81" s="48"/>
-      <c r="K81" s="48"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="42"/>
+      <c r="I81" s="42"/>
+      <c r="J81" s="42"/>
+      <c r="K81" s="42"/>
       <c r="L81" s="11" t="s">
         <v>60</v>
       </c>
@@ -3681,13 +3681,13 @@
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11"/>
-      <c r="E82" s="48"/>
-      <c r="F82" s="48"/>
-      <c r="G82" s="48"/>
-      <c r="H82" s="48"/>
-      <c r="I82" s="48"/>
-      <c r="J82" s="48"/>
-      <c r="K82" s="48"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="42"/>
+      <c r="I82" s="42"/>
+      <c r="J82" s="42"/>
+      <c r="K82" s="42"/>
       <c r="L82" s="11" t="s">
         <v>60</v>
       </c>
@@ -3700,13 +3700,13 @@
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11"/>
-      <c r="E83" s="48"/>
-      <c r="F83" s="48"/>
-      <c r="G83" s="48"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="48"/>
-      <c r="J83" s="48"/>
-      <c r="K83" s="48"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="42"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="42"/>
+      <c r="I83" s="42"/>
+      <c r="J83" s="42"/>
+      <c r="K83" s="42"/>
       <c r="L83" s="11" t="s">
         <v>60</v>
       </c>
@@ -3719,13 +3719,13 @@
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11"/>
-      <c r="E84" s="48"/>
-      <c r="F84" s="48"/>
-      <c r="G84" s="48"/>
-      <c r="H84" s="48"/>
-      <c r="I84" s="48"/>
-      <c r="J84" s="48"/>
-      <c r="K84" s="48"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="42"/>
+      <c r="H84" s="42"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="42"/>
+      <c r="K84" s="42"/>
       <c r="L84" s="11" t="s">
         <v>60</v>
       </c>
@@ -3738,13 +3738,13 @@
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11"/>
-      <c r="E85" s="48"/>
-      <c r="F85" s="48"/>
-      <c r="G85" s="48"/>
-      <c r="H85" s="48"/>
-      <c r="I85" s="48"/>
-      <c r="J85" s="48"/>
-      <c r="K85" s="48"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+      <c r="I85" s="42"/>
+      <c r="J85" s="42"/>
+      <c r="K85" s="42"/>
       <c r="L85" s="11" t="s">
         <v>60</v>
       </c>
@@ -3757,13 +3757,13 @@
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11"/>
-      <c r="E86" s="48"/>
-      <c r="F86" s="48"/>
-      <c r="G86" s="48"/>
-      <c r="H86" s="48"/>
-      <c r="I86" s="48"/>
-      <c r="J86" s="48"/>
-      <c r="K86" s="48"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+      <c r="I86" s="42"/>
+      <c r="J86" s="42"/>
+      <c r="K86" s="42"/>
       <c r="L86" s="11" t="s">
         <v>60</v>
       </c>
@@ -3776,13 +3776,13 @@
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
-      <c r="E87" s="48"/>
-      <c r="F87" s="48"/>
-      <c r="G87" s="48"/>
-      <c r="H87" s="48"/>
-      <c r="I87" s="48"/>
-      <c r="J87" s="48"/>
-      <c r="K87" s="48"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="42"/>
+      <c r="G87" s="42"/>
+      <c r="H87" s="42"/>
+      <c r="I87" s="42"/>
+      <c r="J87" s="42"/>
+      <c r="K87" s="42"/>
       <c r="L87" s="11" t="s">
         <v>60</v>
       </c>
@@ -3795,13 +3795,13 @@
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
-      <c r="J88" s="48"/>
-      <c r="K88" s="48"/>
+      <c r="E88" s="42"/>
+      <c r="F88" s="42"/>
+      <c r="G88" s="42"/>
+      <c r="H88" s="42"/>
+      <c r="I88" s="42"/>
+      <c r="J88" s="42"/>
+      <c r="K88" s="42"/>
       <c r="L88" s="11" t="s">
         <v>60</v>
       </c>
@@ -3814,13 +3814,13 @@
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
-      <c r="E89" s="48"/>
-      <c r="F89" s="48"/>
-      <c r="G89" s="48"/>
-      <c r="H89" s="48"/>
-      <c r="I89" s="48"/>
-      <c r="J89" s="48"/>
-      <c r="K89" s="48"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="42"/>
+      <c r="H89" s="42"/>
+      <c r="I89" s="42"/>
+      <c r="J89" s="42"/>
+      <c r="K89" s="42"/>
       <c r="L89" s="11" t="s">
         <v>60</v>
       </c>
@@ -3833,13 +3833,13 @@
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
-      <c r="E90" s="48"/>
-      <c r="F90" s="48"/>
-      <c r="G90" s="48"/>
-      <c r="H90" s="48"/>
-      <c r="I90" s="48"/>
-      <c r="J90" s="48"/>
-      <c r="K90" s="48"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="42"/>
+      <c r="H90" s="42"/>
+      <c r="I90" s="42"/>
+      <c r="J90" s="42"/>
+      <c r="K90" s="42"/>
       <c r="L90" s="11" t="s">
         <v>60</v>
       </c>
@@ -3852,13 +3852,13 @@
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
-      <c r="E91" s="48"/>
-      <c r="F91" s="48"/>
-      <c r="G91" s="48"/>
-      <c r="H91" s="48"/>
-      <c r="I91" s="48"/>
-      <c r="J91" s="48"/>
-      <c r="K91" s="48"/>
+      <c r="E91" s="42"/>
+      <c r="F91" s="42"/>
+      <c r="G91" s="42"/>
+      <c r="H91" s="42"/>
+      <c r="I91" s="42"/>
+      <c r="J91" s="42"/>
+      <c r="K91" s="42"/>
       <c r="L91" s="11" t="s">
         <v>60</v>
       </c>
@@ -3871,13 +3871,13 @@
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11"/>
-      <c r="E92" s="48"/>
-      <c r="F92" s="48"/>
-      <c r="G92" s="48"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="48"/>
-      <c r="J92" s="48"/>
-      <c r="K92" s="48"/>
+      <c r="E92" s="42"/>
+      <c r="F92" s="42"/>
+      <c r="G92" s="42"/>
+      <c r="H92" s="42"/>
+      <c r="I92" s="42"/>
+      <c r="J92" s="42"/>
+      <c r="K92" s="42"/>
       <c r="L92" s="11" t="s">
         <v>60</v>
       </c>
@@ -3890,13 +3890,13 @@
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11"/>
-      <c r="E93" s="48"/>
-      <c r="F93" s="48"/>
-      <c r="G93" s="48"/>
-      <c r="H93" s="48"/>
-      <c r="I93" s="48"/>
-      <c r="J93" s="48"/>
-      <c r="K93" s="48"/>
+      <c r="E93" s="42"/>
+      <c r="F93" s="42"/>
+      <c r="G93" s="42"/>
+      <c r="H93" s="42"/>
+      <c r="I93" s="42"/>
+      <c r="J93" s="42"/>
+      <c r="K93" s="42"/>
       <c r="L93" s="11" t="s">
         <v>60</v>
       </c>
@@ -3909,13 +3909,13 @@
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
-      <c r="E94" s="48"/>
-      <c r="F94" s="48"/>
-      <c r="G94" s="48"/>
-      <c r="H94" s="48"/>
-      <c r="I94" s="48"/>
-      <c r="J94" s="48"/>
-      <c r="K94" s="48"/>
+      <c r="E94" s="42"/>
+      <c r="F94" s="42"/>
+      <c r="G94" s="42"/>
+      <c r="H94" s="42"/>
+      <c r="I94" s="42"/>
+      <c r="J94" s="42"/>
+      <c r="K94" s="42"/>
       <c r="L94" s="11" t="s">
         <v>60</v>
       </c>
@@ -3928,13 +3928,13 @@
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
-      <c r="E95" s="48"/>
-      <c r="F95" s="48"/>
-      <c r="G95" s="48"/>
-      <c r="H95" s="48"/>
-      <c r="I95" s="48"/>
-      <c r="J95" s="48"/>
-      <c r="K95" s="48"/>
+      <c r="E95" s="42"/>
+      <c r="F95" s="42"/>
+      <c r="G95" s="42"/>
+      <c r="H95" s="42"/>
+      <c r="I95" s="42"/>
+      <c r="J95" s="42"/>
+      <c r="K95" s="42"/>
       <c r="L95" s="11" t="s">
         <v>60</v>
       </c>
@@ -3947,13 +3947,13 @@
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
-      <c r="E96" s="48"/>
-      <c r="F96" s="48"/>
-      <c r="G96" s="48"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="48"/>
-      <c r="J96" s="48"/>
-      <c r="K96" s="48"/>
+      <c r="E96" s="42"/>
+      <c r="F96" s="42"/>
+      <c r="G96" s="42"/>
+      <c r="H96" s="42"/>
+      <c r="I96" s="42"/>
+      <c r="J96" s="42"/>
+      <c r="K96" s="42"/>
       <c r="L96" s="11" t="s">
         <v>60</v>
       </c>
@@ -3966,13 +3966,13 @@
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11"/>
-      <c r="E97" s="48"/>
-      <c r="F97" s="48"/>
-      <c r="G97" s="48"/>
-      <c r="H97" s="48"/>
-      <c r="I97" s="48"/>
-      <c r="J97" s="48"/>
-      <c r="K97" s="48"/>
+      <c r="E97" s="42"/>
+      <c r="F97" s="42"/>
+      <c r="G97" s="42"/>
+      <c r="H97" s="42"/>
+      <c r="I97" s="42"/>
+      <c r="J97" s="42"/>
+      <c r="K97" s="42"/>
       <c r="L97" s="11" t="s">
         <v>60</v>
       </c>
@@ -3985,13 +3985,13 @@
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
+      <c r="E98" s="42"/>
+      <c r="F98" s="42"/>
+      <c r="G98" s="42"/>
+      <c r="H98" s="42"/>
+      <c r="I98" s="42"/>
+      <c r="J98" s="42"/>
+      <c r="K98" s="42"/>
       <c r="L98" s="11" t="s">
         <v>60</v>
       </c>
@@ -4004,13 +4004,13 @@
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
-      <c r="E99" s="48"/>
-      <c r="F99" s="48"/>
-      <c r="G99" s="48"/>
-      <c r="H99" s="48"/>
-      <c r="I99" s="48"/>
-      <c r="J99" s="48"/>
-      <c r="K99" s="48"/>
+      <c r="E99" s="42"/>
+      <c r="F99" s="42"/>
+      <c r="G99" s="42"/>
+      <c r="H99" s="42"/>
+      <c r="I99" s="42"/>
+      <c r="J99" s="42"/>
+      <c r="K99" s="42"/>
       <c r="L99" s="11" t="s">
         <v>60</v>
       </c>
@@ -4023,13 +4023,13 @@
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
-      <c r="E100" s="48"/>
-      <c r="F100" s="48"/>
-      <c r="G100" s="48"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="48"/>
-      <c r="J100" s="48"/>
-      <c r="K100" s="48"/>
+      <c r="E100" s="42"/>
+      <c r="F100" s="42"/>
+      <c r="G100" s="42"/>
+      <c r="H100" s="42"/>
+      <c r="I100" s="42"/>
+      <c r="J100" s="42"/>
+      <c r="K100" s="42"/>
       <c r="L100" s="11" t="s">
         <v>60</v>
       </c>
@@ -4037,50 +4037,134 @@
     </row>
   </sheetData>
   <mergeCells count="196">
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I77:K77"/>
-    <mergeCell ref="I78:K78"/>
-    <mergeCell ref="I79:K79"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I72:K72"/>
-    <mergeCell ref="I73:K73"/>
-    <mergeCell ref="I74:K74"/>
-    <mergeCell ref="I75:K75"/>
-    <mergeCell ref="I76:K76"/>
-    <mergeCell ref="I67:K67"/>
-    <mergeCell ref="I68:K68"/>
-    <mergeCell ref="I69:K69"/>
-    <mergeCell ref="I70:K70"/>
-    <mergeCell ref="I71:K71"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I65:K65"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I57:K57"/>
-    <mergeCell ref="I58:K58"/>
-    <mergeCell ref="I59:K59"/>
-    <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I61:K61"/>
-    <mergeCell ref="I27:K27"/>
-    <mergeCell ref="I29:K29"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="I42:K42"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
-    <mergeCell ref="I45:K45"/>
-    <mergeCell ref="I37:K37"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I41:K41"/>
-    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="E14:H14"/>
+    <mergeCell ref="I14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="A1:M2"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="E12:H12"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="E13:H13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="E23:H23"/>
+    <mergeCell ref="E24:H24"/>
+    <mergeCell ref="E25:H25"/>
+    <mergeCell ref="E26:H26"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="E32:H32"/>
+    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E34:H34"/>
+    <mergeCell ref="E35:H35"/>
+    <mergeCell ref="E36:H36"/>
+    <mergeCell ref="E30:H30"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E42:H42"/>
+    <mergeCell ref="E43:H43"/>
+    <mergeCell ref="E44:H44"/>
+    <mergeCell ref="E45:H45"/>
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E37:H37"/>
+    <mergeCell ref="E38:H38"/>
+    <mergeCell ref="E39:H39"/>
+    <mergeCell ref="E40:H40"/>
+    <mergeCell ref="E41:H41"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="E53:H53"/>
+    <mergeCell ref="E54:H54"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="E56:H56"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="E49:H49"/>
+    <mergeCell ref="E50:H50"/>
+    <mergeCell ref="E51:H51"/>
+    <mergeCell ref="E62:H62"/>
+    <mergeCell ref="E63:H63"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="E65:H65"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="E58:H58"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="E60:H60"/>
+    <mergeCell ref="E61:H61"/>
+    <mergeCell ref="E72:H72"/>
+    <mergeCell ref="E73:H73"/>
+    <mergeCell ref="E74:H74"/>
+    <mergeCell ref="E75:H75"/>
+    <mergeCell ref="E76:H76"/>
+    <mergeCell ref="E67:H67"/>
+    <mergeCell ref="E68:H68"/>
+    <mergeCell ref="E69:H69"/>
+    <mergeCell ref="E70:H70"/>
+    <mergeCell ref="E71:H71"/>
+    <mergeCell ref="E82:H82"/>
+    <mergeCell ref="E83:H83"/>
+    <mergeCell ref="E84:H84"/>
+    <mergeCell ref="E85:H85"/>
+    <mergeCell ref="E86:H86"/>
+    <mergeCell ref="E77:H77"/>
+    <mergeCell ref="E78:H78"/>
+    <mergeCell ref="E79:H79"/>
+    <mergeCell ref="E80:H80"/>
+    <mergeCell ref="E81:H81"/>
+    <mergeCell ref="E92:H92"/>
+    <mergeCell ref="E93:H93"/>
+    <mergeCell ref="E94:H94"/>
+    <mergeCell ref="E95:H95"/>
+    <mergeCell ref="E96:H96"/>
+    <mergeCell ref="E87:H87"/>
+    <mergeCell ref="E88:H88"/>
+    <mergeCell ref="E89:H89"/>
+    <mergeCell ref="E90:H90"/>
+    <mergeCell ref="E91:H91"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="E97:H97"/>
+    <mergeCell ref="E98:H98"/>
+    <mergeCell ref="E99:H99"/>
+    <mergeCell ref="E100:H100"/>
     <mergeCell ref="I94:K94"/>
     <mergeCell ref="I93:K93"/>
     <mergeCell ref="I92:K92"/>
@@ -4105,134 +4189,50 @@
     <mergeCell ref="I49:K49"/>
     <mergeCell ref="I50:K50"/>
     <mergeCell ref="I51:K51"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="E97:H97"/>
-    <mergeCell ref="E98:H98"/>
-    <mergeCell ref="E99:H99"/>
-    <mergeCell ref="E100:H100"/>
-    <mergeCell ref="E92:H92"/>
-    <mergeCell ref="E93:H93"/>
-    <mergeCell ref="E94:H94"/>
-    <mergeCell ref="E95:H95"/>
-    <mergeCell ref="E96:H96"/>
-    <mergeCell ref="E87:H87"/>
-    <mergeCell ref="E88:H88"/>
-    <mergeCell ref="E89:H89"/>
-    <mergeCell ref="E90:H90"/>
-    <mergeCell ref="E91:H91"/>
-    <mergeCell ref="E82:H82"/>
-    <mergeCell ref="E83:H83"/>
-    <mergeCell ref="E84:H84"/>
-    <mergeCell ref="E85:H85"/>
-    <mergeCell ref="E86:H86"/>
-    <mergeCell ref="E77:H77"/>
-    <mergeCell ref="E78:H78"/>
-    <mergeCell ref="E79:H79"/>
-    <mergeCell ref="E80:H80"/>
-    <mergeCell ref="E81:H81"/>
-    <mergeCell ref="E72:H72"/>
-    <mergeCell ref="E73:H73"/>
-    <mergeCell ref="E74:H74"/>
-    <mergeCell ref="E75:H75"/>
-    <mergeCell ref="E76:H76"/>
-    <mergeCell ref="E67:H67"/>
-    <mergeCell ref="E68:H68"/>
-    <mergeCell ref="E69:H69"/>
-    <mergeCell ref="E70:H70"/>
-    <mergeCell ref="E71:H71"/>
-    <mergeCell ref="E62:H62"/>
-    <mergeCell ref="E63:H63"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="E65:H65"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="E58:H58"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="E60:H60"/>
-    <mergeCell ref="E61:H61"/>
-    <mergeCell ref="E52:H52"/>
-    <mergeCell ref="E53:H53"/>
-    <mergeCell ref="E54:H54"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="E56:H56"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="E49:H49"/>
-    <mergeCell ref="E50:H50"/>
-    <mergeCell ref="E51:H51"/>
-    <mergeCell ref="E42:H42"/>
-    <mergeCell ref="E43:H43"/>
-    <mergeCell ref="E44:H44"/>
-    <mergeCell ref="E45:H45"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E37:H37"/>
-    <mergeCell ref="E38:H38"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E40:H40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="E32:H32"/>
-    <mergeCell ref="E33:H33"/>
-    <mergeCell ref="E34:H34"/>
-    <mergeCell ref="E35:H35"/>
-    <mergeCell ref="E36:H36"/>
-    <mergeCell ref="E30:H30"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="E29:G29"/>
-    <mergeCell ref="E27:G27"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E23:H23"/>
-    <mergeCell ref="E24:H24"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:H26"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:K19"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I23:K23"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="A1:M2"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="E12:H12"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="E11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="E18:H18"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="E14:H14"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="I13:K13"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="I42:K42"/>
+    <mergeCell ref="I43:K43"/>
+    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="I37:K37"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I41:K41"/>
+    <mergeCell ref="I28:K28"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I65:K65"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="I58:K58"/>
+    <mergeCell ref="I59:K59"/>
+    <mergeCell ref="I60:K60"/>
+    <mergeCell ref="I61:K61"/>
+    <mergeCell ref="I72:K72"/>
+    <mergeCell ref="I73:K73"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I76:K76"/>
+    <mergeCell ref="I67:K67"/>
+    <mergeCell ref="I68:K68"/>
+    <mergeCell ref="I69:K69"/>
+    <mergeCell ref="I70:K70"/>
+    <mergeCell ref="I71:K71"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I77:K77"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I79:K79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="L4:L100">
@@ -5355,148 +5355,140 @@
   <sheetData>
     <row r="1" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
       <c r="E2" s="24"/>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="65" t="s">
         <v>163</v>
       </c>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="63"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="67"/>
       <c r="M2" s="24"/>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="64" t="s">
         <v>162</v>
       </c>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
+      <c r="O2" s="64"/>
+      <c r="P2" s="64"/>
     </row>
     <row r="3" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="59" t="e" vm="1">
+      <c r="B3" s="63" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
       <c r="E3" s="23"/>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="70" t="s">
         <v>164</v>
       </c>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="70"/>
       <c r="I3" s="23"/>
-      <c r="J3" s="67" t="s">
+      <c r="J3" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
+      <c r="K3" s="70"/>
+      <c r="L3" s="70"/>
       <c r="M3" s="23"/>
-      <c r="N3" s="59" t="e" vm="2">
+      <c r="N3" s="63" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="O3" s="59"/>
-      <c r="P3" s="59"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
     </row>
     <row r="4" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="59"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
       <c r="E4" s="23"/>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="70" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
       <c r="I4" s="23"/>
-      <c r="J4" s="67" t="s">
+      <c r="J4" s="70" t="s">
         <v>168</v>
       </c>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
       <c r="M4" s="23"/>
-      <c r="N4" s="59"/>
-      <c r="O4" s="59"/>
-      <c r="P4" s="59"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
     </row>
     <row r="5" spans="2:16" ht="159.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="68" t="s">
         <v>166</v>
       </c>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="66"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="69"/>
       <c r="M5" s="23"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
+      <c r="N5" s="63"/>
+      <c r="O5" s="63"/>
+      <c r="P5" s="63"/>
     </row>
     <row r="6" spans="2:16" s="22" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:16" x14ac:dyDescent="0.3">
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="59" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
     </row>
     <row r="9" spans="2:16" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="69" t="s">
+      <c r="B9" s="60" t="s">
         <v>175</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="65" t="s">
+      <c r="C9" s="60"/>
+      <c r="D9" s="61" t="s">
         <v>184</v>
       </c>
-      <c r="E9" s="65"/>
-      <c r="F9" s="65"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
     </row>
     <row r="10" spans="2:16" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="65" t="s">
+      <c r="B10" s="61" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="65" t="s">
+      <c r="C10" s="61"/>
+      <c r="D10" s="61" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" spans="2:16" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="65" t="s">
+      <c r="B11" s="61" t="s">
         <v>183</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="70" t="s">
+      <c r="C11" s="61"/>
+      <c r="D11" s="62" t="s">
         <v>189</v>
       </c>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="D11:F11"/>
     <mergeCell ref="N3:P5"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="F2:L2"/>
@@ -5507,6 +5499,14 @@
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="J3:L3"/>
     <mergeCell ref="J4:L4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
